--- a/Pedidos.xlsx
+++ b/Pedidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B776ED7-DE7D-48FE-8F89-DE93555DD4E9}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E7C086B-C609-4997-9B19-8945AF0A6DDF}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
   </bookViews>
@@ -1978,9 +1978,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2026,7 +2028,11 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
@@ -2053,8 +2059,8 @@
     <tableColumn id="4" xr3:uid="{09C6AB47-50A6-4A77-84E1-F9C46CEFB0BA}" name="UF"/>
     <tableColumn id="5" xr3:uid="{60CC8499-AF85-4A3E-B15F-FAC268AEA396}" name="Status"/>
     <tableColumn id="6" xr3:uid="{A7B89925-D806-422B-A861-E9CDD8B38B51}" name="Motivo"/>
-    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão"/>
-    <tableColumn id="8" xr3:uid="{81A912E1-0DAE-4094-8FC5-6F9C3F7FEA4E}" name="Valor (R$)" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{81A912E1-0DAE-4094-8FC5-6F9C3F7FEA4E}" name="Valor (R$)" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2386,8 +2392,8 @@
     <col min="4" max="4" width="5.42578125" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2409,10 +2415,10 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2435,10 +2441,10 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>355.83</v>
       </c>
     </row>
@@ -2461,10 +2467,10 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>373.34</v>
       </c>
     </row>
@@ -2487,10 +2493,10 @@
       <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>507.83</v>
       </c>
     </row>
@@ -2513,10 +2519,10 @@
       <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>507.83</v>
       </c>
     </row>
@@ -2539,10 +2545,10 @@
       <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>507.83</v>
       </c>
     </row>
@@ -2565,10 +2571,10 @@
       <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>281.19</v>
       </c>
     </row>
@@ -2591,10 +2597,10 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>1570.81</v>
       </c>
     </row>
@@ -2617,10 +2623,10 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>430.57</v>
       </c>
     </row>
@@ -2643,10 +2649,10 @@
       <c r="F10" t="s">
         <v>10</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>1699.14</v>
       </c>
     </row>
@@ -2669,10 +2675,10 @@
       <c r="F11" t="s">
         <v>10</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>4800.8100000000004</v>
       </c>
     </row>
@@ -2695,10 +2701,10 @@
       <c r="F12" t="s">
         <v>26</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <v>1007.72</v>
       </c>
     </row>
@@ -2721,10 +2727,10 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <v>1316.93</v>
       </c>
     </row>
@@ -2747,10 +2753,10 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <v>87.45</v>
       </c>
     </row>
@@ -2773,10 +2779,10 @@
       <c r="F15" t="s">
         <v>10</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="3">
         <v>46149</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <v>5197.59</v>
       </c>
     </row>
@@ -2799,10 +2805,10 @@
       <c r="F16" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <v>7664.2</v>
       </c>
     </row>
@@ -2825,10 +2831,10 @@
       <c r="F17" t="s">
         <v>28</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="3">
         <v>46148</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <v>1895.4</v>
       </c>
     </row>
@@ -2851,10 +2857,10 @@
       <c r="F18" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="3">
         <v>46148</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <v>1871.58</v>
       </c>
     </row>
@@ -2877,10 +2883,10 @@
       <c r="F19" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="3">
         <v>46148</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <v>2117.79</v>
       </c>
     </row>
@@ -2903,10 +2909,10 @@
       <c r="F20" t="s">
         <v>28</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="3">
         <v>46148</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="2">
         <v>1119.93</v>
       </c>
     </row>
@@ -2929,10 +2935,10 @@
       <c r="F21" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="2">
         <v>5471.86</v>
       </c>
     </row>
@@ -2955,10 +2961,10 @@
       <c r="F22" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="3">
         <v>46148</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="2">
         <v>4611.8</v>
       </c>
     </row>
@@ -2981,10 +2987,10 @@
       <c r="F23" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="3">
         <v>46148</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="2">
         <v>2331.81</v>
       </c>
     </row>
@@ -3007,10 +3013,10 @@
       <c r="F24" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="3">
         <v>46148</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="2">
         <v>742.4</v>
       </c>
     </row>
@@ -3033,10 +3039,10 @@
       <c r="F25" t="s">
         <v>31</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="2">
         <v>7798.72</v>
       </c>
     </row>
@@ -3059,10 +3065,10 @@
       <c r="F26" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="3">
         <v>46148</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="2">
         <v>2132.04</v>
       </c>
     </row>
@@ -3085,10 +3091,10 @@
       <c r="F27" t="s">
         <v>20</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="2">
         <v>2082.5100000000002</v>
       </c>
     </row>
@@ -3111,10 +3117,10 @@
       <c r="F28" t="s">
         <v>28</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <v>46148</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="2">
         <v>1076.29</v>
       </c>
     </row>
@@ -3137,10 +3143,10 @@
       <c r="F29" t="s">
         <v>28</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <v>46148</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="2">
         <v>3552.33</v>
       </c>
     </row>
@@ -3163,10 +3169,10 @@
       <c r="F30" t="s">
         <v>28</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <v>46148</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="2">
         <v>1117.04</v>
       </c>
     </row>
@@ -3189,10 +3195,10 @@
       <c r="F31" t="s">
         <v>31</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="2">
         <v>1565.3</v>
       </c>
     </row>
@@ -3215,10 +3221,10 @@
       <c r="F32" t="s">
         <v>38</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <v>46149</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <v>2824.8</v>
       </c>
     </row>
@@ -3241,10 +3247,10 @@
       <c r="F33" t="s">
         <v>10</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="2">
         <v>1677.89</v>
       </c>
     </row>
@@ -3267,10 +3273,10 @@
       <c r="F34" t="s">
         <v>10</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="2">
         <v>4754.2</v>
       </c>
     </row>
@@ -3293,10 +3299,10 @@
       <c r="F35" t="s">
         <v>10</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="2">
         <v>4754.2</v>
       </c>
     </row>
@@ -3319,10 +3325,10 @@
       <c r="F36" t="s">
         <v>10</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="2">
         <v>1188.55</v>
       </c>
     </row>
@@ -3345,10 +3351,10 @@
       <c r="F37" t="s">
         <v>10</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="2">
         <v>1188.55</v>
       </c>
     </row>
@@ -3371,10 +3377,10 @@
       <c r="F38" t="s">
         <v>10</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="2">
         <v>4754.2</v>
       </c>
     </row>
@@ -3397,10 +3403,10 @@
       <c r="F39" t="s">
         <v>10</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="2">
         <v>3835.17</v>
       </c>
     </row>
@@ -3423,10 +3429,10 @@
       <c r="F40" t="s">
         <v>10</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="2">
         <v>3835.17</v>
       </c>
     </row>
@@ -3449,10 +3455,10 @@
       <c r="F41" t="s">
         <v>10</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="2">
         <v>3835.17</v>
       </c>
     </row>
@@ -3475,10 +3481,10 @@
       <c r="F42" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="2">
         <v>2718.57</v>
       </c>
     </row>
@@ -3501,10 +3507,10 @@
       <c r="F43" t="s">
         <v>10</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="2">
         <v>4158.87</v>
       </c>
     </row>
@@ -3527,10 +3533,10 @@
       <c r="F44" t="s">
         <v>38</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <v>46149</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="2">
         <v>1138.58</v>
       </c>
     </row>
@@ -3553,10 +3559,10 @@
       <c r="F45" t="s">
         <v>38</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <v>46149</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="2">
         <v>1797.82</v>
       </c>
     </row>
@@ -3579,10 +3585,10 @@
       <c r="F46" t="s">
         <v>43</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="2">
         <v>5139.2700000000004</v>
       </c>
     </row>
@@ -3605,10 +3611,10 @@
       <c r="F47" t="s">
         <v>46</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <v>46153</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="2">
         <v>7060.01</v>
       </c>
     </row>
@@ -3631,10 +3637,10 @@
       <c r="F48" t="s">
         <v>10</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="2">
         <v>139.09</v>
       </c>
     </row>
@@ -3657,10 +3663,10 @@
       <c r="F49" t="s">
         <v>10</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="2">
         <v>278.18</v>
       </c>
     </row>
@@ -3683,10 +3689,10 @@
       <c r="F50" t="s">
         <v>10</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="2">
         <v>278.18</v>
       </c>
     </row>
@@ -3709,10 +3715,10 @@
       <c r="F51" t="s">
         <v>10</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="2">
         <v>278.18</v>
       </c>
     </row>
@@ -3735,10 +3741,10 @@
       <c r="F52" t="s">
         <v>10</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="2">
         <v>139.09</v>
       </c>
     </row>
@@ -3761,10 +3767,10 @@
       <c r="F53" t="s">
         <v>50</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G53" s="3">
         <v>46149</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="2">
         <v>2249.8000000000002</v>
       </c>
     </row>
@@ -3787,10 +3793,10 @@
       <c r="F54" t="s">
         <v>14</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <v>46149</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="2">
         <v>143022.59</v>
       </c>
     </row>
@@ -3813,10 +3819,10 @@
       <c r="F55" t="s">
         <v>14</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <v>46149</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55" s="2">
         <v>92986.37</v>
       </c>
     </row>
@@ -3839,10 +3845,10 @@
       <c r="F56" t="s">
         <v>14</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <v>46149</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56" s="2">
         <v>126974.77</v>
       </c>
     </row>
@@ -3865,10 +3871,10 @@
       <c r="F57" t="s">
         <v>14</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <v>46149</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="2">
         <v>174088.36</v>
       </c>
     </row>
@@ -3891,10 +3897,10 @@
       <c r="F58" t="s">
         <v>10</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="2">
         <v>278.18</v>
       </c>
     </row>
@@ -3917,10 +3923,10 @@
       <c r="F59" t="s">
         <v>10</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="2">
         <v>139.09</v>
       </c>
     </row>
@@ -3943,10 +3949,10 @@
       <c r="F60" t="s">
         <v>10</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60" s="2">
         <v>304.23</v>
       </c>
     </row>
@@ -3969,10 +3975,10 @@
       <c r="F61" t="s">
         <v>10</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61" s="2">
         <v>278.18</v>
       </c>
     </row>
@@ -3995,10 +4001,10 @@
       <c r="F62" t="s">
         <v>10</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="2">
         <v>152.11000000000001</v>
       </c>
     </row>
@@ -4021,10 +4027,10 @@
       <c r="F63" t="s">
         <v>14</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <v>46149</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63" s="2">
         <v>1609.29</v>
       </c>
     </row>
@@ -4047,10 +4053,10 @@
       <c r="F64" t="s">
         <v>10</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="3">
         <v>46153</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H64" s="2">
         <v>14956.83</v>
       </c>
     </row>
@@ -4073,10 +4079,10 @@
       <c r="F65" t="s">
         <v>10</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65" s="2">
         <v>304.23</v>
       </c>
     </row>
@@ -4099,10 +4105,10 @@
       <c r="F66" t="s">
         <v>14</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="3">
         <v>46149</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H66" s="2">
         <v>1003.73</v>
       </c>
     </row>
@@ -4125,10 +4131,10 @@
       <c r="F67" t="s">
         <v>14</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="3">
         <v>46149</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67" s="2">
         <v>1278.51</v>
       </c>
     </row>
@@ -4151,10 +4157,10 @@
       <c r="F68" t="s">
         <v>10</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H68" s="2">
         <v>2952.16</v>
       </c>
     </row>
@@ -4177,10 +4183,10 @@
       <c r="F69" t="s">
         <v>10</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H69" s="2">
         <v>275948.40999999997</v>
       </c>
     </row>
@@ -4203,10 +4209,10 @@
       <c r="F70" t="s">
         <v>14</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="3">
         <v>46149</v>
       </c>
-      <c r="H70" s="3">
+      <c r="H70" s="2">
         <v>1062.9000000000001</v>
       </c>
     </row>
@@ -4229,10 +4235,10 @@
       <c r="F71" t="s">
         <v>28</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="3">
         <v>46148</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H71" s="2">
         <v>13095.84</v>
       </c>
     </row>
@@ -4255,10 +4261,10 @@
       <c r="F72" t="s">
         <v>14</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="3">
         <v>46149</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="2">
         <v>1437.46</v>
       </c>
     </row>
@@ -4281,10 +4287,10 @@
       <c r="F73" t="s">
         <v>14</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="3">
         <v>46149</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73" s="2">
         <v>531.45000000000005</v>
       </c>
     </row>
@@ -4307,10 +4313,10 @@
       <c r="F74" t="s">
         <v>14</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="3">
         <v>46149</v>
       </c>
-      <c r="H74" s="3">
+      <c r="H74" s="2">
         <v>239.58</v>
       </c>
     </row>
@@ -4333,10 +4339,10 @@
       <c r="F75" t="s">
         <v>14</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="3">
         <v>46149</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75" s="2">
         <v>470.98</v>
       </c>
     </row>
@@ -4359,10 +4365,10 @@
       <c r="F76" t="s">
         <v>14</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="3">
         <v>46149</v>
       </c>
-      <c r="H76" s="3">
+      <c r="H76" s="2">
         <v>1197.8800000000001</v>
       </c>
     </row>
@@ -4385,10 +4391,10 @@
       <c r="F77" t="s">
         <v>14</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="3">
         <v>46149</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H77" s="2">
         <v>1197.8800000000001</v>
       </c>
     </row>
@@ -4411,10 +4417,10 @@
       <c r="F78" t="s">
         <v>28</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="3">
         <v>46148</v>
       </c>
-      <c r="H78" s="3">
+      <c r="H78" s="2">
         <v>2394</v>
       </c>
     </row>
@@ -4437,10 +4443,10 @@
       <c r="F79" t="s">
         <v>14</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="3">
         <v>46149</v>
       </c>
-      <c r="H79" s="3">
+      <c r="H79" s="2">
         <v>479.15</v>
       </c>
     </row>
@@ -4463,10 +4469,10 @@
       <c r="F80" t="s">
         <v>14</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="3">
         <v>46149</v>
       </c>
-      <c r="H80" s="3">
+      <c r="H80" s="2">
         <v>479.15</v>
       </c>
     </row>
@@ -4489,10 +4495,10 @@
       <c r="F81" t="s">
         <v>14</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="3">
         <v>46149</v>
       </c>
-      <c r="H81" s="3">
+      <c r="H81" s="2">
         <v>479.15</v>
       </c>
     </row>
@@ -4515,10 +4521,10 @@
       <c r="F82" t="s">
         <v>28</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="3">
         <v>46148</v>
       </c>
-      <c r="H82" s="3">
+      <c r="H82" s="2">
         <v>2704.07</v>
       </c>
     </row>
@@ -4541,10 +4547,10 @@
       <c r="F83" t="s">
         <v>14</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="3">
         <v>46149</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="2">
         <v>494.78</v>
       </c>
     </row>
@@ -4567,10 +4573,10 @@
       <c r="F84" t="s">
         <v>14</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="3">
         <v>46149</v>
       </c>
-      <c r="H84" s="3">
+      <c r="H84" s="2">
         <v>1236.95</v>
       </c>
     </row>
@@ -4593,10 +4599,10 @@
       <c r="F85" t="s">
         <v>14</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="3">
         <v>46149</v>
       </c>
-      <c r="H85" s="3">
+      <c r="H85" s="2">
         <v>277.42</v>
       </c>
     </row>
@@ -4619,10 +4625,10 @@
       <c r="F86" t="s">
         <v>14</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="3">
         <v>46149</v>
       </c>
-      <c r="H86" s="3">
+      <c r="H86" s="2">
         <v>1009.75</v>
       </c>
     </row>
@@ -4645,10 +4651,10 @@
       <c r="F87" t="s">
         <v>14</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="3">
         <v>46149</v>
       </c>
-      <c r="H87" s="3">
+      <c r="H87" s="2">
         <v>246.67</v>
       </c>
     </row>
@@ -4671,10 +4677,10 @@
       <c r="F88" t="s">
         <v>14</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="3">
         <v>46149</v>
       </c>
-      <c r="H88" s="3">
+      <c r="H88" s="2">
         <v>757.31</v>
       </c>
     </row>
@@ -4697,10 +4703,10 @@
       <c r="F89" t="s">
         <v>14</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="3">
         <v>46149</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="2">
         <v>1262.19</v>
       </c>
     </row>
@@ -4723,10 +4729,10 @@
       <c r="F90" t="s">
         <v>14</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="3">
         <v>46149</v>
       </c>
-      <c r="H90" s="3">
+      <c r="H90" s="2">
         <v>1009.75</v>
       </c>
     </row>
@@ -4749,10 +4755,10 @@
       <c r="F91" t="s">
         <v>10</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="3">
         <v>46151</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="2">
         <v>1401.09</v>
       </c>
     </row>
@@ -4775,10 +4781,10 @@
       <c r="F92" t="s">
         <v>14</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="3">
         <v>46149</v>
       </c>
-      <c r="H92" s="3">
+      <c r="H92" s="2">
         <v>1009.75</v>
       </c>
     </row>
@@ -4801,10 +4807,10 @@
       <c r="F93" t="s">
         <v>14</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="3">
         <v>46149</v>
       </c>
-      <c r="H93" s="3">
+      <c r="H93" s="2">
         <v>757.73</v>
       </c>
     </row>
@@ -4827,10 +4833,10 @@
       <c r="F94" t="s">
         <v>14</v>
       </c>
-      <c r="G94">
+      <c r="G94" s="3">
         <v>46149</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="2">
         <v>749.34</v>
       </c>
     </row>
@@ -4853,10 +4859,10 @@
       <c r="F95" t="s">
         <v>14</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="3">
         <v>46149</v>
       </c>
-      <c r="H95" s="3">
+      <c r="H95" s="2">
         <v>263.41000000000003</v>
       </c>
     </row>
@@ -4879,10 +4885,10 @@
       <c r="F96" t="s">
         <v>14</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="3">
         <v>46149</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="2">
         <v>1317.03</v>
       </c>
     </row>
@@ -4905,10 +4911,10 @@
       <c r="F97" t="s">
         <v>14</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="3">
         <v>46149</v>
       </c>
-      <c r="H97" s="3">
+      <c r="H97" s="2">
         <v>265.72000000000003</v>
       </c>
     </row>
@@ -4931,10 +4937,10 @@
       <c r="F98" t="s">
         <v>14</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G98" s="3">
         <v>46149</v>
       </c>
-      <c r="H98" s="3">
+      <c r="H98" s="2">
         <v>445.9</v>
       </c>
     </row>
@@ -4957,10 +4963,10 @@
       <c r="F99" t="s">
         <v>14</v>
       </c>
-      <c r="G99">
+      <c r="G99" s="3">
         <v>46149</v>
       </c>
-      <c r="H99" s="3">
+      <c r="H99" s="2">
         <v>445.9</v>
       </c>
     </row>
@@ -4983,10 +4989,10 @@
       <c r="F100" t="s">
         <v>14</v>
       </c>
-      <c r="G100">
+      <c r="G100" s="3">
         <v>46149</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="2">
         <v>268.02</v>
       </c>
     </row>
@@ -5009,10 +5015,10 @@
       <c r="F101" t="s">
         <v>14</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="3">
         <v>46149</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="2">
         <v>488.93</v>
       </c>
     </row>
@@ -5035,10 +5041,10 @@
       <c r="F102" t="s">
         <v>10</v>
       </c>
-      <c r="G102" t="s">
+      <c r="G102" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102" s="2">
         <v>180.45</v>
       </c>
     </row>
@@ -5061,10 +5067,10 @@
       <c r="F103" t="s">
         <v>14</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="3">
         <v>46149</v>
       </c>
-      <c r="H103" s="3">
+      <c r="H103" s="2">
         <v>227.17</v>
       </c>
     </row>
@@ -5087,10 +5093,10 @@
       <c r="F104" t="s">
         <v>14</v>
       </c>
-      <c r="G104">
+      <c r="G104" s="3">
         <v>46149</v>
       </c>
-      <c r="H104" s="3">
+      <c r="H104" s="2">
         <v>1341.07</v>
       </c>
     </row>
@@ -5113,10 +5119,10 @@
       <c r="F105" t="s">
         <v>14</v>
       </c>
-      <c r="G105">
+      <c r="G105" s="3">
         <v>46149</v>
       </c>
-      <c r="H105" s="3">
+      <c r="H105" s="2">
         <v>2675.52</v>
       </c>
     </row>
@@ -5139,10 +5145,10 @@
       <c r="F106" t="s">
         <v>14</v>
       </c>
-      <c r="G106">
+      <c r="G106" s="3">
         <v>46149</v>
       </c>
-      <c r="H106" s="3">
+      <c r="H106" s="2">
         <v>646.14</v>
       </c>
     </row>
@@ -5165,10 +5171,10 @@
       <c r="F107" t="s">
         <v>14</v>
       </c>
-      <c r="G107">
+      <c r="G107" s="3">
         <v>46149</v>
       </c>
-      <c r="H107" s="3">
+      <c r="H107" s="2">
         <v>1062.9000000000001</v>
       </c>
     </row>
@@ -5191,10 +5197,10 @@
       <c r="F108" t="s">
         <v>14</v>
       </c>
-      <c r="G108">
+      <c r="G108" s="3">
         <v>46149</v>
       </c>
-      <c r="H108" s="3">
+      <c r="H108" s="2">
         <v>454.34</v>
       </c>
     </row>
@@ -5217,10 +5223,10 @@
       <c r="F109" t="s">
         <v>14</v>
       </c>
-      <c r="G109">
+      <c r="G109" s="3">
         <v>46149</v>
       </c>
-      <c r="H109" s="3">
+      <c r="H109" s="2">
         <v>998.83</v>
       </c>
     </row>
@@ -5243,10 +5249,10 @@
       <c r="F110" t="s">
         <v>14</v>
       </c>
-      <c r="G110">
+      <c r="G110" s="3">
         <v>46149</v>
       </c>
-      <c r="H110" s="3">
+      <c r="H110" s="2">
         <v>1466.8</v>
       </c>
     </row>
@@ -5269,10 +5275,10 @@
       <c r="F111" t="s">
         <v>14</v>
       </c>
-      <c r="G111">
+      <c r="G111" s="3">
         <v>46149</v>
       </c>
-      <c r="H111" s="3">
+      <c r="H111" s="2">
         <v>1072.8599999999999</v>
       </c>
     </row>
@@ -5295,10 +5301,10 @@
       <c r="F112" t="s">
         <v>10</v>
       </c>
-      <c r="G112" t="s">
+      <c r="G112" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H112" s="3">
+      <c r="H112" s="2">
         <v>584.91999999999996</v>
       </c>
     </row>
@@ -5321,10 +5327,10 @@
       <c r="F113" t="s">
         <v>14</v>
       </c>
-      <c r="G113">
+      <c r="G113" s="3">
         <v>46149</v>
       </c>
-      <c r="H113" s="3">
+      <c r="H113" s="2">
         <v>92.7</v>
       </c>
     </row>
@@ -5347,10 +5353,10 @@
       <c r="F114" t="s">
         <v>14</v>
       </c>
-      <c r="G114">
+      <c r="G114" s="3">
         <v>46149</v>
       </c>
-      <c r="H114" s="3">
+      <c r="H114" s="2">
         <v>1062.9000000000001</v>
       </c>
     </row>
@@ -5373,10 +5379,10 @@
       <c r="F115" t="s">
         <v>28</v>
       </c>
-      <c r="G115">
+      <c r="G115" s="3">
         <v>46148</v>
       </c>
-      <c r="H115" s="3">
+      <c r="H115" s="2">
         <v>1222.33</v>
       </c>
     </row>
@@ -5399,10 +5405,10 @@
       <c r="F116" t="s">
         <v>28</v>
       </c>
-      <c r="G116">
+      <c r="G116" s="3">
         <v>46148</v>
       </c>
-      <c r="H116" s="3">
+      <c r="H116" s="2">
         <v>1877.5</v>
       </c>
     </row>
@@ -5425,10 +5431,10 @@
       <c r="F117" t="s">
         <v>14</v>
       </c>
-      <c r="G117">
+      <c r="G117" s="3">
         <v>46149</v>
       </c>
-      <c r="H117" s="3">
+      <c r="H117" s="2">
         <v>749.12</v>
       </c>
     </row>
@@ -5451,10 +5457,10 @@
       <c r="F118" t="s">
         <v>14</v>
       </c>
-      <c r="G118">
+      <c r="G118" s="3">
         <v>46149</v>
       </c>
-      <c r="H118" s="3">
+      <c r="H118" s="2">
         <v>1363.02</v>
       </c>
     </row>
@@ -5477,10 +5483,10 @@
       <c r="F119" t="s">
         <v>14</v>
       </c>
-      <c r="G119">
+      <c r="G119" s="3">
         <v>46149</v>
       </c>
-      <c r="H119" s="3">
+      <c r="H119" s="2">
         <v>840.6</v>
       </c>
     </row>
@@ -5503,10 +5509,10 @@
       <c r="F120" t="s">
         <v>14</v>
       </c>
-      <c r="G120" s="1">
+      <c r="G120" s="3">
         <v>46149</v>
       </c>
-      <c r="H120" s="3">
+      <c r="H120" s="2">
         <v>559.62</v>
       </c>
     </row>
@@ -5529,10 +5535,10 @@
       <c r="F121" t="s">
         <v>14</v>
       </c>
-      <c r="G121">
+      <c r="G121" s="3">
         <v>46149</v>
       </c>
-      <c r="H121" s="3">
+      <c r="H121" s="2">
         <v>1932.44</v>
       </c>
     </row>
@@ -5555,10 +5561,10 @@
       <c r="F122" t="s">
         <v>10</v>
       </c>
-      <c r="G122" t="s">
+      <c r="G122" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H122" s="3">
+      <c r="H122" s="2">
         <v>188.17</v>
       </c>
     </row>
@@ -5581,10 +5587,10 @@
       <c r="F123" t="s">
         <v>46</v>
       </c>
-      <c r="G123">
+      <c r="G123" s="3">
         <v>46167</v>
       </c>
-      <c r="H123" s="3">
+      <c r="H123" s="2">
         <v>4679.57</v>
       </c>
     </row>
@@ -5607,10 +5613,10 @@
       <c r="F124" t="s">
         <v>46</v>
       </c>
-      <c r="G124" t="s">
+      <c r="G124" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H124" s="3">
+      <c r="H124" s="2">
         <v>4679.57</v>
       </c>
     </row>
@@ -5633,10 +5639,10 @@
       <c r="F125" t="s">
         <v>14</v>
       </c>
-      <c r="G125">
+      <c r="G125" s="3">
         <v>46149</v>
       </c>
-      <c r="H125" s="3">
+      <c r="H125" s="2">
         <v>1148.1099999999999</v>
       </c>
     </row>
@@ -5659,10 +5665,10 @@
       <c r="F126" t="s">
         <v>50</v>
       </c>
-      <c r="G126">
+      <c r="G126" s="3">
         <v>46154</v>
       </c>
-      <c r="H126" s="3">
+      <c r="H126" s="2">
         <v>7593.16</v>
       </c>
     </row>
@@ -5685,10 +5691,10 @@
       <c r="F127" t="s">
         <v>10</v>
       </c>
-      <c r="G127" t="s">
+      <c r="G127" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H127" s="3">
+      <c r="H127" s="2">
         <v>4748.58</v>
       </c>
     </row>
@@ -5711,10 +5717,10 @@
       <c r="F128" t="s">
         <v>50</v>
       </c>
-      <c r="G128" t="s">
+      <c r="G128" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H128" s="3">
+      <c r="H128" s="2">
         <v>20730.54</v>
       </c>
     </row>
@@ -5737,10 +5743,10 @@
       <c r="F129" t="s">
         <v>10</v>
       </c>
-      <c r="G129" t="s">
+      <c r="G129" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H129" s="3">
+      <c r="H129" s="2">
         <v>7101.86</v>
       </c>
     </row>
@@ -5763,10 +5769,10 @@
       <c r="F130" t="s">
         <v>10</v>
       </c>
-      <c r="G130" t="s">
+      <c r="G130" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H130" s="3">
+      <c r="H130" s="2">
         <v>1554.84</v>
       </c>
     </row>
@@ -5789,10 +5795,10 @@
       <c r="F131" t="s">
         <v>50</v>
       </c>
-      <c r="G131">
+      <c r="G131" s="3">
         <v>46153</v>
       </c>
-      <c r="H131" s="3">
+      <c r="H131" s="2">
         <v>15909.49</v>
       </c>
     </row>
@@ -5815,10 +5821,10 @@
       <c r="F132" t="s">
         <v>10</v>
       </c>
-      <c r="G132" t="s">
+      <c r="G132" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H132" s="3">
+      <c r="H132" s="2">
         <v>7227.93</v>
       </c>
     </row>
@@ -5841,10 +5847,10 @@
       <c r="F133" t="s">
         <v>10</v>
       </c>
-      <c r="G133" t="s">
+      <c r="G133" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H133" s="3">
+      <c r="H133" s="2">
         <v>2713.5</v>
       </c>
     </row>
@@ -5867,10 +5873,10 @@
       <c r="F134" t="s">
         <v>10</v>
       </c>
-      <c r="G134">
+      <c r="G134" s="3">
         <v>46148</v>
       </c>
-      <c r="H134" s="3">
+      <c r="H134" s="2">
         <v>12055.96</v>
       </c>
     </row>
@@ -5893,10 +5899,10 @@
       <c r="F135" t="s">
         <v>115</v>
       </c>
-      <c r="G135">
+      <c r="G135" s="3">
         <v>46171</v>
       </c>
-      <c r="H135" s="3">
+      <c r="H135" s="2">
         <v>12055.96</v>
       </c>
     </row>
@@ -5919,10 +5925,10 @@
       <c r="F136" t="s">
         <v>14</v>
       </c>
-      <c r="G136">
+      <c r="G136" s="3">
         <v>46149</v>
       </c>
-      <c r="H136" s="3">
+      <c r="H136" s="2">
         <v>1329</v>
       </c>
     </row>
@@ -5945,10 +5951,10 @@
       <c r="F137" t="s">
         <v>20</v>
       </c>
-      <c r="G137">
+      <c r="G137" s="3">
         <v>46149</v>
       </c>
-      <c r="H137" s="3">
+      <c r="H137" s="2">
         <v>4001.13</v>
       </c>
     </row>
@@ -5971,10 +5977,10 @@
       <c r="F138" t="s">
         <v>28</v>
       </c>
-      <c r="G138">
+      <c r="G138" s="3">
         <v>46148</v>
       </c>
-      <c r="H138" s="3">
+      <c r="H138" s="2">
         <v>4825.58</v>
       </c>
     </row>
@@ -5997,10 +6003,10 @@
       <c r="F139" t="s">
         <v>50</v>
       </c>
-      <c r="G139">
+      <c r="G139" s="3">
         <v>46150</v>
       </c>
-      <c r="H139" s="3">
+      <c r="H139" s="2">
         <v>16603.72</v>
       </c>
     </row>
@@ -6023,10 +6029,10 @@
       <c r="F140" t="s">
         <v>10</v>
       </c>
-      <c r="G140" t="s">
+      <c r="G140" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H140" s="3">
+      <c r="H140" s="2">
         <v>152.11000000000001</v>
       </c>
     </row>
@@ -6049,10 +6055,10 @@
       <c r="F141" t="s">
         <v>10</v>
       </c>
-      <c r="G141" t="s">
+      <c r="G141" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H141" s="3">
+      <c r="H141" s="2">
         <v>139.09</v>
       </c>
     </row>
@@ -6075,10 +6081,10 @@
       <c r="F142" t="s">
         <v>10</v>
       </c>
-      <c r="G142" t="s">
+      <c r="G142" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H142" s="3">
+      <c r="H142" s="2">
         <v>139.09</v>
       </c>
     </row>
@@ -6101,10 +6107,10 @@
       <c r="F143" t="s">
         <v>10</v>
       </c>
-      <c r="G143" t="s">
+      <c r="G143" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H143" s="3">
+      <c r="H143" s="2">
         <v>152.11000000000001</v>
       </c>
     </row>
@@ -6127,10 +6133,10 @@
       <c r="F144" t="s">
         <v>50</v>
       </c>
-      <c r="G144" t="s">
+      <c r="G144" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H144" s="3">
+      <c r="H144" s="2">
         <v>153277.92000000001</v>
       </c>
     </row>
@@ -6153,10 +6159,10 @@
       <c r="F145" t="s">
         <v>50</v>
       </c>
-      <c r="G145" t="s">
+      <c r="G145" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H145" s="3">
+      <c r="H145" s="2">
         <v>162401.60000000001</v>
       </c>
     </row>
@@ -6179,10 +6185,10 @@
       <c r="F146" t="s">
         <v>50</v>
       </c>
-      <c r="G146">
+      <c r="G146" s="3">
         <v>46171</v>
       </c>
-      <c r="H146" s="3">
+      <c r="H146" s="2">
         <v>28950.21</v>
       </c>
     </row>
@@ -6205,10 +6211,10 @@
       <c r="F147" t="s">
         <v>10</v>
       </c>
-      <c r="G147">
+      <c r="G147" s="3">
         <v>46149</v>
       </c>
-      <c r="H147" s="3">
+      <c r="H147" s="2">
         <v>31786.92</v>
       </c>
     </row>
@@ -6231,10 +6237,10 @@
       <c r="F148" t="s">
         <v>46</v>
       </c>
-      <c r="G148">
+      <c r="G148" s="3">
         <v>46171</v>
       </c>
-      <c r="H148" s="3">
+      <c r="H148" s="2">
         <v>31786.92</v>
       </c>
     </row>
@@ -6257,10 +6263,10 @@
       <c r="F149" t="s">
         <v>10</v>
       </c>
-      <c r="G149">
+      <c r="G149" s="3">
         <v>46148</v>
       </c>
-      <c r="H149" s="3">
+      <c r="H149" s="2">
         <v>49116.3</v>
       </c>
     </row>
@@ -6283,10 +6289,10 @@
       <c r="F150" t="s">
         <v>50</v>
       </c>
-      <c r="G150">
+      <c r="G150" s="3">
         <v>46171</v>
       </c>
-      <c r="H150" s="3">
+      <c r="H150" s="2">
         <v>44204.67</v>
       </c>
     </row>
@@ -6309,10 +6315,10 @@
       <c r="F151" t="s">
         <v>50</v>
       </c>
-      <c r="G151">
+      <c r="G151" s="3">
         <v>46149</v>
       </c>
-      <c r="H151" s="3">
+      <c r="H151" s="2">
         <v>21503.15</v>
       </c>
     </row>
@@ -6335,10 +6341,10 @@
       <c r="F152" t="s">
         <v>14</v>
       </c>
-      <c r="G152">
+      <c r="G152" s="3">
         <v>46149</v>
       </c>
-      <c r="H152" s="3">
+      <c r="H152" s="2">
         <v>844.75</v>
       </c>
     </row>
@@ -6361,10 +6367,10 @@
       <c r="F153" t="s">
         <v>10</v>
       </c>
-      <c r="G153" t="s">
+      <c r="G153" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H153" s="3">
+      <c r="H153" s="2">
         <v>139.09</v>
       </c>
     </row>
@@ -6387,10 +6393,10 @@
       <c r="F154" t="s">
         <v>10</v>
       </c>
-      <c r="G154" t="s">
+      <c r="G154" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H154" s="3">
+      <c r="H154" s="2">
         <v>139.09</v>
       </c>
     </row>
@@ -6413,10 +6419,10 @@
       <c r="F155" t="s">
         <v>10</v>
       </c>
-      <c r="G155" t="s">
+      <c r="G155" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H155" s="3">
+      <c r="H155" s="2">
         <v>139.09</v>
       </c>
     </row>
@@ -6439,10 +6445,10 @@
       <c r="F156" t="s">
         <v>20</v>
       </c>
-      <c r="G156" s="1">
+      <c r="G156" s="3">
         <v>46149</v>
       </c>
-      <c r="H156" s="3">
+      <c r="H156" s="2">
         <v>3127.96</v>
       </c>
     </row>
@@ -6465,10 +6471,10 @@
       <c r="F157" t="s">
         <v>14</v>
       </c>
-      <c r="G157">
+      <c r="G157" s="3">
         <v>46149</v>
       </c>
-      <c r="H157" s="3">
+      <c r="H157" s="2">
         <v>827.49</v>
       </c>
     </row>
@@ -6491,10 +6497,10 @@
       <c r="F158" t="s">
         <v>10</v>
       </c>
-      <c r="G158" t="s">
+      <c r="G158" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H158" s="3">
+      <c r="H158" s="2">
         <v>152.11000000000001</v>
       </c>
     </row>
@@ -6517,10 +6523,10 @@
       <c r="F159" t="s">
         <v>10</v>
       </c>
-      <c r="G159" t="s">
+      <c r="G159" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H159" s="3">
+      <c r="H159" s="2">
         <v>152.11000000000001</v>
       </c>
     </row>
@@ -6543,10 +6549,10 @@
       <c r="F160" t="s">
         <v>10</v>
       </c>
-      <c r="G160" t="s">
+      <c r="G160" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H160" s="3">
+      <c r="H160" s="2">
         <v>152.11000000000001</v>
       </c>
     </row>
@@ -6569,10 +6575,10 @@
       <c r="F161" t="s">
         <v>31</v>
       </c>
-      <c r="G161" t="s">
+      <c r="G161" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H161" s="3">
+      <c r="H161" s="2">
         <v>275.95</v>
       </c>
     </row>
@@ -6595,10 +6601,10 @@
       <c r="F162" t="s">
         <v>28</v>
       </c>
-      <c r="G162">
+      <c r="G162" s="3">
         <v>46148</v>
       </c>
-      <c r="H162" s="3">
+      <c r="H162" s="2">
         <v>703.96</v>
       </c>
     </row>
@@ -6621,10 +6627,10 @@
       <c r="F163" t="s">
         <v>10</v>
       </c>
-      <c r="G163" s="1" t="s">
+      <c r="G163" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H163" s="3">
+      <c r="H163" s="2">
         <v>152.11000000000001</v>
       </c>
     </row>
@@ -6647,10 +6653,10 @@
       <c r="F164" t="s">
         <v>10</v>
       </c>
-      <c r="G164" t="s">
+      <c r="G164" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H164" s="3">
+      <c r="H164" s="2">
         <v>278.18</v>
       </c>
     </row>
@@ -6673,10 +6679,10 @@
       <c r="F165" t="s">
         <v>20</v>
       </c>
-      <c r="G165">
+      <c r="G165" s="3">
         <v>46149</v>
       </c>
-      <c r="H165" s="3">
+      <c r="H165" s="2">
         <v>14556.39</v>
       </c>
     </row>
@@ -6699,10 +6705,10 @@
       <c r="F166" t="s">
         <v>14</v>
       </c>
-      <c r="G166">
+      <c r="G166" s="3">
         <v>46149</v>
       </c>
-      <c r="H166" s="3">
+      <c r="H166" s="2">
         <v>805.13</v>
       </c>
     </row>
@@ -6725,10 +6731,10 @@
       <c r="F167" t="s">
         <v>14</v>
       </c>
-      <c r="G167">
+      <c r="G167" s="3">
         <v>46149</v>
       </c>
-      <c r="H167" s="3">
+      <c r="H167" s="2">
         <v>10373.65</v>
       </c>
     </row>
@@ -6751,10 +6757,10 @@
       <c r="F168" t="s">
         <v>50</v>
       </c>
-      <c r="G168">
+      <c r="G168" s="3">
         <v>46150</v>
       </c>
-      <c r="H168" s="3">
+      <c r="H168" s="2">
         <v>11722.62</v>
       </c>
     </row>
@@ -6777,10 +6783,10 @@
       <c r="F169" t="s">
         <v>10</v>
       </c>
-      <c r="G169" t="s">
+      <c r="G169" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H169" s="3">
+      <c r="H169" s="2">
         <v>237.46</v>
       </c>
     </row>
@@ -6803,10 +6809,10 @@
       <c r="F170" t="s">
         <v>50</v>
       </c>
-      <c r="G170" t="s">
+      <c r="G170" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H170" s="3">
+      <c r="H170" s="2">
         <v>10034.64</v>
       </c>
     </row>
@@ -6829,10 +6835,10 @@
       <c r="F171" t="s">
         <v>10</v>
       </c>
-      <c r="G171" t="s">
+      <c r="G171" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H171" s="3">
+      <c r="H171" s="2">
         <v>60.61</v>
       </c>
     </row>
@@ -6855,10 +6861,10 @@
       <c r="F172" t="s">
         <v>50</v>
       </c>
-      <c r="G172" s="1" t="s">
+      <c r="G172" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H172" s="3">
+      <c r="H172" s="2">
         <v>38762.660000000003</v>
       </c>
     </row>
@@ -6881,10 +6887,10 @@
       <c r="F173" t="s">
         <v>50</v>
       </c>
-      <c r="G173" s="1" t="s">
+      <c r="G173" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H173" s="3">
+      <c r="H173" s="2">
         <v>38772.480000000003</v>
       </c>
     </row>
@@ -6907,10 +6913,10 @@
       <c r="F174" t="s">
         <v>85</v>
       </c>
-      <c r="G174">
+      <c r="G174" s="3">
         <v>46149</v>
       </c>
-      <c r="H174" s="3">
+      <c r="H174" s="2">
         <v>5327.99</v>
       </c>
     </row>
@@ -6933,10 +6939,10 @@
       <c r="F175" t="s">
         <v>14</v>
       </c>
-      <c r="G175">
+      <c r="G175" s="3">
         <v>46149</v>
       </c>
-      <c r="H175" s="3">
+      <c r="H175" s="2">
         <v>267.39</v>
       </c>
     </row>
@@ -6959,10 +6965,10 @@
       <c r="F176" t="s">
         <v>20</v>
       </c>
-      <c r="G176">
+      <c r="G176" s="3">
         <v>46149</v>
       </c>
-      <c r="H176" s="3">
+      <c r="H176" s="2">
         <v>21634.95</v>
       </c>
     </row>
@@ -6985,10 +6991,10 @@
       <c r="F177" t="s">
         <v>31</v>
       </c>
-      <c r="G177" t="s">
+      <c r="G177" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H177" s="3">
+      <c r="H177" s="2">
         <v>9073.61</v>
       </c>
     </row>
@@ -7011,10 +7017,10 @@
       <c r="F178" t="s">
         <v>50</v>
       </c>
-      <c r="G178">
+      <c r="G178" s="3">
         <v>46160</v>
       </c>
-      <c r="H178" s="3">
+      <c r="H178" s="2">
         <v>23378.18</v>
       </c>
     </row>
@@ -7037,10 +7043,10 @@
       <c r="F179" t="s">
         <v>28</v>
       </c>
-      <c r="G179">
+      <c r="G179" s="3">
         <v>46148</v>
       </c>
-      <c r="H179" s="3">
+      <c r="H179" s="2">
         <v>3330.29</v>
       </c>
     </row>
@@ -7063,10 +7069,10 @@
       <c r="F180" t="s">
         <v>20</v>
       </c>
-      <c r="G180">
+      <c r="G180" s="3">
         <v>46149</v>
       </c>
-      <c r="H180" s="3">
+      <c r="H180" s="2">
         <v>1246.19</v>
       </c>
     </row>
@@ -7089,10 +7095,10 @@
       <c r="F181" t="s">
         <v>28</v>
       </c>
-      <c r="G181">
+      <c r="G181" s="3">
         <v>46148</v>
       </c>
-      <c r="H181" s="3">
+      <c r="H181" s="2">
         <v>2341.08</v>
       </c>
     </row>
@@ -7115,10 +7121,10 @@
       <c r="F182" t="s">
         <v>10</v>
       </c>
-      <c r="G182">
+      <c r="G182" s="3">
         <v>46150</v>
       </c>
-      <c r="H182" s="3">
+      <c r="H182" s="2">
         <v>20633.3</v>
       </c>
     </row>
@@ -7141,10 +7147,10 @@
       <c r="F183" t="s">
         <v>14</v>
       </c>
-      <c r="G183">
+      <c r="G183" s="3">
         <v>46149</v>
       </c>
-      <c r="H183" s="3">
+      <c r="H183" s="2">
         <v>563.16999999999996</v>
       </c>
     </row>
@@ -7167,10 +7173,10 @@
       <c r="F184" t="s">
         <v>14</v>
       </c>
-      <c r="G184">
+      <c r="G184" s="3">
         <v>46149</v>
       </c>
-      <c r="H184" s="3">
+      <c r="H184" s="2">
         <v>2251.67</v>
       </c>
     </row>
@@ -7193,10 +7199,10 @@
       <c r="F185" t="s">
         <v>10</v>
       </c>
-      <c r="G185" s="1">
+      <c r="G185" s="3">
         <v>46153</v>
       </c>
-      <c r="H185" s="3">
+      <c r="H185" s="2">
         <v>95070.45</v>
       </c>
     </row>
@@ -7219,10 +7225,10 @@
       <c r="F186" t="s">
         <v>10</v>
       </c>
-      <c r="G186">
+      <c r="G186" s="3">
         <v>46153</v>
       </c>
-      <c r="H186" s="3">
+      <c r="H186" s="2">
         <v>3063.59</v>
       </c>
     </row>
@@ -7245,10 +7251,10 @@
       <c r="F187" t="s">
         <v>28</v>
       </c>
-      <c r="G187">
+      <c r="G187" s="3">
         <v>46148</v>
       </c>
-      <c r="H187" s="3">
+      <c r="H187" s="2">
         <v>16186.64</v>
       </c>
     </row>
@@ -7271,10 +7277,10 @@
       <c r="F188" t="s">
         <v>28</v>
       </c>
-      <c r="G188">
+      <c r="G188" s="3">
         <v>46148</v>
       </c>
-      <c r="H188" s="3">
+      <c r="H188" s="2">
         <v>4496.3500000000004</v>
       </c>
     </row>
@@ -7297,10 +7303,10 @@
       <c r="F189" t="s">
         <v>26</v>
       </c>
-      <c r="G189" t="s">
+      <c r="G189" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H189" s="3">
+      <c r="H189" s="2">
         <v>4220.66</v>
       </c>
     </row>
@@ -7323,10 +7329,10 @@
       <c r="F190" t="s">
         <v>10</v>
       </c>
-      <c r="G190" s="1">
+      <c r="G190" s="3">
         <v>46151</v>
       </c>
-      <c r="H190" s="3">
+      <c r="H190" s="2">
         <v>3276.43</v>
       </c>
     </row>
@@ -7349,10 +7355,10 @@
       <c r="F191" t="s">
         <v>10</v>
       </c>
-      <c r="G191" t="s">
+      <c r="G191" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H191" s="3">
+      <c r="H191" s="2">
         <v>1060.1400000000001</v>
       </c>
     </row>
@@ -7375,10 +7381,10 @@
       <c r="F192" t="s">
         <v>14</v>
       </c>
-      <c r="G192" s="1">
+      <c r="G192" s="3">
         <v>46149</v>
       </c>
-      <c r="H192" s="3">
+      <c r="H192" s="2">
         <v>1639.89</v>
       </c>
     </row>
@@ -7401,10 +7407,10 @@
       <c r="F193" t="s">
         <v>14</v>
       </c>
-      <c r="G193" s="1">
+      <c r="G193" s="3">
         <v>46149</v>
       </c>
-      <c r="H193" s="3">
+      <c r="H193" s="2">
         <v>294.2</v>
       </c>
     </row>
@@ -7427,10 +7433,10 @@
       <c r="F194" t="s">
         <v>10</v>
       </c>
-      <c r="G194" s="1" t="s">
+      <c r="G194" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H194" s="3">
+      <c r="H194" s="2">
         <v>5787.55</v>
       </c>
     </row>
@@ -7453,10 +7459,10 @@
       <c r="F195" t="s">
         <v>28</v>
       </c>
-      <c r="G195">
+      <c r="G195" s="3">
         <v>46148</v>
       </c>
-      <c r="H195" s="3">
+      <c r="H195" s="2">
         <v>2340.36</v>
       </c>
     </row>
@@ -7479,10 +7485,10 @@
       <c r="F196" t="s">
         <v>10</v>
       </c>
-      <c r="G196" s="1" t="s">
+      <c r="G196" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H196" s="3">
+      <c r="H196" s="2">
         <v>17318.32</v>
       </c>
     </row>
@@ -7505,10 +7511,10 @@
       <c r="F197" t="s">
         <v>31</v>
       </c>
-      <c r="G197" s="1" t="s">
+      <c r="G197" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H197" s="3">
+      <c r="H197" s="2">
         <v>9596.25</v>
       </c>
     </row>
@@ -7531,10 +7537,10 @@
       <c r="F198" t="s">
         <v>10</v>
       </c>
-      <c r="G198" t="s">
+      <c r="G198" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H198" s="3">
+      <c r="H198" s="2">
         <v>5026.55</v>
       </c>
     </row>
@@ -7557,10 +7563,10 @@
       <c r="F199" t="s">
         <v>50</v>
       </c>
-      <c r="G199" s="1" t="s">
+      <c r="G199" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H199" s="3">
+      <c r="H199" s="2">
         <v>7654.58</v>
       </c>
     </row>
@@ -7583,10 +7589,10 @@
       <c r="F200" t="s">
         <v>28</v>
       </c>
-      <c r="G200">
+      <c r="G200" s="3">
         <v>46148</v>
       </c>
-      <c r="H200" s="3">
+      <c r="H200" s="2">
         <v>3981.22</v>
       </c>
     </row>
@@ -7609,10 +7615,10 @@
       <c r="F201" t="s">
         <v>28</v>
       </c>
-      <c r="G201" s="1">
+      <c r="G201" s="3">
         <v>46148</v>
       </c>
-      <c r="H201" s="3">
+      <c r="H201" s="2">
         <v>2105.63</v>
       </c>
     </row>
@@ -7635,10 +7641,10 @@
       <c r="F202" t="s">
         <v>28</v>
       </c>
-      <c r="G202">
+      <c r="G202" s="3">
         <v>46148</v>
       </c>
-      <c r="H202" s="3">
+      <c r="H202" s="2">
         <v>8150.79</v>
       </c>
     </row>
@@ -7661,10 +7667,10 @@
       <c r="F203" t="s">
         <v>28</v>
       </c>
-      <c r="G203">
+      <c r="G203" s="3">
         <v>46148</v>
       </c>
-      <c r="H203" s="3">
+      <c r="H203" s="2">
         <v>10232.66</v>
       </c>
     </row>
@@ -7687,10 +7693,10 @@
       <c r="F204" t="s">
         <v>50</v>
       </c>
-      <c r="G204">
+      <c r="G204" s="3">
         <v>46157</v>
       </c>
-      <c r="H204" s="3">
+      <c r="H204" s="2">
         <v>7109.39</v>
       </c>
     </row>
@@ -7713,10 +7719,10 @@
       <c r="F205" t="s">
         <v>14</v>
       </c>
-      <c r="G205" s="1">
+      <c r="G205" s="3">
         <v>46149</v>
       </c>
-      <c r="H205" s="3">
+      <c r="H205" s="2">
         <v>922.89</v>
       </c>
     </row>
@@ -7739,10 +7745,10 @@
       <c r="F206" t="s">
         <v>14</v>
       </c>
-      <c r="G206" s="1">
+      <c r="G206" s="3">
         <v>46149</v>
       </c>
-      <c r="H206" s="3">
+      <c r="H206" s="2">
         <v>2674.64</v>
       </c>
     </row>
@@ -7765,10 +7771,10 @@
       <c r="F207" t="s">
         <v>31</v>
       </c>
-      <c r="G207" s="1" t="s">
+      <c r="G207" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H207" s="3">
+      <c r="H207" s="2">
         <v>12724.3</v>
       </c>
     </row>
@@ -7791,10 +7797,10 @@
       <c r="F208" t="s">
         <v>10</v>
       </c>
-      <c r="G208" s="1" t="s">
+      <c r="G208" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H208" s="3">
+      <c r="H208" s="2">
         <v>2720.16</v>
       </c>
     </row>
@@ -7817,10 +7823,10 @@
       <c r="F209" t="s">
         <v>28</v>
       </c>
-      <c r="G209">
+      <c r="G209" s="3">
         <v>46148</v>
       </c>
-      <c r="H209" s="3">
+      <c r="H209" s="2">
         <v>5391.97</v>
       </c>
     </row>
@@ -7843,10 +7849,10 @@
       <c r="F210" t="s">
         <v>20</v>
       </c>
-      <c r="G210">
+      <c r="G210" s="3">
         <v>46149</v>
       </c>
-      <c r="H210" s="3">
+      <c r="H210" s="2">
         <v>2487.2600000000002</v>
       </c>
     </row>
@@ -7869,10 +7875,10 @@
       <c r="F211" t="s">
         <v>28</v>
       </c>
-      <c r="G211">
+      <c r="G211" s="3">
         <v>46148</v>
       </c>
-      <c r="H211" s="3">
+      <c r="H211" s="2">
         <v>2351.1999999999998</v>
       </c>
     </row>
@@ -7895,10 +7901,10 @@
       <c r="F212" t="s">
         <v>50</v>
       </c>
-      <c r="G212" s="1">
+      <c r="G212" s="3">
         <v>46154</v>
       </c>
-      <c r="H212" s="3">
+      <c r="H212" s="2">
         <v>6315.48</v>
       </c>
     </row>
@@ -7921,10 +7927,10 @@
       <c r="F213" t="s">
         <v>10</v>
       </c>
-      <c r="G213">
+      <c r="G213" s="3">
         <v>46148</v>
       </c>
-      <c r="H213" s="3">
+      <c r="H213" s="2">
         <v>5652.73</v>
       </c>
     </row>
@@ -7947,10 +7953,10 @@
       <c r="F214" t="s">
         <v>28</v>
       </c>
-      <c r="G214">
+      <c r="G214" s="3">
         <v>46148</v>
       </c>
-      <c r="H214" s="3">
+      <c r="H214" s="2">
         <v>2789.86</v>
       </c>
     </row>
@@ -7973,10 +7979,10 @@
       <c r="F215" t="s">
         <v>31</v>
       </c>
-      <c r="G215" s="1" t="s">
+      <c r="G215" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H215" s="3">
+      <c r="H215" s="2">
         <v>6670.13</v>
       </c>
     </row>
@@ -7999,10 +8005,10 @@
       <c r="F216" t="s">
         <v>85</v>
       </c>
-      <c r="G216" s="1">
+      <c r="G216" s="3">
         <v>46149</v>
       </c>
-      <c r="H216" s="3">
+      <c r="H216" s="2">
         <v>10651.56</v>
       </c>
     </row>
@@ -8025,10 +8031,10 @@
       <c r="F217" t="s">
         <v>28</v>
       </c>
-      <c r="G217" s="1">
+      <c r="G217" s="3">
         <v>46148</v>
       </c>
-      <c r="H217" s="3">
+      <c r="H217" s="2">
         <v>4039.71</v>
       </c>
     </row>
@@ -8051,10 +8057,10 @@
       <c r="F218" t="s">
         <v>10</v>
       </c>
-      <c r="G218">
+      <c r="G218" s="3">
         <v>46151</v>
       </c>
-      <c r="H218" s="3">
+      <c r="H218" s="2">
         <v>18947.439999999999</v>
       </c>
     </row>
@@ -8077,10 +8083,10 @@
       <c r="F219" t="s">
         <v>28</v>
       </c>
-      <c r="G219">
+      <c r="G219" s="3">
         <v>46148</v>
       </c>
-      <c r="H219" s="3">
+      <c r="H219" s="2">
         <v>2462.92</v>
       </c>
     </row>
@@ -8103,10 +8109,10 @@
       <c r="F220" t="s">
         <v>14</v>
       </c>
-      <c r="G220">
+      <c r="G220" s="3">
         <v>46149</v>
       </c>
-      <c r="H220" s="3">
+      <c r="H220" s="2">
         <v>1223.49</v>
       </c>
     </row>
@@ -8129,10 +8135,10 @@
       <c r="F221" t="s">
         <v>10</v>
       </c>
-      <c r="G221">
+      <c r="G221" s="3">
         <v>46151</v>
       </c>
-      <c r="H221" s="3">
+      <c r="H221" s="2">
         <v>7441.55</v>
       </c>
     </row>
@@ -8155,10 +8161,10 @@
       <c r="F222" t="s">
         <v>28</v>
       </c>
-      <c r="G222" s="1">
+      <c r="G222" s="3">
         <v>46148</v>
       </c>
-      <c r="H222" s="3">
+      <c r="H222" s="2">
         <v>1962.77</v>
       </c>
     </row>
@@ -8181,10 +8187,10 @@
       <c r="F223" t="s">
         <v>28</v>
       </c>
-      <c r="G223">
+      <c r="G223" s="3">
         <v>46148</v>
       </c>
-      <c r="H223" s="3">
+      <c r="H223" s="2">
         <v>3143.07</v>
       </c>
     </row>
@@ -8207,10 +8213,10 @@
       <c r="F224" t="s">
         <v>50</v>
       </c>
-      <c r="G224" t="s">
+      <c r="G224" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H224" s="3">
+      <c r="H224" s="2">
         <v>10044.99</v>
       </c>
     </row>
@@ -8233,10 +8239,10 @@
       <c r="F225" t="s">
         <v>28</v>
       </c>
-      <c r="G225">
+      <c r="G225" s="3">
         <v>46148</v>
       </c>
-      <c r="H225" s="3">
+      <c r="H225" s="2">
         <v>2541.9899999999998</v>
       </c>
     </row>
@@ -8259,10 +8265,10 @@
       <c r="F226" t="s">
         <v>10</v>
       </c>
-      <c r="G226">
+      <c r="G226" s="3">
         <v>46155</v>
       </c>
-      <c r="H226" s="3">
+      <c r="H226" s="2">
         <v>5499.11</v>
       </c>
     </row>
@@ -8285,10 +8291,10 @@
       <c r="F227" t="s">
         <v>10</v>
       </c>
-      <c r="G227">
+      <c r="G227" s="3">
         <v>46155</v>
       </c>
-      <c r="H227" s="3">
+      <c r="H227" s="2">
         <v>49841.98</v>
       </c>
     </row>
@@ -8311,10 +8317,10 @@
       <c r="F228" t="s">
         <v>10</v>
       </c>
-      <c r="G228" s="1">
+      <c r="G228" s="3">
         <v>46151</v>
       </c>
-      <c r="H228" s="3">
+      <c r="H228" s="2">
         <v>38652.699999999997</v>
       </c>
     </row>
@@ -8337,10 +8343,10 @@
       <c r="F229" t="s">
         <v>28</v>
       </c>
-      <c r="G229">
+      <c r="G229" s="3">
         <v>46148</v>
       </c>
-      <c r="H229" s="3">
+      <c r="H229" s="2">
         <v>4554.4799999999996</v>
       </c>
     </row>
@@ -8363,10 +8369,10 @@
       <c r="F230" t="s">
         <v>10</v>
       </c>
-      <c r="G230">
+      <c r="G230" s="3">
         <v>46151</v>
       </c>
-      <c r="H230" s="3">
+      <c r="H230" s="2">
         <v>61129.67</v>
       </c>
     </row>
@@ -8389,10 +8395,10 @@
       <c r="F231" t="s">
         <v>28</v>
       </c>
-      <c r="G231">
+      <c r="G231" s="3">
         <v>46148</v>
       </c>
-      <c r="H231" s="3">
+      <c r="H231" s="2">
         <v>3411.74</v>
       </c>
     </row>
@@ -8415,10 +8421,10 @@
       <c r="F232" t="s">
         <v>10</v>
       </c>
-      <c r="G232" s="1">
+      <c r="G232" s="3">
         <v>46151</v>
       </c>
-      <c r="H232" s="3">
+      <c r="H232" s="2">
         <v>7897.83</v>
       </c>
     </row>
@@ -8441,10 +8447,10 @@
       <c r="F233" t="s">
         <v>50</v>
       </c>
-      <c r="G233" t="s">
+      <c r="G233" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H233" s="3">
+      <c r="H233" s="2">
         <v>38772.480000000003</v>
       </c>
     </row>
@@ -8467,10 +8473,10 @@
       <c r="F234" t="s">
         <v>50</v>
       </c>
-      <c r="G234" s="1" t="s">
+      <c r="G234" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H234" s="3">
+      <c r="H234" s="2">
         <v>38772.480000000003</v>
       </c>
     </row>
@@ -8493,10 +8499,10 @@
       <c r="F235" t="s">
         <v>10</v>
       </c>
-      <c r="G235">
+      <c r="G235" s="3">
         <v>46155</v>
       </c>
-      <c r="H235" s="3">
+      <c r="H235" s="2">
         <v>22147.42</v>
       </c>
     </row>
@@ -8519,10 +8525,10 @@
       <c r="F236" t="s">
         <v>10</v>
       </c>
-      <c r="G236" s="1">
+      <c r="G236" s="3">
         <v>46155</v>
       </c>
-      <c r="H236" s="3">
+      <c r="H236" s="2">
         <v>740.64</v>
       </c>
     </row>
@@ -8545,10 +8551,10 @@
       <c r="F237" t="s">
         <v>10</v>
       </c>
-      <c r="G237" s="1">
+      <c r="G237" s="3">
         <v>46151</v>
       </c>
-      <c r="H237" s="3">
+      <c r="H237" s="2">
         <v>49947.23</v>
       </c>
     </row>
@@ -8571,10 +8577,10 @@
       <c r="F238" t="s">
         <v>10</v>
       </c>
-      <c r="G238">
+      <c r="G238" s="3">
         <v>46151</v>
       </c>
-      <c r="H238" s="3">
+      <c r="H238" s="2">
         <v>6640.43</v>
       </c>
     </row>
@@ -8597,10 +8603,10 @@
       <c r="F239" t="s">
         <v>10</v>
       </c>
-      <c r="G239">
+      <c r="G239" s="3">
         <v>46155</v>
       </c>
-      <c r="H239" s="3">
+      <c r="H239" s="2">
         <v>2491.98</v>
       </c>
     </row>
@@ -8623,10 +8629,10 @@
       <c r="F240" t="s">
         <v>10</v>
       </c>
-      <c r="G240" t="s">
+      <c r="G240" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H240" s="3">
+      <c r="H240" s="2">
         <v>15255.15</v>
       </c>
     </row>
@@ -8649,10 +8655,10 @@
       <c r="F241" t="s">
         <v>10</v>
       </c>
-      <c r="G241">
+      <c r="G241" s="3">
         <v>46151</v>
       </c>
-      <c r="H241" s="3">
+      <c r="H241" s="2">
         <v>15333.16</v>
       </c>
     </row>
@@ -8675,10 +8681,10 @@
       <c r="F242" t="s">
         <v>10</v>
       </c>
-      <c r="G242">
+      <c r="G242" s="3">
         <v>46155</v>
       </c>
-      <c r="H242" s="3">
+      <c r="H242" s="2">
         <v>11879.75</v>
       </c>
     </row>
@@ -8701,10 +8707,10 @@
       <c r="F243" t="s">
         <v>20</v>
       </c>
-      <c r="G243">
+      <c r="G243" s="3">
         <v>46149</v>
       </c>
-      <c r="H243" s="3">
+      <c r="H243" s="2">
         <v>15068.48</v>
       </c>
     </row>
@@ -8727,10 +8733,10 @@
       <c r="F244" t="s">
         <v>28</v>
       </c>
-      <c r="G244">
+      <c r="G244" s="3">
         <v>46148</v>
       </c>
-      <c r="H244" s="3">
+      <c r="H244" s="2">
         <v>3568.07</v>
       </c>
     </row>
@@ -8753,10 +8759,10 @@
       <c r="F245" t="s">
         <v>28</v>
       </c>
-      <c r="G245" s="1">
+      <c r="G245" s="3">
         <v>46148</v>
       </c>
-      <c r="H245" s="3">
+      <c r="H245" s="2">
         <v>4599.9799999999996</v>
       </c>
     </row>
@@ -8779,10 +8785,10 @@
       <c r="F246" t="s">
         <v>10</v>
       </c>
-      <c r="G246">
+      <c r="G246" s="3">
         <v>46151</v>
       </c>
-      <c r="H246" s="3">
+      <c r="H246" s="2">
         <v>7357.35</v>
       </c>
     </row>
@@ -8805,10 +8811,10 @@
       <c r="F247" t="s">
         <v>10</v>
       </c>
-      <c r="G247" s="1">
+      <c r="G247" s="3">
         <v>46151</v>
       </c>
-      <c r="H247" s="3">
+      <c r="H247" s="2">
         <v>75424.399999999994</v>
       </c>
     </row>
@@ -8831,10 +8837,10 @@
       <c r="F248" t="s">
         <v>10</v>
       </c>
-      <c r="G248" t="s">
+      <c r="G248" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H248" s="3">
+      <c r="H248" s="2">
         <v>575.69000000000005</v>
       </c>
     </row>
@@ -8857,10 +8863,10 @@
       <c r="F249" t="s">
         <v>10</v>
       </c>
-      <c r="G249" t="s">
+      <c r="G249" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H249" s="3">
+      <c r="H249" s="2">
         <v>199.68</v>
       </c>
     </row>
@@ -8883,10 +8889,10 @@
       <c r="F250" t="s">
         <v>10</v>
       </c>
-      <c r="G250" s="1" t="s">
+      <c r="G250" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H250" s="3">
+      <c r="H250" s="2">
         <v>971.18</v>
       </c>
     </row>
@@ -8909,10 +8915,10 @@
       <c r="F251" t="s">
         <v>10</v>
       </c>
-      <c r="G251" s="1" t="s">
+      <c r="G251" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H251" s="3">
+      <c r="H251" s="2">
         <v>399.37</v>
       </c>
     </row>
@@ -8935,10 +8941,10 @@
       <c r="F252" t="s">
         <v>10</v>
       </c>
-      <c r="G252" s="1" t="s">
+      <c r="G252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H252" s="3">
+      <c r="H252" s="2">
         <v>595.04</v>
       </c>
     </row>
@@ -8961,10 +8967,10 @@
       <c r="F253" t="s">
         <v>28</v>
       </c>
-      <c r="G253">
+      <c r="G253" s="3">
         <v>46148</v>
       </c>
-      <c r="H253" s="3">
+      <c r="H253" s="2">
         <v>3354.74</v>
       </c>
     </row>
@@ -8987,10 +8993,10 @@
       <c r="F254" t="s">
         <v>28</v>
       </c>
-      <c r="G254" s="1">
+      <c r="G254" s="3">
         <v>46148</v>
       </c>
-      <c r="H254" s="3">
+      <c r="H254" s="2">
         <v>11274.52</v>
       </c>
     </row>
@@ -9013,10 +9019,10 @@
       <c r="F255" t="s">
         <v>14</v>
       </c>
-      <c r="G255">
+      <c r="G255" s="3">
         <v>46149</v>
       </c>
-      <c r="H255" s="3">
+      <c r="H255" s="2">
         <v>12966.57</v>
       </c>
     </row>
@@ -9039,10 +9045,10 @@
       <c r="F256" t="s">
         <v>28</v>
       </c>
-      <c r="G256" s="1">
+      <c r="G256" s="3">
         <v>46148</v>
       </c>
-      <c r="H256" s="3">
+      <c r="H256" s="2">
         <v>5624.61</v>
       </c>
     </row>
@@ -9065,10 +9071,10 @@
       <c r="F257" t="s">
         <v>10</v>
       </c>
-      <c r="G257" s="1">
+      <c r="G257" s="3">
         <v>46148</v>
       </c>
-      <c r="H257" s="3">
+      <c r="H257" s="2">
         <v>19360.95</v>
       </c>
     </row>
@@ -9091,10 +9097,10 @@
       <c r="F258" t="s">
         <v>10</v>
       </c>
-      <c r="G258">
+      <c r="G258" s="3">
         <v>46155</v>
       </c>
-      <c r="H258" s="3">
+      <c r="H258" s="2">
         <v>4850.1099999999997</v>
       </c>
     </row>
@@ -9117,10 +9123,10 @@
       <c r="F259" t="s">
         <v>10</v>
       </c>
-      <c r="G259" t="s">
+      <c r="G259" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H259" s="3">
+      <c r="H259" s="2">
         <v>6173.41</v>
       </c>
     </row>
@@ -9143,10 +9149,10 @@
       <c r="F260" t="s">
         <v>10</v>
       </c>
-      <c r="G260">
+      <c r="G260" s="3">
         <v>46155</v>
       </c>
-      <c r="H260" s="3">
+      <c r="H260" s="2">
         <v>2317.73</v>
       </c>
     </row>
@@ -9169,10 +9175,10 @@
       <c r="F261" t="s">
         <v>50</v>
       </c>
-      <c r="G261">
+      <c r="G261" s="3">
         <v>46161</v>
       </c>
-      <c r="H261" s="3">
+      <c r="H261" s="2">
         <v>16603.72</v>
       </c>
     </row>
@@ -9195,10 +9201,10 @@
       <c r="F262" t="s">
         <v>10</v>
       </c>
-      <c r="G262">
+      <c r="G262" s="3">
         <v>46169</v>
       </c>
-      <c r="H262" s="3">
+      <c r="H262" s="2">
         <v>2944.58</v>
       </c>
     </row>
@@ -9221,10 +9227,10 @@
       <c r="F263" t="s">
         <v>28</v>
       </c>
-      <c r="G263" s="1">
+      <c r="G263" s="3">
         <v>46148</v>
       </c>
-      <c r="H263" s="3">
+      <c r="H263" s="2">
         <v>395.47</v>
       </c>
     </row>
@@ -9247,10 +9253,10 @@
       <c r="F264" t="s">
         <v>10</v>
       </c>
-      <c r="G264" s="1">
+      <c r="G264" s="3">
         <v>46151</v>
       </c>
-      <c r="H264" s="3">
+      <c r="H264" s="2">
         <v>14140.87</v>
       </c>
     </row>
@@ -9273,10 +9279,10 @@
       <c r="F265" t="s">
         <v>28</v>
       </c>
-      <c r="G265" s="1">
+      <c r="G265" s="3">
         <v>46148</v>
       </c>
-      <c r="H265" s="3">
+      <c r="H265" s="2">
         <v>7607.43</v>
       </c>
     </row>
@@ -9299,10 +9305,10 @@
       <c r="F266" t="s">
         <v>10</v>
       </c>
-      <c r="G266" s="1" t="s">
+      <c r="G266" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H266" s="3">
+      <c r="H266" s="2">
         <v>31217.52</v>
       </c>
     </row>
@@ -9325,10 +9331,10 @@
       <c r="F267" t="s">
         <v>28</v>
       </c>
-      <c r="G267" s="1">
+      <c r="G267" s="3">
         <v>46148</v>
       </c>
-      <c r="H267" s="3">
+      <c r="H267" s="2">
         <v>2357.02</v>
       </c>
     </row>
@@ -9351,10 +9357,10 @@
       <c r="F268" t="s">
         <v>50</v>
       </c>
-      <c r="G268" s="1">
+      <c r="G268" s="3">
         <v>46171</v>
       </c>
-      <c r="H268" s="3">
+      <c r="H268" s="2">
         <v>9517.56</v>
       </c>
     </row>
@@ -9377,10 +9383,10 @@
       <c r="F269" t="s">
         <v>10</v>
       </c>
-      <c r="G269">
+      <c r="G269" s="3">
         <v>46151</v>
       </c>
-      <c r="H269" s="3">
+      <c r="H269" s="2">
         <v>17166.189999999999</v>
       </c>
     </row>
@@ -9403,10 +9409,10 @@
       <c r="F270" t="s">
         <v>10</v>
       </c>
-      <c r="G270" s="1">
+      <c r="G270" s="3">
         <v>46151</v>
       </c>
-      <c r="H270" s="3">
+      <c r="H270" s="2">
         <v>5703.29</v>
       </c>
     </row>
@@ -9429,10 +9435,10 @@
       <c r="F271" t="s">
         <v>10</v>
       </c>
-      <c r="G271" s="1">
+      <c r="G271" s="3">
         <v>46151</v>
       </c>
-      <c r="H271" s="3">
+      <c r="H271" s="2">
         <v>3356.65</v>
       </c>
     </row>
@@ -9455,10 +9461,10 @@
       <c r="F272" t="s">
         <v>10</v>
       </c>
-      <c r="G272">
+      <c r="G272" s="3">
         <v>46151</v>
       </c>
-      <c r="H272" s="3">
+      <c r="H272" s="2">
         <v>20950.75</v>
       </c>
     </row>
@@ -9481,10 +9487,10 @@
       <c r="F273" t="s">
         <v>10</v>
       </c>
-      <c r="G273">
+      <c r="G273" s="3">
         <v>46151</v>
       </c>
-      <c r="H273" s="3">
+      <c r="H273" s="2">
         <v>4453.47</v>
       </c>
     </row>
@@ -9507,10 +9513,10 @@
       <c r="F274" t="s">
         <v>10</v>
       </c>
-      <c r="G274">
+      <c r="G274" s="3">
         <v>46151</v>
       </c>
-      <c r="H274" s="3">
+      <c r="H274" s="2">
         <v>12347.47</v>
       </c>
     </row>
@@ -9533,10 +9539,10 @@
       <c r="F275" t="s">
         <v>10</v>
       </c>
-      <c r="G275" s="1">
+      <c r="G275" s="3">
         <v>46151</v>
       </c>
-      <c r="H275" s="3">
+      <c r="H275" s="2">
         <v>5303.98</v>
       </c>
     </row>
@@ -9559,10 +9565,10 @@
       <c r="F276" t="s">
         <v>10</v>
       </c>
-      <c r="G276">
+      <c r="G276" s="3">
         <v>46151</v>
       </c>
-      <c r="H276" s="3">
+      <c r="H276" s="2">
         <v>7714.88</v>
       </c>
     </row>
@@ -9585,10 +9591,10 @@
       <c r="F277" t="s">
         <v>10</v>
       </c>
-      <c r="G277">
+      <c r="G277" s="3">
         <v>46151</v>
       </c>
-      <c r="H277" s="3">
+      <c r="H277" s="2">
         <v>3010.39</v>
       </c>
     </row>
@@ -9611,10 +9617,10 @@
       <c r="F278" t="s">
         <v>10</v>
       </c>
-      <c r="G278" t="s">
+      <c r="G278" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H278" s="3">
+      <c r="H278" s="2">
         <v>146.13999999999999</v>
       </c>
     </row>
@@ -9637,10 +9643,10 @@
       <c r="F279" t="s">
         <v>10</v>
       </c>
-      <c r="G279">
+      <c r="G279" s="3">
         <v>46151</v>
       </c>
-      <c r="H279" s="3">
+      <c r="H279" s="2">
         <v>5135.55</v>
       </c>
     </row>
@@ -9663,10 +9669,10 @@
       <c r="F280" t="s">
         <v>10</v>
       </c>
-      <c r="G280" s="1">
+      <c r="G280" s="3">
         <v>46153</v>
       </c>
-      <c r="H280" s="3">
+      <c r="H280" s="2">
         <v>5266.3</v>
       </c>
     </row>
@@ -9689,10 +9695,10 @@
       <c r="F281" t="s">
         <v>10</v>
       </c>
-      <c r="G281">
+      <c r="G281" s="3">
         <v>46151</v>
       </c>
-      <c r="H281" s="3">
+      <c r="H281" s="2">
         <v>8468.2000000000007</v>
       </c>
     </row>
@@ -9715,10 +9721,10 @@
       <c r="F282" t="s">
         <v>10</v>
       </c>
-      <c r="G282">
+      <c r="G282" s="3">
         <v>46151</v>
       </c>
-      <c r="H282" s="3">
+      <c r="H282" s="2">
         <v>3347.49</v>
       </c>
     </row>
@@ -9741,10 +9747,10 @@
       <c r="F283" t="s">
         <v>10</v>
       </c>
-      <c r="G283" s="1">
+      <c r="G283" s="3">
         <v>46151</v>
       </c>
-      <c r="H283" s="3">
+      <c r="H283" s="2">
         <v>4228.7700000000004</v>
       </c>
     </row>
@@ -9767,10 +9773,10 @@
       <c r="F284" t="s">
         <v>10</v>
       </c>
-      <c r="G284" s="1">
+      <c r="G284" s="3">
         <v>46151</v>
       </c>
-      <c r="H284" s="3">
+      <c r="H284" s="2">
         <v>2645.5</v>
       </c>
     </row>
@@ -9793,10 +9799,10 @@
       <c r="F285" t="s">
         <v>10</v>
       </c>
-      <c r="G285" s="1">
+      <c r="G285" s="3">
         <v>46151</v>
       </c>
-      <c r="H285" s="3">
+      <c r="H285" s="2">
         <v>5012.8599999999997</v>
       </c>
     </row>
@@ -9819,10 +9825,10 @@
       <c r="F286" t="s">
         <v>14</v>
       </c>
-      <c r="G286">
+      <c r="G286" s="3">
         <v>46149</v>
       </c>
-      <c r="H286" s="3">
+      <c r="H286" s="2">
         <v>296.81</v>
       </c>
     </row>
@@ -9845,10 +9851,10 @@
       <c r="F287" t="s">
         <v>28</v>
       </c>
-      <c r="G287" s="1">
+      <c r="G287" s="3">
         <v>46148</v>
       </c>
-      <c r="H287" s="3">
+      <c r="H287" s="2">
         <v>1923.83</v>
       </c>
     </row>
@@ -9871,10 +9877,10 @@
       <c r="F288" t="s">
         <v>28</v>
       </c>
-      <c r="G288" s="1">
+      <c r="G288" s="3">
         <v>46148</v>
       </c>
-      <c r="H288" s="3">
+      <c r="H288" s="2">
         <v>4228.3599999999997</v>
       </c>
     </row>
@@ -9897,10 +9903,10 @@
       <c r="F289" t="s">
         <v>28</v>
       </c>
-      <c r="G289" s="1">
+      <c r="G289" s="3">
         <v>46148</v>
       </c>
-      <c r="H289" s="3">
+      <c r="H289" s="2">
         <v>5649.08</v>
       </c>
     </row>
@@ -9923,10 +9929,10 @@
       <c r="F290" t="s">
         <v>28</v>
       </c>
-      <c r="G290" s="1">
+      <c r="G290" s="3">
         <v>46148</v>
       </c>
-      <c r="H290" s="3">
+      <c r="H290" s="2">
         <v>12063.65</v>
       </c>
     </row>
@@ -9949,10 +9955,10 @@
       <c r="F291" t="s">
         <v>10</v>
       </c>
-      <c r="G291" s="1">
+      <c r="G291" s="3">
         <v>46148</v>
       </c>
-      <c r="H291" s="3">
+      <c r="H291" s="2">
         <v>5859.7</v>
       </c>
     </row>
@@ -9975,10 +9981,10 @@
       <c r="F292" t="s">
         <v>50</v>
       </c>
-      <c r="G292" s="1">
+      <c r="G292" s="3">
         <v>46160</v>
       </c>
-      <c r="H292" s="3">
+      <c r="H292" s="2">
         <v>142341.65</v>
       </c>
     </row>
@@ -10001,10 +10007,10 @@
       <c r="F293" t="s">
         <v>14</v>
       </c>
-      <c r="G293">
+      <c r="G293" s="3">
         <v>46149</v>
       </c>
-      <c r="H293" s="3">
+      <c r="H293" s="2">
         <v>475.96</v>
       </c>
     </row>
@@ -10027,10 +10033,10 @@
       <c r="F294" t="s">
         <v>10</v>
       </c>
-      <c r="G294" s="1" t="s">
+      <c r="G294" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H294" s="3">
+      <c r="H294" s="2">
         <v>2528.14</v>
       </c>
     </row>
@@ -10053,10 +10059,10 @@
       <c r="F295" t="s">
         <v>10</v>
       </c>
-      <c r="G295" s="1">
+      <c r="G295" s="3">
         <v>46148</v>
       </c>
-      <c r="H295" s="3">
+      <c r="H295" s="2">
         <v>5417.89</v>
       </c>
     </row>
@@ -10079,10 +10085,10 @@
       <c r="F296" t="s">
         <v>10</v>
       </c>
-      <c r="G296" s="1">
+      <c r="G296" s="3">
         <v>46149</v>
       </c>
-      <c r="H296" s="3">
+      <c r="H296" s="2">
         <v>31874.639999999999</v>
       </c>
     </row>
@@ -10105,10 +10111,10 @@
       <c r="F297" t="s">
         <v>10</v>
       </c>
-      <c r="G297" s="1">
+      <c r="G297" s="3">
         <v>46150</v>
       </c>
-      <c r="H297" s="3">
+      <c r="H297" s="2">
         <v>20633.3</v>
       </c>
     </row>
@@ -10131,10 +10137,10 @@
       <c r="F298" t="s">
         <v>10</v>
       </c>
-      <c r="G298" s="1">
+      <c r="G298" s="3">
         <v>46163</v>
       </c>
-      <c r="H298" s="3">
+      <c r="H298" s="2">
         <v>4111.03</v>
       </c>
     </row>
@@ -10157,10 +10163,10 @@
       <c r="F299" t="s">
         <v>10</v>
       </c>
-      <c r="G299" s="1">
+      <c r="G299" s="3">
         <v>46151</v>
       </c>
-      <c r="H299" s="3">
+      <c r="H299" s="2">
         <v>6727.04</v>
       </c>
     </row>
@@ -10183,10 +10189,10 @@
       <c r="F300" t="s">
         <v>10</v>
       </c>
-      <c r="G300" s="1">
+      <c r="G300" s="3">
         <v>46151</v>
       </c>
-      <c r="H300" s="3">
+      <c r="H300" s="2">
         <v>3171.33</v>
       </c>
     </row>
@@ -10209,10 +10215,10 @@
       <c r="F301" t="s">
         <v>28</v>
       </c>
-      <c r="G301" s="1">
+      <c r="G301" s="3">
         <v>46148</v>
       </c>
-      <c r="H301" s="3">
+      <c r="H301" s="2">
         <v>16443.810000000001</v>
       </c>
     </row>
@@ -10235,10 +10241,10 @@
       <c r="F302" t="s">
         <v>10</v>
       </c>
-      <c r="G302" s="1">
+      <c r="G302" s="3">
         <v>46163</v>
       </c>
-      <c r="H302" s="3">
+      <c r="H302" s="2">
         <v>5671.06</v>
       </c>
     </row>
@@ -10261,10 +10267,10 @@
       <c r="F303" t="s">
         <v>10</v>
       </c>
-      <c r="G303" s="1">
+      <c r="G303" s="3">
         <v>46155</v>
       </c>
-      <c r="H303" s="3">
+      <c r="H303" s="2">
         <v>31461.02</v>
       </c>
     </row>
@@ -10287,10 +10293,10 @@
       <c r="F304" t="s">
         <v>10</v>
       </c>
-      <c r="G304" s="1">
+      <c r="G304" s="3">
         <v>46151</v>
       </c>
-      <c r="H304" s="3">
+      <c r="H304" s="2">
         <v>42169.61</v>
       </c>
     </row>
@@ -10313,10 +10319,10 @@
       <c r="F305" t="s">
         <v>10</v>
       </c>
-      <c r="G305">
+      <c r="G305" s="3">
         <v>46155</v>
       </c>
-      <c r="H305" s="3">
+      <c r="H305" s="2">
         <v>6002.64</v>
       </c>
     </row>
@@ -10339,10 +10345,10 @@
       <c r="F306" t="s">
         <v>10</v>
       </c>
-      <c r="G306" s="1">
+      <c r="G306" s="3">
         <v>46155</v>
       </c>
-      <c r="H306" s="3">
+      <c r="H306" s="2">
         <v>6262.57</v>
       </c>
     </row>
@@ -10365,10 +10371,10 @@
       <c r="F307" t="s">
         <v>10</v>
       </c>
-      <c r="G307">
+      <c r="G307" s="3">
         <v>46163</v>
       </c>
-      <c r="H307" s="3">
+      <c r="H307" s="2">
         <v>24666.34</v>
       </c>
     </row>
@@ -10391,10 +10397,10 @@
       <c r="F308" t="s">
         <v>10</v>
       </c>
-      <c r="G308">
+      <c r="G308" s="3">
         <v>46154</v>
       </c>
-      <c r="H308" s="3">
+      <c r="H308" s="2">
         <v>226431.51</v>
       </c>
     </row>
@@ -10417,10 +10423,10 @@
       <c r="F309" t="s">
         <v>50</v>
       </c>
-      <c r="G309" s="1" t="s">
+      <c r="G309" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H309" s="3">
+      <c r="H309" s="2">
         <v>5524.09</v>
       </c>
     </row>
@@ -10443,10 +10449,10 @@
       <c r="F310" t="s">
         <v>10</v>
       </c>
-      <c r="G310" s="1">
+      <c r="G310" s="3">
         <v>46155</v>
       </c>
-      <c r="H310" s="3">
+      <c r="H310" s="2">
         <v>8534.49</v>
       </c>
     </row>
@@ -10469,10 +10475,10 @@
       <c r="F311" t="s">
         <v>10</v>
       </c>
-      <c r="G311" s="1">
+      <c r="G311" s="3">
         <v>46151</v>
       </c>
-      <c r="H311" s="3">
+      <c r="H311" s="2">
         <v>2582.1799999999998</v>
       </c>
     </row>
@@ -10495,10 +10501,10 @@
       <c r="F312" t="s">
         <v>10</v>
       </c>
-      <c r="G312">
+      <c r="G312" s="3">
         <v>46151</v>
       </c>
-      <c r="H312" s="3">
+      <c r="H312" s="2">
         <v>5597.14</v>
       </c>
     </row>
@@ -10521,10 +10527,10 @@
       <c r="F313" t="s">
         <v>28</v>
       </c>
-      <c r="G313">
+      <c r="G313" s="3">
         <v>46148</v>
       </c>
-      <c r="H313" s="3">
+      <c r="H313" s="2">
         <v>24475.43</v>
       </c>
     </row>
@@ -10547,10 +10553,10 @@
       <c r="F314" t="s">
         <v>10</v>
       </c>
-      <c r="G314" s="1">
+      <c r="G314" s="3">
         <v>46170</v>
       </c>
-      <c r="H314" s="3">
+      <c r="H314" s="2">
         <v>5310.11</v>
       </c>
     </row>
@@ -10573,10 +10579,10 @@
       <c r="F315" t="s">
         <v>20</v>
       </c>
-      <c r="G315" s="1">
+      <c r="G315" s="3">
         <v>46149</v>
       </c>
-      <c r="H315" s="3">
+      <c r="H315" s="2">
         <v>4661.3500000000004</v>
       </c>
     </row>
@@ -10599,10 +10605,10 @@
       <c r="F316" t="s">
         <v>20</v>
       </c>
-      <c r="G316">
+      <c r="G316" s="3">
         <v>46149</v>
       </c>
-      <c r="H316" s="3">
+      <c r="H316" s="2">
         <v>643.91</v>
       </c>
     </row>
@@ -10625,10 +10631,10 @@
       <c r="F317" t="s">
         <v>10</v>
       </c>
-      <c r="G317">
+      <c r="G317" s="3">
         <v>46155</v>
       </c>
-      <c r="H317" s="3">
+      <c r="H317" s="2">
         <v>6731.73</v>
       </c>
     </row>
@@ -10651,10 +10657,10 @@
       <c r="F318" t="s">
         <v>10</v>
       </c>
-      <c r="G318" s="1">
+      <c r="G318" s="3">
         <v>46155</v>
       </c>
-      <c r="H318" s="3">
+      <c r="H318" s="2">
         <v>29749.62</v>
       </c>
     </row>
@@ -10677,10 +10683,10 @@
       <c r="F319" t="s">
         <v>10</v>
       </c>
-      <c r="G319">
+      <c r="G319" s="3">
         <v>46163</v>
       </c>
-      <c r="H319" s="3">
+      <c r="H319" s="2">
         <v>4364.91</v>
       </c>
     </row>
@@ -10703,10 +10709,10 @@
       <c r="F320" t="s">
         <v>10</v>
       </c>
-      <c r="G320" s="1">
+      <c r="G320" s="3">
         <v>46151</v>
       </c>
-      <c r="H320" s="3">
+      <c r="H320" s="2">
         <v>2629.78</v>
       </c>
     </row>
@@ -10729,10 +10735,10 @@
       <c r="F321" t="s">
         <v>10</v>
       </c>
-      <c r="G321">
+      <c r="G321" s="3">
         <v>46151</v>
       </c>
-      <c r="H321" s="3">
+      <c r="H321" s="2">
         <v>2334.58</v>
       </c>
     </row>
@@ -10755,10 +10761,10 @@
       <c r="F322" t="s">
         <v>50</v>
       </c>
-      <c r="G322" s="1">
+      <c r="G322" s="3">
         <v>46167</v>
       </c>
-      <c r="H322" s="3">
+      <c r="H322" s="2">
         <v>3854.16</v>
       </c>
     </row>
@@ -10781,10 +10787,10 @@
       <c r="F323" t="s">
         <v>31</v>
       </c>
-      <c r="G323" s="1" t="s">
+      <c r="G323" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H323" s="3">
+      <c r="H323" s="2">
         <v>3417.94</v>
       </c>
     </row>
@@ -10807,10 +10813,10 @@
       <c r="F324" t="s">
         <v>10</v>
       </c>
-      <c r="G324">
+      <c r="G324" s="3">
         <v>46151</v>
       </c>
-      <c r="H324" s="3">
+      <c r="H324" s="2">
         <v>2443.96</v>
       </c>
     </row>
@@ -10833,10 +10839,10 @@
       <c r="F325" t="s">
         <v>10</v>
       </c>
-      <c r="G325" s="1">
+      <c r="G325" s="3">
         <v>46153</v>
       </c>
-      <c r="H325" s="3">
+      <c r="H325" s="2">
         <v>8195.27</v>
       </c>
     </row>
@@ -10859,10 +10865,10 @@
       <c r="F326" t="s">
         <v>10</v>
       </c>
-      <c r="G326">
+      <c r="G326" s="3">
         <v>46151</v>
       </c>
-      <c r="H326" s="3">
+      <c r="H326" s="2">
         <v>8746.77</v>
       </c>
     </row>
@@ -10885,10 +10891,10 @@
       <c r="F327" t="s">
         <v>10</v>
       </c>
-      <c r="G327">
+      <c r="G327" s="3">
         <v>46151</v>
       </c>
-      <c r="H327" s="3">
+      <c r="H327" s="2">
         <v>12370.21</v>
       </c>
     </row>
@@ -10911,10 +10917,10 @@
       <c r="F328" t="s">
         <v>10</v>
       </c>
-      <c r="G328">
+      <c r="G328" s="3">
         <v>46151</v>
       </c>
-      <c r="H328" s="3">
+      <c r="H328" s="2">
         <v>15230.42</v>
       </c>
     </row>
@@ -10937,10 +10943,10 @@
       <c r="F329" t="s">
         <v>10</v>
       </c>
-      <c r="G329">
+      <c r="G329" s="3">
         <v>46151</v>
       </c>
-      <c r="H329" s="3">
+      <c r="H329" s="2">
         <v>9369.59</v>
       </c>
     </row>
@@ -10963,10 +10969,10 @@
       <c r="F330" t="s">
         <v>10</v>
       </c>
-      <c r="G330">
+      <c r="G330" s="3">
         <v>46148</v>
       </c>
-      <c r="H330" s="3">
+      <c r="H330" s="2">
         <v>2775.18</v>
       </c>
     </row>
@@ -10989,10 +10995,10 @@
       <c r="F331" t="s">
         <v>10</v>
       </c>
-      <c r="G331" t="s">
+      <c r="G331" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H331" s="3">
+      <c r="H331" s="2">
         <v>7252.39</v>
       </c>
     </row>
@@ -11015,10 +11021,10 @@
       <c r="F332" t="s">
         <v>10</v>
       </c>
-      <c r="G332" s="1">
+      <c r="G332" s="3">
         <v>46163</v>
       </c>
-      <c r="H332" s="3">
+      <c r="H332" s="2">
         <v>11303.35</v>
       </c>
     </row>
@@ -11041,10 +11047,10 @@
       <c r="F333" t="s">
         <v>28</v>
       </c>
-      <c r="G333" s="1">
+      <c r="G333" s="3">
         <v>46148</v>
       </c>
-      <c r="H333" s="3">
+      <c r="H333" s="2">
         <v>3898.36</v>
       </c>
     </row>
@@ -11067,10 +11073,10 @@
       <c r="F334" t="s">
         <v>10</v>
       </c>
-      <c r="G334">
+      <c r="G334" s="3">
         <v>46151</v>
       </c>
-      <c r="H334" s="3">
+      <c r="H334" s="2">
         <v>2698.81</v>
       </c>
     </row>
@@ -11093,10 +11099,10 @@
       <c r="F335" t="s">
         <v>10</v>
       </c>
-      <c r="G335" s="1">
+      <c r="G335" s="3">
         <v>46155</v>
       </c>
-      <c r="H335" s="3">
+      <c r="H335" s="2">
         <v>1503.12</v>
       </c>
     </row>
@@ -11119,10 +11125,10 @@
       <c r="F336" t="s">
         <v>31</v>
       </c>
-      <c r="G336" s="1" t="s">
+      <c r="G336" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H336" s="3">
+      <c r="H336" s="2">
         <v>3453.14</v>
       </c>
     </row>
@@ -11145,10 +11151,10 @@
       <c r="F337" t="s">
         <v>10</v>
       </c>
-      <c r="G337" s="1">
+      <c r="G337" s="3">
         <v>46153</v>
       </c>
-      <c r="H337" s="3">
+      <c r="H337" s="2">
         <v>3192.63</v>
       </c>
     </row>
@@ -11171,10 +11177,10 @@
       <c r="F338" t="s">
         <v>10</v>
       </c>
-      <c r="G338">
+      <c r="G338" s="3">
         <v>46155</v>
       </c>
-      <c r="H338" s="3">
+      <c r="H338" s="2">
         <v>1619</v>
       </c>
     </row>
@@ -11197,10 +11203,10 @@
       <c r="F339" t="s">
         <v>10</v>
       </c>
-      <c r="G339" s="1">
+      <c r="G339" s="3">
         <v>46153</v>
       </c>
-      <c r="H339" s="3">
+      <c r="H339" s="2">
         <v>89003.21</v>
       </c>
     </row>
@@ -11223,10 +11229,10 @@
       <c r="F340" t="s">
         <v>10</v>
       </c>
-      <c r="G340" s="1">
+      <c r="G340" s="3">
         <v>46148</v>
       </c>
-      <c r="H340" s="3">
+      <c r="H340" s="2">
         <v>1790.18</v>
       </c>
     </row>
@@ -11249,10 +11255,10 @@
       <c r="F341" t="s">
         <v>28</v>
       </c>
-      <c r="G341" s="1">
+      <c r="G341" s="3">
         <v>46148</v>
       </c>
-      <c r="H341" s="3">
+      <c r="H341" s="2">
         <v>1580.19</v>
       </c>
     </row>
@@ -11275,10 +11281,10 @@
       <c r="F342" t="s">
         <v>10</v>
       </c>
-      <c r="G342">
+      <c r="G342" s="3">
         <v>46149</v>
       </c>
-      <c r="H342" s="3">
+      <c r="H342" s="2">
         <v>4851.21</v>
       </c>
     </row>
@@ -11301,10 +11307,10 @@
       <c r="F343" t="s">
         <v>28</v>
       </c>
-      <c r="G343">
+      <c r="G343" s="3">
         <v>46148</v>
       </c>
-      <c r="H343" s="3">
+      <c r="H343" s="2">
         <v>2408.5300000000002</v>
       </c>
     </row>
@@ -11327,10 +11333,10 @@
       <c r="F344" t="s">
         <v>10</v>
       </c>
-      <c r="G344">
+      <c r="G344" s="3">
         <v>46155</v>
       </c>
-      <c r="H344" s="3">
+      <c r="H344" s="2">
         <v>5123.87</v>
       </c>
     </row>
@@ -11353,10 +11359,10 @@
       <c r="F345" t="s">
         <v>10</v>
       </c>
-      <c r="G345">
+      <c r="G345" s="3">
         <v>46149</v>
       </c>
-      <c r="H345" s="3">
+      <c r="H345" s="2">
         <v>4212.59</v>
       </c>
     </row>
@@ -11379,10 +11385,10 @@
       <c r="F346" t="s">
         <v>50</v>
       </c>
-      <c r="G346" t="s">
+      <c r="G346" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H346" s="3">
+      <c r="H346" s="2">
         <v>6670.4</v>
       </c>
     </row>
@@ -11405,10 +11411,10 @@
       <c r="F347" t="s">
         <v>10</v>
       </c>
-      <c r="G347">
+      <c r="G347" s="3">
         <v>46148</v>
       </c>
-      <c r="H347" s="3">
+      <c r="H347" s="2">
         <v>4429.41</v>
       </c>
     </row>
@@ -11431,10 +11437,10 @@
       <c r="F348" t="s">
         <v>10</v>
       </c>
-      <c r="G348">
+      <c r="G348" s="3">
         <v>46149</v>
       </c>
-      <c r="H348" s="3">
+      <c r="H348" s="2">
         <v>3904.86</v>
       </c>
     </row>
@@ -11457,10 +11463,10 @@
       <c r="F349" t="s">
         <v>10</v>
       </c>
-      <c r="G349">
+      <c r="G349" s="3">
         <v>46149</v>
       </c>
-      <c r="H349" s="3">
+      <c r="H349" s="2">
         <v>19635.96</v>
       </c>
     </row>
@@ -11483,10 +11489,10 @@
       <c r="F350" t="s">
         <v>10</v>
       </c>
-      <c r="G350">
+      <c r="G350" s="3">
         <v>46155</v>
       </c>
-      <c r="H350" s="3">
+      <c r="H350" s="2">
         <v>6192.64</v>
       </c>
     </row>
@@ -11509,10 +11515,10 @@
       <c r="F351" t="s">
         <v>10</v>
       </c>
-      <c r="G351" s="1">
+      <c r="G351" s="3">
         <v>46149</v>
       </c>
-      <c r="H351" s="3">
+      <c r="H351" s="2">
         <v>3958.55</v>
       </c>
     </row>
@@ -11535,10 +11541,10 @@
       <c r="F352" t="s">
         <v>10</v>
       </c>
-      <c r="G352">
+      <c r="G352" s="3">
         <v>46153</v>
       </c>
-      <c r="H352" s="3">
+      <c r="H352" s="2">
         <v>1842.42</v>
       </c>
     </row>
@@ -11561,10 +11567,10 @@
       <c r="F353" t="s">
         <v>10</v>
       </c>
-      <c r="G353" s="1">
+      <c r="G353" s="3">
         <v>46155</v>
       </c>
-      <c r="H353" s="3">
+      <c r="H353" s="2">
         <v>13812.5</v>
       </c>
     </row>
@@ -11587,10 +11593,10 @@
       <c r="F354" t="s">
         <v>10</v>
       </c>
-      <c r="G354">
+      <c r="G354" s="3">
         <v>46151</v>
       </c>
-      <c r="H354" s="3">
+      <c r="H354" s="2">
         <v>94582.47</v>
       </c>
     </row>
@@ -11613,10 +11619,10 @@
       <c r="F355" t="s">
         <v>10</v>
       </c>
-      <c r="G355" s="1">
+      <c r="G355" s="3">
         <v>46153</v>
       </c>
-      <c r="H355" s="3">
+      <c r="H355" s="2">
         <v>1639.39</v>
       </c>
     </row>
@@ -11639,10 +11645,10 @@
       <c r="F356" t="s">
         <v>14</v>
       </c>
-      <c r="G356" s="1">
+      <c r="G356" s="3">
         <v>46149</v>
       </c>
-      <c r="H356" s="3">
+      <c r="H356" s="2">
         <v>1846.27</v>
       </c>
     </row>
@@ -11665,10 +11671,10 @@
       <c r="F357" t="s">
         <v>10</v>
       </c>
-      <c r="G357">
+      <c r="G357" s="3">
         <v>46149</v>
       </c>
-      <c r="H357" s="3">
+      <c r="H357" s="2">
         <v>1635.9</v>
       </c>
     </row>
@@ -11691,10 +11697,10 @@
       <c r="F358" t="s">
         <v>14</v>
       </c>
-      <c r="G358" s="1">
+      <c r="G358" s="3">
         <v>46149</v>
       </c>
-      <c r="H358" s="3">
+      <c r="H358" s="2">
         <v>1609.21</v>
       </c>
     </row>
@@ -11717,10 +11723,10 @@
       <c r="F359" t="s">
         <v>10</v>
       </c>
-      <c r="G359">
+      <c r="G359" s="3">
         <v>46153</v>
       </c>
-      <c r="H359" s="3">
+      <c r="H359" s="2">
         <v>1867.47</v>
       </c>
     </row>
@@ -11743,10 +11749,10 @@
       <c r="F360" t="s">
         <v>10</v>
       </c>
-      <c r="G360" s="1">
+      <c r="G360" s="3">
         <v>46151</v>
       </c>
-      <c r="H360" s="3">
+      <c r="H360" s="2">
         <v>80790.100000000006</v>
       </c>
     </row>
@@ -11769,10 +11775,10 @@
       <c r="F361" t="s">
         <v>10</v>
       </c>
-      <c r="G361">
+      <c r="G361" s="3">
         <v>46155</v>
       </c>
-      <c r="H361" s="3">
+      <c r="H361" s="2">
         <v>6620.35</v>
       </c>
     </row>
@@ -11795,10 +11801,10 @@
       <c r="F362" t="s">
         <v>10</v>
       </c>
-      <c r="G362">
+      <c r="G362" s="3">
         <v>46153</v>
       </c>
-      <c r="H362" s="3">
+      <c r="H362" s="2">
         <v>81273.23</v>
       </c>
     </row>
@@ -11821,10 +11827,10 @@
       <c r="F363" t="s">
         <v>10</v>
       </c>
-      <c r="G363" s="1">
+      <c r="G363" s="3">
         <v>46153</v>
       </c>
-      <c r="H363" s="3">
+      <c r="H363" s="2">
         <v>10291</v>
       </c>
     </row>
@@ -11847,10 +11853,10 @@
       <c r="F364" t="s">
         <v>10</v>
       </c>
-      <c r="G364">
+      <c r="G364" s="3">
         <v>46155</v>
       </c>
-      <c r="H364" s="3">
+      <c r="H364" s="2">
         <v>6723.53</v>
       </c>
     </row>
@@ -11873,10 +11879,10 @@
       <c r="F365" t="s">
         <v>10</v>
       </c>
-      <c r="G365">
+      <c r="G365" s="3">
         <v>46155</v>
       </c>
-      <c r="H365" s="3">
+      <c r="H365" s="2">
         <v>4073.3</v>
       </c>
     </row>
@@ -11899,10 +11905,10 @@
       <c r="F366" t="s">
         <v>28</v>
       </c>
-      <c r="G366">
+      <c r="G366" s="3">
         <v>46148</v>
       </c>
-      <c r="H366" s="3">
+      <c r="H366" s="2">
         <v>21353.02</v>
       </c>
     </row>
@@ -11925,10 +11931,10 @@
       <c r="F367" t="s">
         <v>10</v>
       </c>
-      <c r="G367">
+      <c r="G367" s="3">
         <v>46155</v>
       </c>
-      <c r="H367" s="3">
+      <c r="H367" s="2">
         <v>4089.21</v>
       </c>
     </row>
@@ -11951,10 +11957,10 @@
       <c r="F368" t="s">
         <v>10</v>
       </c>
-      <c r="G368" s="1">
+      <c r="G368" s="3">
         <v>46155</v>
       </c>
-      <c r="H368" s="3">
+      <c r="H368" s="2">
         <v>4363.8900000000003</v>
       </c>
     </row>
@@ -11977,10 +11983,10 @@
       <c r="F369" t="s">
         <v>28</v>
       </c>
-      <c r="G369">
+      <c r="G369" s="3">
         <v>46148</v>
       </c>
-      <c r="H369" s="3">
+      <c r="H369" s="2">
         <v>63033.38</v>
       </c>
     </row>
@@ -12003,10 +12009,10 @@
       <c r="F370" t="s">
         <v>10</v>
       </c>
-      <c r="G370">
+      <c r="G370" s="3">
         <v>46149</v>
       </c>
-      <c r="H370" s="3">
+      <c r="H370" s="2">
         <v>19928.669999999998</v>
       </c>
     </row>
@@ -12029,10 +12035,10 @@
       <c r="F371" t="s">
         <v>10</v>
       </c>
-      <c r="G371">
+      <c r="G371" s="3">
         <v>46155</v>
       </c>
-      <c r="H371" s="3">
+      <c r="H371" s="2">
         <v>4050.83</v>
       </c>
     </row>
@@ -12055,10 +12061,10 @@
       <c r="F372" t="s">
         <v>10</v>
       </c>
-      <c r="G372">
+      <c r="G372" s="3">
         <v>46153</v>
       </c>
-      <c r="H372" s="3">
+      <c r="H372" s="2">
         <v>20436.259999999998</v>
       </c>
     </row>
@@ -12081,10 +12087,10 @@
       <c r="F373" t="s">
         <v>10</v>
       </c>
-      <c r="G373">
+      <c r="G373" s="3">
         <v>46155</v>
       </c>
-      <c r="H373" s="3">
+      <c r="H373" s="2">
         <v>4097.6099999999997</v>
       </c>
     </row>
@@ -12107,10 +12113,10 @@
       <c r="F374" t="s">
         <v>28</v>
       </c>
-      <c r="G374">
+      <c r="G374" s="3">
         <v>46148</v>
       </c>
-      <c r="H374" s="3">
+      <c r="H374" s="2">
         <v>9325.02</v>
       </c>
     </row>
@@ -12133,10 +12139,10 @@
       <c r="F375" t="s">
         <v>10</v>
       </c>
-      <c r="G375">
+      <c r="G375" s="3">
         <v>46153</v>
       </c>
-      <c r="H375" s="3">
+      <c r="H375" s="2">
         <v>3997.08</v>
       </c>
     </row>
@@ -12159,10 +12165,10 @@
       <c r="F376" t="s">
         <v>10</v>
       </c>
-      <c r="G376">
+      <c r="G376" s="3">
         <v>46151</v>
       </c>
-      <c r="H376" s="3">
+      <c r="H376" s="2">
         <v>8352.59</v>
       </c>
     </row>
@@ -12185,10 +12191,10 @@
       <c r="F377" t="s">
         <v>10</v>
       </c>
-      <c r="G377" s="1">
+      <c r="G377" s="3">
         <v>46157</v>
       </c>
-      <c r="H377" s="3">
+      <c r="H377" s="2">
         <v>5191.22</v>
       </c>
     </row>
@@ -12211,10 +12217,10 @@
       <c r="F378" t="s">
         <v>10</v>
       </c>
-      <c r="G378">
+      <c r="G378" s="3">
         <v>46151</v>
       </c>
-      <c r="H378" s="3">
+      <c r="H378" s="2">
         <v>6245.99</v>
       </c>
     </row>
@@ -12237,10 +12243,10 @@
       <c r="F379" t="s">
         <v>20</v>
       </c>
-      <c r="G379">
+      <c r="G379" s="3">
         <v>46149</v>
       </c>
-      <c r="H379" s="3">
+      <c r="H379" s="2">
         <v>26079.09</v>
       </c>
     </row>
@@ -12263,10 +12269,10 @@
       <c r="F380" t="s">
         <v>20</v>
       </c>
-      <c r="G380">
+      <c r="G380" s="3">
         <v>46149</v>
       </c>
-      <c r="H380" s="3">
+      <c r="H380" s="2">
         <v>16649.5</v>
       </c>
     </row>
@@ -12289,10 +12295,10 @@
       <c r="F381" t="s">
         <v>28</v>
       </c>
-      <c r="G381">
+      <c r="G381" s="3">
         <v>46148</v>
       </c>
-      <c r="H381" s="3">
+      <c r="H381" s="2">
         <v>36151.300000000003</v>
       </c>
     </row>
@@ -12315,10 +12321,10 @@
       <c r="F382" t="s">
         <v>20</v>
       </c>
-      <c r="G382" s="1">
+      <c r="G382" s="3">
         <v>46149</v>
       </c>
-      <c r="H382" s="3">
+      <c r="H382" s="2">
         <v>26399.99</v>
       </c>
     </row>
@@ -12341,10 +12347,10 @@
       <c r="F383" t="s">
         <v>10</v>
       </c>
-      <c r="G383">
+      <c r="G383" s="3">
         <v>46153</v>
       </c>
-      <c r="H383" s="3">
+      <c r="H383" s="2">
         <v>60975.12</v>
       </c>
     </row>
@@ -12367,10 +12373,10 @@
       <c r="F384" t="s">
         <v>28</v>
       </c>
-      <c r="G384" s="1">
+      <c r="G384" s="3">
         <v>46148</v>
       </c>
-      <c r="H384" s="3">
+      <c r="H384" s="2">
         <v>3547.88</v>
       </c>
     </row>
@@ -12393,10 +12399,10 @@
       <c r="F385" t="s">
         <v>10</v>
       </c>
-      <c r="G385">
+      <c r="G385" s="3">
         <v>46151</v>
       </c>
-      <c r="H385" s="3">
+      <c r="H385" s="2">
         <v>6133.16</v>
       </c>
     </row>
@@ -12419,10 +12425,10 @@
       <c r="F386" t="s">
         <v>28</v>
       </c>
-      <c r="G386" s="1">
+      <c r="G386" s="3">
         <v>46148</v>
       </c>
-      <c r="H386" s="3">
+      <c r="H386" s="2">
         <v>6389.65</v>
       </c>
     </row>
@@ -12445,10 +12451,10 @@
       <c r="F387" t="s">
         <v>50</v>
       </c>
-      <c r="G387" t="s">
+      <c r="G387" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H387" s="3">
+      <c r="H387" s="2">
         <v>6428.1</v>
       </c>
     </row>
@@ -12471,10 +12477,10 @@
       <c r="F388" t="s">
         <v>28</v>
       </c>
-      <c r="G388" s="1">
+      <c r="G388" s="3">
         <v>46148</v>
       </c>
-      <c r="H388" s="3">
+      <c r="H388" s="2">
         <v>1308.06</v>
       </c>
     </row>
@@ -12497,10 +12503,10 @@
       <c r="F389" t="s">
         <v>28</v>
       </c>
-      <c r="G389">
+      <c r="G389" s="3">
         <v>46148</v>
       </c>
-      <c r="H389" s="3">
+      <c r="H389" s="2">
         <v>1249.18</v>
       </c>
     </row>
@@ -12523,10 +12529,10 @@
       <c r="F390" t="s">
         <v>28</v>
       </c>
-      <c r="G390" s="1">
+      <c r="G390" s="3">
         <v>46148</v>
       </c>
-      <c r="H390" s="3">
+      <c r="H390" s="2">
         <v>5340.06</v>
       </c>
     </row>
@@ -12549,10 +12555,10 @@
       <c r="F391" t="s">
         <v>28</v>
       </c>
-      <c r="G391" s="1">
+      <c r="G391" s="3">
         <v>46148</v>
       </c>
-      <c r="H391" s="3">
+      <c r="H391" s="2">
         <v>1340.43</v>
       </c>
     </row>
@@ -12575,10 +12581,10 @@
       <c r="F392" t="s">
         <v>10</v>
       </c>
-      <c r="G392" s="1">
+      <c r="G392" s="3">
         <v>46151</v>
       </c>
-      <c r="H392" s="3">
+      <c r="H392" s="2">
         <v>4031.45</v>
       </c>
     </row>
@@ -12601,10 +12607,10 @@
       <c r="F393" t="s">
         <v>28</v>
       </c>
-      <c r="G393" s="1">
+      <c r="G393" s="3">
         <v>46148</v>
       </c>
-      <c r="H393" s="3">
+      <c r="H393" s="2">
         <v>1534.89</v>
       </c>
     </row>
@@ -12627,10 +12633,10 @@
       <c r="F394" t="s">
         <v>28</v>
       </c>
-      <c r="G394">
+      <c r="G394" s="3">
         <v>46148</v>
       </c>
-      <c r="H394" s="3">
+      <c r="H394" s="2">
         <v>1803.4</v>
       </c>
     </row>
@@ -12653,10 +12659,10 @@
       <c r="F395" t="s">
         <v>10</v>
       </c>
-      <c r="G395" s="1">
+      <c r="G395" s="3">
         <v>46153</v>
       </c>
-      <c r="H395" s="3">
+      <c r="H395" s="2">
         <v>3189.9</v>
       </c>
     </row>
@@ -12679,10 +12685,10 @@
       <c r="F396" t="s">
         <v>28</v>
       </c>
-      <c r="G396" s="1">
+      <c r="G396" s="3">
         <v>46148</v>
       </c>
-      <c r="H396" s="3">
+      <c r="H396" s="2">
         <v>1387.87</v>
       </c>
     </row>
@@ -12705,10 +12711,10 @@
       <c r="F397" t="s">
         <v>28</v>
       </c>
-      <c r="G397">
+      <c r="G397" s="3">
         <v>46148</v>
       </c>
-      <c r="H397" s="3">
+      <c r="H397" s="2">
         <v>1725.55</v>
       </c>
     </row>
@@ -12731,10 +12737,10 @@
       <c r="F398" t="s">
         <v>28</v>
       </c>
-      <c r="G398" s="1">
+      <c r="G398" s="3">
         <v>46148</v>
       </c>
-      <c r="H398" s="3">
+      <c r="H398" s="2">
         <v>3891.47</v>
       </c>
     </row>
@@ -12757,10 +12763,10 @@
       <c r="F399" t="s">
         <v>10</v>
       </c>
-      <c r="G399" s="1">
+      <c r="G399" s="3">
         <v>46149</v>
       </c>
-      <c r="H399" s="3">
+      <c r="H399" s="2">
         <v>1852.48</v>
       </c>
     </row>
@@ -12783,10 +12789,10 @@
       <c r="F400" t="s">
         <v>10</v>
       </c>
-      <c r="G400">
+      <c r="G400" s="3">
         <v>46163</v>
       </c>
-      <c r="H400" s="3">
+      <c r="H400" s="2">
         <v>5264.9</v>
       </c>
     </row>
@@ -12809,10 +12815,10 @@
       <c r="F401" t="s">
         <v>10</v>
       </c>
-      <c r="G401">
+      <c r="G401" s="3">
         <v>46149</v>
       </c>
-      <c r="H401" s="3">
+      <c r="H401" s="2">
         <v>10151.92</v>
       </c>
     </row>
@@ -12835,10 +12841,10 @@
       <c r="F402" t="s">
         <v>10</v>
       </c>
-      <c r="G402">
+      <c r="G402" s="3">
         <v>46149</v>
       </c>
-      <c r="H402" s="3">
+      <c r="H402" s="2">
         <v>14223.32</v>
       </c>
     </row>
@@ -12861,10 +12867,10 @@
       <c r="F403" t="s">
         <v>10</v>
       </c>
-      <c r="G403" s="1">
+      <c r="G403" s="3">
         <v>46149</v>
       </c>
-      <c r="H403" s="3">
+      <c r="H403" s="2">
         <v>31775.14</v>
       </c>
     </row>
@@ -12887,10 +12893,10 @@
       <c r="F404" t="s">
         <v>26</v>
       </c>
-      <c r="G404" t="s">
+      <c r="G404" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H404" s="3">
+      <c r="H404" s="2">
         <v>5381.49</v>
       </c>
     </row>
@@ -12913,10 +12919,10 @@
       <c r="F405" t="s">
         <v>10</v>
       </c>
-      <c r="G405">
+      <c r="G405" s="3">
         <v>46155</v>
       </c>
-      <c r="H405" s="3">
+      <c r="H405" s="2">
         <v>5620.29</v>
       </c>
     </row>
@@ -12939,10 +12945,10 @@
       <c r="F406" t="s">
         <v>28</v>
       </c>
-      <c r="G406">
+      <c r="G406" s="3">
         <v>46148</v>
       </c>
-      <c r="H406" s="3">
+      <c r="H406" s="2">
         <v>1198.51</v>
       </c>
     </row>
@@ -12965,10 +12971,10 @@
       <c r="F407" t="s">
         <v>28</v>
       </c>
-      <c r="G407">
+      <c r="G407" s="3">
         <v>46148</v>
       </c>
-      <c r="H407" s="3">
+      <c r="H407" s="2">
         <v>1267.42</v>
       </c>
     </row>
@@ -12991,10 +12997,10 @@
       <c r="F408" t="s">
         <v>28</v>
       </c>
-      <c r="G408" s="1">
+      <c r="G408" s="3">
         <v>46148</v>
       </c>
-      <c r="H408" s="3">
+      <c r="H408" s="2">
         <v>1160.28</v>
       </c>
     </row>
@@ -13017,10 +13023,10 @@
       <c r="F409" t="s">
         <v>28</v>
       </c>
-      <c r="G409">
+      <c r="G409" s="3">
         <v>46148</v>
       </c>
-      <c r="H409" s="3">
+      <c r="H409" s="2">
         <v>1269.57</v>
       </c>
     </row>
@@ -13043,10 +13049,10 @@
       <c r="F410" t="s">
         <v>28</v>
       </c>
-      <c r="G410">
+      <c r="G410" s="3">
         <v>46148</v>
       </c>
-      <c r="H410" s="3">
+      <c r="H410" s="2">
         <v>1409.75</v>
       </c>
     </row>
@@ -13069,10 +13075,10 @@
       <c r="F411" t="s">
         <v>28</v>
       </c>
-      <c r="G411" s="1">
+      <c r="G411" s="3">
         <v>46148</v>
       </c>
-      <c r="H411" s="3">
+      <c r="H411" s="2">
         <v>1241.21</v>
       </c>
     </row>
@@ -13095,10 +13101,10 @@
       <c r="F412" t="s">
         <v>10</v>
       </c>
-      <c r="G412">
+      <c r="G412" s="3">
         <v>46149</v>
       </c>
-      <c r="H412" s="3">
+      <c r="H412" s="2">
         <v>1319.77</v>
       </c>
     </row>
@@ -13121,10 +13127,10 @@
       <c r="F413" t="s">
         <v>10</v>
       </c>
-      <c r="G413" s="1">
+      <c r="G413" s="3">
         <v>46153</v>
       </c>
-      <c r="H413" s="3">
+      <c r="H413" s="2">
         <v>6228.95</v>
       </c>
     </row>
@@ -13147,10 +13153,10 @@
       <c r="F414" t="s">
         <v>125</v>
       </c>
-      <c r="G414">
+      <c r="G414" s="3">
         <v>46149</v>
       </c>
-      <c r="H414" s="3">
+      <c r="H414" s="2">
         <v>581.29999999999995</v>
       </c>
     </row>
@@ -13173,10 +13179,10 @@
       <c r="F415" t="s">
         <v>125</v>
       </c>
-      <c r="G415">
+      <c r="G415" s="3">
         <v>46149</v>
       </c>
-      <c r="H415" s="3">
+      <c r="H415" s="2">
         <v>854.39</v>
       </c>
     </row>
@@ -13199,10 +13205,10 @@
       <c r="F416" t="s">
         <v>10</v>
       </c>
-      <c r="G416" s="1">
+      <c r="G416" s="3">
         <v>46155</v>
       </c>
-      <c r="H416" s="3">
+      <c r="H416" s="2">
         <v>1458.79</v>
       </c>
     </row>
@@ -13225,10 +13231,10 @@
       <c r="F417" t="s">
         <v>10</v>
       </c>
-      <c r="G417">
+      <c r="G417" s="3">
         <v>46148</v>
       </c>
-      <c r="H417" s="3">
+      <c r="H417" s="2">
         <v>463.94</v>
       </c>
     </row>
@@ -13251,10 +13257,10 @@
       <c r="F418" t="s">
         <v>125</v>
       </c>
-      <c r="G418" s="1">
+      <c r="G418" s="3">
         <v>46149</v>
       </c>
-      <c r="H418" s="3">
+      <c r="H418" s="2">
         <v>489.54</v>
       </c>
     </row>
@@ -13277,10 +13283,10 @@
       <c r="F419" t="s">
         <v>10</v>
       </c>
-      <c r="G419" s="1">
+      <c r="G419" s="3">
         <v>46155</v>
       </c>
-      <c r="H419" s="3">
+      <c r="H419" s="2">
         <v>781.64</v>
       </c>
     </row>
@@ -13303,10 +13309,10 @@
       <c r="F420" t="s">
         <v>10</v>
       </c>
-      <c r="G420" s="1">
+      <c r="G420" s="3">
         <v>46148</v>
       </c>
-      <c r="H420" s="3">
+      <c r="H420" s="2">
         <v>434.29</v>
       </c>
     </row>
@@ -13329,10 +13335,10 @@
       <c r="F421" t="s">
         <v>10</v>
       </c>
-      <c r="G421" s="1">
+      <c r="G421" s="3">
         <v>46148</v>
       </c>
-      <c r="H421" s="3">
+      <c r="H421" s="2">
         <v>756.86</v>
       </c>
     </row>
@@ -13355,10 +13361,10 @@
       <c r="F422" t="s">
         <v>125</v>
       </c>
-      <c r="G422" s="1">
+      <c r="G422" s="3">
         <v>46149</v>
       </c>
-      <c r="H422" s="3">
+      <c r="H422" s="2">
         <v>415.94</v>
       </c>
     </row>
@@ -13381,10 +13387,10 @@
       <c r="F423" t="s">
         <v>125</v>
       </c>
-      <c r="G423" s="1">
+      <c r="G423" s="3">
         <v>46149</v>
       </c>
-      <c r="H423" s="3">
+      <c r="H423" s="2">
         <v>447.92</v>
       </c>
     </row>
@@ -13407,10 +13413,10 @@
       <c r="F424" t="s">
         <v>125</v>
       </c>
-      <c r="G424">
+      <c r="G424" s="3">
         <v>46149</v>
       </c>
-      <c r="H424" s="3">
+      <c r="H424" s="2">
         <v>3003.79</v>
       </c>
     </row>
@@ -13433,10 +13439,10 @@
       <c r="F425" t="s">
         <v>10</v>
       </c>
-      <c r="G425">
+      <c r="G425" s="3">
         <v>46155</v>
       </c>
-      <c r="H425" s="3">
+      <c r="H425" s="2">
         <v>454.49</v>
       </c>
     </row>
@@ -13459,10 +13465,10 @@
       <c r="F426" t="s">
         <v>125</v>
       </c>
-      <c r="G426" s="1">
+      <c r="G426" s="3">
         <v>46149</v>
       </c>
-      <c r="H426" s="3">
+      <c r="H426" s="2">
         <v>443.85</v>
       </c>
     </row>
@@ -13485,10 +13491,10 @@
       <c r="F427" t="s">
         <v>10</v>
       </c>
-      <c r="G427" s="1">
+      <c r="G427" s="3">
         <v>46148</v>
       </c>
-      <c r="H427" s="3">
+      <c r="H427" s="2">
         <v>2945.82</v>
       </c>
     </row>
@@ -13511,10 +13517,10 @@
       <c r="F428" t="s">
         <v>125</v>
       </c>
-      <c r="G428" s="1">
+      <c r="G428" s="3">
         <v>46149</v>
       </c>
-      <c r="H428" s="3">
+      <c r="H428" s="2">
         <v>865.22</v>
       </c>
     </row>
@@ -13537,10 +13543,10 @@
       <c r="F429" t="s">
         <v>10</v>
       </c>
-      <c r="G429" s="1">
+      <c r="G429" s="3">
         <v>46148</v>
       </c>
-      <c r="H429" s="3">
+      <c r="H429" s="2">
         <v>1086.3900000000001</v>
       </c>
     </row>
@@ -13563,10 +13569,10 @@
       <c r="F430" t="s">
         <v>10</v>
       </c>
-      <c r="G430" s="1">
+      <c r="G430" s="3">
         <v>46148</v>
       </c>
-      <c r="H430" s="3">
+      <c r="H430" s="2">
         <v>1459.55</v>
       </c>
     </row>
@@ -13589,10 +13595,10 @@
       <c r="F431" t="s">
         <v>10</v>
       </c>
-      <c r="G431">
+      <c r="G431" s="3">
         <v>46155</v>
       </c>
-      <c r="H431" s="3">
+      <c r="H431" s="2">
         <v>630.49</v>
       </c>
     </row>
@@ -13615,10 +13621,10 @@
       <c r="F432" t="s">
         <v>10</v>
       </c>
-      <c r="G432" s="1">
+      <c r="G432" s="3">
         <v>46148</v>
       </c>
-      <c r="H432" s="3">
+      <c r="H432" s="2">
         <v>2870.7</v>
       </c>
     </row>
@@ -13641,10 +13647,10 @@
       <c r="F433" t="s">
         <v>125</v>
       </c>
-      <c r="G433" s="1">
+      <c r="G433" s="3">
         <v>46149</v>
       </c>
-      <c r="H433" s="3">
+      <c r="H433" s="2">
         <v>549.37</v>
       </c>
     </row>
@@ -13667,10 +13673,10 @@
       <c r="F434" t="s">
         <v>10</v>
       </c>
-      <c r="G434" s="1">
+      <c r="G434" s="3">
         <v>46155</v>
       </c>
-      <c r="H434" s="3">
+      <c r="H434" s="2">
         <v>2496.85</v>
       </c>
     </row>
@@ -13693,10 +13699,10 @@
       <c r="F435" t="s">
         <v>125</v>
       </c>
-      <c r="G435" s="1">
+      <c r="G435" s="3">
         <v>46149</v>
       </c>
-      <c r="H435" s="3">
+      <c r="H435" s="2">
         <v>447.54</v>
       </c>
     </row>
@@ -13719,10 +13725,10 @@
       <c r="F436" t="s">
         <v>10</v>
       </c>
-      <c r="G436" s="1">
+      <c r="G436" s="3">
         <v>46148</v>
       </c>
-      <c r="H436" s="3">
+      <c r="H436" s="2">
         <v>1007.48</v>
       </c>
     </row>
@@ -13745,10 +13751,10 @@
       <c r="F437" t="s">
         <v>125</v>
       </c>
-      <c r="G437">
+      <c r="G437" s="3">
         <v>46149</v>
       </c>
-      <c r="H437" s="3">
+      <c r="H437" s="2">
         <v>418.48</v>
       </c>
     </row>
@@ -13771,10 +13777,10 @@
       <c r="F438" t="s">
         <v>125</v>
       </c>
-      <c r="G438">
+      <c r="G438" s="3">
         <v>46149</v>
       </c>
-      <c r="H438" s="3">
+      <c r="H438" s="2">
         <v>493.03</v>
       </c>
     </row>
@@ -13797,10 +13803,10 @@
       <c r="F439" t="s">
         <v>125</v>
       </c>
-      <c r="G439" s="1">
+      <c r="G439" s="3">
         <v>46149</v>
       </c>
-      <c r="H439" s="3">
+      <c r="H439" s="2">
         <v>1119.02</v>
       </c>
     </row>
@@ -13823,10 +13829,10 @@
       <c r="F440" t="s">
         <v>10</v>
       </c>
-      <c r="G440" s="1">
+      <c r="G440" s="3">
         <v>46148</v>
       </c>
-      <c r="H440" s="3">
+      <c r="H440" s="2">
         <v>450.09</v>
       </c>
     </row>
@@ -13849,10 +13855,10 @@
       <c r="F441" t="s">
         <v>10</v>
       </c>
-      <c r="G441">
+      <c r="G441" s="3">
         <v>46148</v>
       </c>
-      <c r="H441" s="3">
+      <c r="H441" s="2">
         <v>541.74</v>
       </c>
     </row>
@@ -13875,10 +13881,10 @@
       <c r="F442" t="s">
         <v>125</v>
       </c>
-      <c r="G442">
+      <c r="G442" s="3">
         <v>46149</v>
       </c>
-      <c r="H442" s="3">
+      <c r="H442" s="2">
         <v>596.64</v>
       </c>
     </row>
@@ -13901,10 +13907,10 @@
       <c r="F443" t="s">
         <v>125</v>
       </c>
-      <c r="G443" s="1">
+      <c r="G443" s="3">
         <v>46149</v>
       </c>
-      <c r="H443" s="3">
+      <c r="H443" s="2">
         <v>413.02</v>
       </c>
     </row>
@@ -13927,10 +13933,10 @@
       <c r="F444" t="s">
         <v>10</v>
       </c>
-      <c r="G444" s="1">
+      <c r="G444" s="3">
         <v>46148</v>
       </c>
-      <c r="H444" s="3">
+      <c r="H444" s="2">
         <v>569.02</v>
       </c>
     </row>
@@ -13953,10 +13959,10 @@
       <c r="F445" t="s">
         <v>125</v>
       </c>
-      <c r="G445">
+      <c r="G445" s="3">
         <v>46149</v>
       </c>
-      <c r="H445" s="3">
+      <c r="H445" s="2">
         <v>495.26</v>
       </c>
     </row>
@@ -13979,10 +13985,10 @@
       <c r="F446" t="s">
         <v>10</v>
       </c>
-      <c r="G446">
+      <c r="G446" s="3">
         <v>46153</v>
       </c>
-      <c r="H446" s="3">
+      <c r="H446" s="2">
         <v>520.69000000000005</v>
       </c>
     </row>
@@ -14005,10 +14011,10 @@
       <c r="F447" t="s">
         <v>125</v>
       </c>
-      <c r="G447">
+      <c r="G447" s="3">
         <v>46149</v>
       </c>
-      <c r="H447" s="3">
+      <c r="H447" s="2">
         <v>485.23</v>
       </c>
     </row>
@@ -14031,10 +14037,10 @@
       <c r="F448" t="s">
         <v>10</v>
       </c>
-      <c r="G448" s="1">
+      <c r="G448" s="3">
         <v>46148</v>
       </c>
-      <c r="H448" s="3">
+      <c r="H448" s="2">
         <v>438.43</v>
       </c>
     </row>
@@ -14057,10 +14063,10 @@
       <c r="F449" t="s">
         <v>31</v>
       </c>
-      <c r="G449" s="1" t="s">
+      <c r="G449" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H449" s="3">
+      <c r="H449" s="2">
         <v>1004.22</v>
       </c>
     </row>
@@ -14083,10 +14089,10 @@
       <c r="F450" t="s">
         <v>10</v>
       </c>
-      <c r="G450">
+      <c r="G450" s="3">
         <v>46148</v>
       </c>
-      <c r="H450" s="3">
+      <c r="H450" s="2">
         <v>1222</v>
       </c>
     </row>
@@ -14109,10 +14115,10 @@
       <c r="F451" t="s">
         <v>10</v>
       </c>
-      <c r="G451">
+      <c r="G451" s="3">
         <v>46155</v>
       </c>
-      <c r="H451" s="3">
+      <c r="H451" s="2">
         <v>805.15</v>
       </c>
     </row>
@@ -14135,10 +14141,10 @@
       <c r="F452" t="s">
         <v>10</v>
       </c>
-      <c r="G452">
+      <c r="G452" s="3">
         <v>46153</v>
       </c>
-      <c r="H452" s="3">
+      <c r="H452" s="2">
         <v>1086.6600000000001</v>
       </c>
     </row>
@@ -14161,10 +14167,10 @@
       <c r="F453" t="s">
         <v>10</v>
       </c>
-      <c r="G453" s="1">
+      <c r="G453" s="3">
         <v>46153</v>
       </c>
-      <c r="H453" s="3">
+      <c r="H453" s="2">
         <v>1677.04</v>
       </c>
     </row>
@@ -14187,10 +14193,10 @@
       <c r="F454" t="s">
         <v>10</v>
       </c>
-      <c r="G454" s="1" t="s">
+      <c r="G454" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H454" s="3">
+      <c r="H454" s="2">
         <v>1630.26</v>
       </c>
     </row>
@@ -14213,10 +14219,10 @@
       <c r="F455" t="s">
         <v>10</v>
       </c>
-      <c r="G455" s="1">
+      <c r="G455" s="3">
         <v>46155</v>
       </c>
-      <c r="H455" s="3">
+      <c r="H455" s="2">
         <v>2773.36</v>
       </c>
     </row>
@@ -14239,10 +14245,10 @@
       <c r="F456" t="s">
         <v>10</v>
       </c>
-      <c r="G456" s="1">
+      <c r="G456" s="3">
         <v>46155</v>
       </c>
-      <c r="H456" s="3">
+      <c r="H456" s="2">
         <v>2126.3200000000002</v>
       </c>
     </row>
@@ -14265,10 +14271,10 @@
       <c r="F457" t="s">
         <v>10</v>
       </c>
-      <c r="G457" s="1">
+      <c r="G457" s="3">
         <v>46148</v>
       </c>
-      <c r="H457" s="3">
+      <c r="H457" s="2">
         <v>1591.09</v>
       </c>
     </row>
@@ -14291,10 +14297,10 @@
       <c r="F458" t="s">
         <v>10</v>
       </c>
-      <c r="G458" s="1" t="s">
+      <c r="G458" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H458" s="3">
+      <c r="H458" s="2">
         <v>1411.13</v>
       </c>
     </row>
@@ -14317,10 +14323,10 @@
       <c r="F459" t="s">
         <v>10</v>
       </c>
-      <c r="G459" s="1">
+      <c r="G459" s="3">
         <v>46148</v>
       </c>
-      <c r="H459" s="3">
+      <c r="H459" s="2">
         <v>1670.13</v>
       </c>
     </row>
@@ -14343,10 +14349,10 @@
       <c r="F460" t="s">
         <v>10</v>
       </c>
-      <c r="G460" s="1">
+      <c r="G460" s="3">
         <v>46149</v>
       </c>
-      <c r="H460" s="3">
+      <c r="H460" s="2">
         <v>15651.46</v>
       </c>
     </row>
@@ -14369,10 +14375,10 @@
       <c r="F461" t="s">
         <v>10</v>
       </c>
-      <c r="G461">
+      <c r="G461" s="3">
         <v>46149</v>
       </c>
-      <c r="H461" s="3">
+      <c r="H461" s="2">
         <v>3654.36</v>
       </c>
     </row>
@@ -14395,10 +14401,10 @@
       <c r="F462" t="s">
         <v>10</v>
       </c>
-      <c r="G462">
+      <c r="G462" s="3">
         <v>46149</v>
       </c>
-      <c r="H462" s="3">
+      <c r="H462" s="2">
         <v>3794.7</v>
       </c>
     </row>
@@ -14421,10 +14427,10 @@
       <c r="F463" t="s">
         <v>10</v>
       </c>
-      <c r="G463">
+      <c r="G463" s="3">
         <v>46151</v>
       </c>
-      <c r="H463" s="3">
+      <c r="H463" s="2">
         <v>3662.02</v>
       </c>
     </row>
@@ -14447,10 +14453,10 @@
       <c r="F464" t="s">
         <v>28</v>
       </c>
-      <c r="G464" s="1">
+      <c r="G464" s="3">
         <v>46148</v>
       </c>
-      <c r="H464" s="3">
+      <c r="H464" s="2">
         <v>39340.839999999997</v>
       </c>
     </row>
@@ -14473,10 +14479,10 @@
       <c r="F465" t="s">
         <v>28</v>
       </c>
-      <c r="G465">
+      <c r="G465" s="3">
         <v>46148</v>
       </c>
-      <c r="H465" s="3">
+      <c r="H465" s="2">
         <v>5591.24</v>
       </c>
     </row>
@@ -14499,10 +14505,10 @@
       <c r="F466" t="s">
         <v>28</v>
       </c>
-      <c r="G466">
+      <c r="G466" s="3">
         <v>46148</v>
       </c>
-      <c r="H466" s="3">
+      <c r="H466" s="2">
         <v>13412.74</v>
       </c>
     </row>
@@ -14525,10 +14531,10 @@
       <c r="F467" t="s">
         <v>31</v>
       </c>
-      <c r="G467" s="1" t="s">
+      <c r="G467" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H467" s="3">
+      <c r="H467" s="2">
         <v>7619.39</v>
       </c>
     </row>
@@ -14551,10 +14557,10 @@
       <c r="F468" t="s">
         <v>28</v>
       </c>
-      <c r="G468" s="1">
+      <c r="G468" s="3">
         <v>46148</v>
       </c>
-      <c r="H468" s="3">
+      <c r="H468" s="2">
         <v>3707.96</v>
       </c>
     </row>
@@ -14577,10 +14583,10 @@
       <c r="F469" t="s">
         <v>10</v>
       </c>
-      <c r="G469">
+      <c r="G469" s="3">
         <v>46151</v>
       </c>
-      <c r="H469" s="3">
+      <c r="H469" s="2">
         <v>4028.02</v>
       </c>
     </row>
@@ -14603,10 +14609,10 @@
       <c r="F470" t="s">
         <v>10</v>
       </c>
-      <c r="G470">
+      <c r="G470" s="3">
         <v>46151</v>
       </c>
-      <c r="H470" s="3">
+      <c r="H470" s="2">
         <v>4032.84</v>
       </c>
     </row>
@@ -14629,10 +14635,10 @@
       <c r="F471" t="s">
         <v>20</v>
       </c>
-      <c r="G471" s="1">
+      <c r="G471" s="3">
         <v>46149</v>
       </c>
-      <c r="H471" s="3">
+      <c r="H471" s="2">
         <v>4601.8500000000004</v>
       </c>
     </row>
@@ -14655,10 +14661,10 @@
       <c r="F472" t="s">
         <v>28</v>
       </c>
-      <c r="G472" s="1">
+      <c r="G472" s="3">
         <v>46148</v>
       </c>
-      <c r="H472" s="3">
+      <c r="H472" s="2">
         <v>3502.06</v>
       </c>
     </row>
@@ -14681,10 +14687,10 @@
       <c r="F473" t="s">
         <v>10</v>
       </c>
-      <c r="G473">
+      <c r="G473" s="3">
         <v>46151</v>
       </c>
-      <c r="H473" s="3">
+      <c r="H473" s="2">
         <v>6596.79</v>
       </c>
     </row>
@@ -14707,10 +14713,10 @@
       <c r="F474" t="s">
         <v>10</v>
       </c>
-      <c r="G474">
+      <c r="G474" s="3">
         <v>46149</v>
       </c>
-      <c r="H474" s="3">
+      <c r="H474" s="2">
         <v>6087.21</v>
       </c>
     </row>
@@ -14733,10 +14739,10 @@
       <c r="F475" t="s">
         <v>10</v>
       </c>
-      <c r="G475">
+      <c r="G475" s="3">
         <v>46149</v>
       </c>
-      <c r="H475" s="3">
+      <c r="H475" s="2">
         <v>28997.65</v>
       </c>
     </row>
@@ -14759,10 +14765,10 @@
       <c r="F476" t="s">
         <v>28</v>
       </c>
-      <c r="G476">
+      <c r="G476" s="3">
         <v>46148</v>
       </c>
-      <c r="H476" s="3">
+      <c r="H476" s="2">
         <v>4180.82</v>
       </c>
     </row>
@@ -14785,10 +14791,10 @@
       <c r="F477" t="s">
         <v>28</v>
       </c>
-      <c r="G477">
+      <c r="G477" s="3">
         <v>46148</v>
       </c>
-      <c r="H477" s="3">
+      <c r="H477" s="2">
         <v>3699.46</v>
       </c>
     </row>
@@ -14811,10 +14817,10 @@
       <c r="F478" t="s">
         <v>28</v>
       </c>
-      <c r="G478">
+      <c r="G478" s="3">
         <v>46148</v>
       </c>
-      <c r="H478" s="3">
+      <c r="H478" s="2">
         <v>3441.23</v>
       </c>
     </row>
@@ -14837,10 +14843,10 @@
       <c r="F479" t="s">
         <v>28</v>
       </c>
-      <c r="G479" s="1">
+      <c r="G479" s="3">
         <v>46148</v>
       </c>
-      <c r="H479" s="3">
+      <c r="H479" s="2">
         <v>6895.58</v>
       </c>
     </row>
@@ -14863,10 +14869,10 @@
       <c r="F480" t="s">
         <v>28</v>
       </c>
-      <c r="G480" s="1">
+      <c r="G480" s="3">
         <v>46148</v>
       </c>
-      <c r="H480" s="3">
+      <c r="H480" s="2">
         <v>1108.42</v>
       </c>
     </row>
@@ -14889,10 +14895,10 @@
       <c r="F481" t="s">
         <v>28</v>
       </c>
-      <c r="G481" s="1">
+      <c r="G481" s="3">
         <v>46148</v>
       </c>
-      <c r="H481" s="3">
+      <c r="H481" s="2">
         <v>3107.83</v>
       </c>
     </row>
@@ -14915,10 +14921,10 @@
       <c r="F482" t="s">
         <v>10</v>
       </c>
-      <c r="G482">
+      <c r="G482" s="3">
         <v>46149</v>
       </c>
-      <c r="H482" s="3">
+      <c r="H482" s="2">
         <v>10050.58</v>
       </c>
     </row>
@@ -14941,10 +14947,10 @@
       <c r="F483" t="s">
         <v>10</v>
       </c>
-      <c r="G483" s="1">
+      <c r="G483" s="3">
         <v>46149</v>
       </c>
-      <c r="H483" s="3">
+      <c r="H483" s="2">
         <v>8981.4</v>
       </c>
     </row>
@@ -14967,10 +14973,10 @@
       <c r="F484" t="s">
         <v>50</v>
       </c>
-      <c r="G484">
+      <c r="G484" s="3">
         <v>46156</v>
       </c>
-      <c r="H484" s="3">
+      <c r="H484" s="2">
         <v>103262.47</v>
       </c>
     </row>
@@ -14993,10 +14999,10 @@
       <c r="F485" t="s">
         <v>28</v>
       </c>
-      <c r="G485">
+      <c r="G485" s="3">
         <v>46148</v>
       </c>
-      <c r="H485" s="3">
+      <c r="H485" s="2">
         <v>4034.79</v>
       </c>
     </row>
@@ -15019,10 +15025,10 @@
       <c r="F486" t="s">
         <v>10</v>
       </c>
-      <c r="G486">
+      <c r="G486" s="3">
         <v>46149</v>
       </c>
-      <c r="H486" s="3">
+      <c r="H486" s="2">
         <v>3306.56</v>
       </c>
     </row>
@@ -15045,10 +15051,10 @@
       <c r="F487" t="s">
         <v>28</v>
       </c>
-      <c r="G487" s="1">
+      <c r="G487" s="3">
         <v>46148</v>
       </c>
-      <c r="H487" s="3">
+      <c r="H487" s="2">
         <v>17884.45</v>
       </c>
     </row>
@@ -15071,10 +15077,10 @@
       <c r="F488" t="s">
         <v>28</v>
       </c>
-      <c r="G488" s="1">
+      <c r="G488" s="3">
         <v>46148</v>
       </c>
-      <c r="H488" s="3">
+      <c r="H488" s="2">
         <v>3321.37</v>
       </c>
     </row>
@@ -15097,10 +15103,10 @@
       <c r="F489" t="s">
         <v>28</v>
       </c>
-      <c r="G489" s="1">
+      <c r="G489" s="3">
         <v>46148</v>
       </c>
-      <c r="H489" s="3">
+      <c r="H489" s="2">
         <v>2423.5100000000002</v>
       </c>
     </row>
@@ -15123,10 +15129,10 @@
       <c r="F490" t="s">
         <v>50</v>
       </c>
-      <c r="G490" s="1" t="s">
+      <c r="G490" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H490" s="3">
+      <c r="H490" s="2">
         <v>3688.21</v>
       </c>
     </row>
@@ -15149,10 +15155,10 @@
       <c r="F491" t="s">
         <v>28</v>
       </c>
-      <c r="G491">
+      <c r="G491" s="3">
         <v>46148</v>
       </c>
-      <c r="H491" s="3">
+      <c r="H491" s="2">
         <v>7261.84</v>
       </c>
     </row>
@@ -15175,10 +15181,10 @@
       <c r="F492" t="s">
         <v>10</v>
       </c>
-      <c r="G492" s="1">
+      <c r="G492" s="3">
         <v>46151</v>
       </c>
-      <c r="H492" s="3">
+      <c r="H492" s="2">
         <v>2366.69</v>
       </c>
     </row>
@@ -15201,10 +15207,10 @@
       <c r="F493" t="s">
         <v>50</v>
       </c>
-      <c r="G493" t="s">
+      <c r="G493" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H493" s="3">
+      <c r="H493" s="2">
         <v>9123.69</v>
       </c>
     </row>
@@ -15227,10 +15233,10 @@
       <c r="F494" t="s">
         <v>14</v>
       </c>
-      <c r="G494">
+      <c r="G494" s="3">
         <v>46149</v>
       </c>
-      <c r="H494" s="3">
+      <c r="H494" s="2">
         <v>6741.46</v>
       </c>
     </row>
@@ -15253,10 +15259,10 @@
       <c r="F495" t="s">
         <v>50</v>
       </c>
-      <c r="G495" s="1" t="s">
+      <c r="G495" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H495" s="3">
+      <c r="H495" s="2">
         <v>6741.46</v>
       </c>
     </row>
@@ -15279,10 +15285,10 @@
       <c r="F496" t="s">
         <v>10</v>
       </c>
-      <c r="G496">
+      <c r="G496" s="3">
         <v>46155</v>
       </c>
-      <c r="H496" s="3">
+      <c r="H496" s="2">
         <v>7875.45</v>
       </c>
     </row>
@@ -15305,10 +15311,10 @@
       <c r="F497" t="s">
         <v>50</v>
       </c>
-      <c r="G497" s="1">
+      <c r="G497" s="3">
         <v>46167</v>
       </c>
-      <c r="H497" s="3">
+      <c r="H497" s="2">
         <v>3210.51</v>
       </c>
     </row>
@@ -15331,10 +15337,10 @@
       <c r="F498" t="s">
         <v>10</v>
       </c>
-      <c r="G498">
+      <c r="G498" s="3">
         <v>46149</v>
       </c>
-      <c r="H498" s="3">
+      <c r="H498" s="2">
         <v>1265.23</v>
       </c>
     </row>
@@ -15357,10 +15363,10 @@
       <c r="F499" t="s">
         <v>28</v>
       </c>
-      <c r="G499">
+      <c r="G499" s="3">
         <v>46148</v>
       </c>
-      <c r="H499" s="3">
+      <c r="H499" s="2">
         <v>14412.83</v>
       </c>
     </row>
@@ -15383,10 +15389,10 @@
       <c r="F500" t="s">
         <v>28</v>
       </c>
-      <c r="G500" s="1">
+      <c r="G500" s="3">
         <v>46148</v>
       </c>
-      <c r="H500" s="3">
+      <c r="H500" s="2">
         <v>4453.71</v>
       </c>
     </row>
@@ -15409,10 +15415,10 @@
       <c r="F501" t="s">
         <v>10</v>
       </c>
-      <c r="G501">
+      <c r="G501" s="3">
         <v>46149</v>
       </c>
-      <c r="H501" s="3">
+      <c r="H501" s="2">
         <v>1696.03</v>
       </c>
     </row>
@@ -15435,10 +15441,10 @@
       <c r="F502" t="s">
         <v>31</v>
       </c>
-      <c r="G502" s="1" t="s">
+      <c r="G502" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H502" s="3">
+      <c r="H502" s="2">
         <v>5974.97</v>
       </c>
     </row>
@@ -15461,10 +15467,10 @@
       <c r="F503" t="s">
         <v>20</v>
       </c>
-      <c r="G503" s="1">
+      <c r="G503" s="3">
         <v>46149</v>
       </c>
-      <c r="H503" s="3">
+      <c r="H503" s="2">
         <v>6577.26</v>
       </c>
     </row>
@@ -15487,10 +15493,10 @@
       <c r="F504" t="s">
         <v>28</v>
       </c>
-      <c r="G504">
+      <c r="G504" s="3">
         <v>46148</v>
       </c>
-      <c r="H504" s="3">
+      <c r="H504" s="2">
         <v>2576.35</v>
       </c>
     </row>
@@ -15513,10 +15519,10 @@
       <c r="F505" t="s">
         <v>28</v>
       </c>
-      <c r="G505" s="1">
+      <c r="G505" s="3">
         <v>46148</v>
       </c>
-      <c r="H505" s="3">
+      <c r="H505" s="2">
         <v>1182.6400000000001</v>
       </c>
     </row>
@@ -15539,10 +15545,10 @@
       <c r="F506" t="s">
         <v>50</v>
       </c>
-      <c r="G506" s="1" t="s">
+      <c r="G506" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H506" s="3">
+      <c r="H506" s="2">
         <v>19255.88</v>
       </c>
     </row>
@@ -15565,10 +15571,10 @@
       <c r="F507" t="s">
         <v>10</v>
       </c>
-      <c r="G507">
+      <c r="G507" s="3">
         <v>46149</v>
       </c>
-      <c r="H507" s="3">
+      <c r="H507" s="2">
         <v>2404.65</v>
       </c>
     </row>
@@ -15591,10 +15597,10 @@
       <c r="F508" t="s">
         <v>10</v>
       </c>
-      <c r="G508">
+      <c r="G508" s="3">
         <v>46149</v>
       </c>
-      <c r="H508" s="3">
+      <c r="H508" s="2">
         <v>2594.71</v>
       </c>
     </row>
@@ -15617,10 +15623,10 @@
       <c r="F509" t="s">
         <v>10</v>
       </c>
-      <c r="G509">
+      <c r="G509" s="3">
         <v>46149</v>
       </c>
-      <c r="H509" s="3">
+      <c r="H509" s="2">
         <v>2763.56</v>
       </c>
     </row>
@@ -15643,10 +15649,10 @@
       <c r="F510" t="s">
         <v>10</v>
       </c>
-      <c r="G510">
+      <c r="G510" s="3">
         <v>46149</v>
       </c>
-      <c r="H510" s="3">
+      <c r="H510" s="2">
         <v>2570</v>
       </c>
     </row>
@@ -15669,10 +15675,10 @@
       <c r="F511" t="s">
         <v>10</v>
       </c>
-      <c r="G511">
+      <c r="G511" s="3">
         <v>46155</v>
       </c>
-      <c r="H511" s="3">
+      <c r="H511" s="2">
         <v>23667.82</v>
       </c>
     </row>
@@ -15695,10 +15701,10 @@
       <c r="F512" t="s">
         <v>10</v>
       </c>
-      <c r="G512">
+      <c r="G512" s="3">
         <v>46149</v>
       </c>
-      <c r="H512" s="3">
+      <c r="H512" s="2">
         <v>2034.57</v>
       </c>
     </row>
@@ -15721,10 +15727,10 @@
       <c r="F513" t="s">
         <v>50</v>
       </c>
-      <c r="G513">
+      <c r="G513" s="3">
         <v>46163</v>
       </c>
-      <c r="H513" s="3">
+      <c r="H513" s="2">
         <v>5337.81</v>
       </c>
     </row>
@@ -15747,10 +15753,10 @@
       <c r="F514" t="s">
         <v>28</v>
       </c>
-      <c r="G514" s="1">
+      <c r="G514" s="3">
         <v>46148</v>
       </c>
-      <c r="H514" s="3">
+      <c r="H514" s="2">
         <v>4574.32</v>
       </c>
     </row>
@@ -15773,10 +15779,10 @@
       <c r="F515" t="s">
         <v>10</v>
       </c>
-      <c r="G515">
+      <c r="G515" s="3">
         <v>46149</v>
       </c>
-      <c r="H515" s="3">
+      <c r="H515" s="2">
         <v>2180.16</v>
       </c>
     </row>
@@ -15799,10 +15805,10 @@
       <c r="F516" t="s">
         <v>28</v>
       </c>
-      <c r="G516">
+      <c r="G516" s="3">
         <v>46148</v>
       </c>
-      <c r="H516" s="3">
+      <c r="H516" s="2">
         <v>1306.95</v>
       </c>
     </row>
@@ -15825,10 +15831,10 @@
       <c r="F517" t="s">
         <v>10</v>
       </c>
-      <c r="G517" s="1">
+      <c r="G517" s="3">
         <v>46148</v>
       </c>
-      <c r="H517" s="3">
+      <c r="H517" s="2">
         <v>6517.72</v>
       </c>
     </row>
@@ -15851,10 +15857,10 @@
       <c r="F518" t="s">
         <v>10</v>
       </c>
-      <c r="G518" s="1">
+      <c r="G518" s="3">
         <v>46149</v>
       </c>
-      <c r="H518" s="3">
+      <c r="H518" s="2">
         <v>1319.72</v>
       </c>
     </row>
@@ -15877,10 +15883,10 @@
       <c r="F519" t="s">
         <v>28</v>
       </c>
-      <c r="G519">
+      <c r="G519" s="3">
         <v>46148</v>
       </c>
-      <c r="H519" s="3">
+      <c r="H519" s="2">
         <v>3374.13</v>
       </c>
     </row>
@@ -15903,10 +15909,10 @@
       <c r="F520" t="s">
         <v>115</v>
       </c>
-      <c r="G520">
+      <c r="G520" s="3">
         <v>46163</v>
       </c>
-      <c r="H520" s="3">
+      <c r="H520" s="2">
         <v>44044.57</v>
       </c>
     </row>
@@ -15929,10 +15935,10 @@
       <c r="F521" t="s">
         <v>28</v>
       </c>
-      <c r="G521" s="1">
+      <c r="G521" s="3">
         <v>46148</v>
       </c>
-      <c r="H521" s="3">
+      <c r="H521" s="2">
         <v>10363.09</v>
       </c>
     </row>
@@ -15955,10 +15961,10 @@
       <c r="F522" t="s">
         <v>10</v>
       </c>
-      <c r="G522">
+      <c r="G522" s="3">
         <v>46149</v>
       </c>
-      <c r="H522" s="3">
+      <c r="H522" s="2">
         <v>4489.66</v>
       </c>
     </row>
@@ -15981,10 +15987,10 @@
       <c r="F523" t="s">
         <v>31</v>
       </c>
-      <c r="G523" t="s">
+      <c r="G523" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H523" s="3">
+      <c r="H523" s="2">
         <v>5952.14</v>
       </c>
     </row>
@@ -16007,10 +16013,10 @@
       <c r="F524" t="s">
         <v>28</v>
       </c>
-      <c r="G524">
+      <c r="G524" s="3">
         <v>46148</v>
       </c>
-      <c r="H524" s="3">
+      <c r="H524" s="2">
         <v>3868.03</v>
       </c>
     </row>
@@ -16033,10 +16039,10 @@
       <c r="F525" t="s">
         <v>10</v>
       </c>
-      <c r="G525">
+      <c r="G525" s="3">
         <v>46149</v>
       </c>
-      <c r="H525" s="3">
+      <c r="H525" s="2">
         <v>2073.39</v>
       </c>
     </row>
@@ -16059,10 +16065,10 @@
       <c r="F526" t="s">
         <v>10</v>
       </c>
-      <c r="G526" s="1">
+      <c r="G526" s="3">
         <v>46163</v>
       </c>
-      <c r="H526" s="3">
+      <c r="H526" s="2">
         <v>12315.3</v>
       </c>
     </row>
@@ -16085,10 +16091,10 @@
       <c r="F527" t="s">
         <v>10</v>
       </c>
-      <c r="G527" s="1">
+      <c r="G527" s="3">
         <v>46163</v>
       </c>
-      <c r="H527" s="3">
+      <c r="H527" s="2">
         <v>11170.17</v>
       </c>
     </row>
@@ -16111,10 +16117,10 @@
       <c r="F528" t="s">
         <v>28</v>
       </c>
-      <c r="G528">
+      <c r="G528" s="3">
         <v>46148</v>
       </c>
-      <c r="H528" s="3">
+      <c r="H528" s="2">
         <v>5027.91</v>
       </c>
     </row>
@@ -16137,10 +16143,10 @@
       <c r="F529" t="s">
         <v>31</v>
       </c>
-      <c r="G529" s="1" t="s">
+      <c r="G529" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H529" s="3">
+      <c r="H529" s="2">
         <v>2106.66</v>
       </c>
     </row>
@@ -16163,10 +16169,10 @@
       <c r="F530" t="s">
         <v>10</v>
       </c>
-      <c r="G530" s="1">
+      <c r="G530" s="3">
         <v>46151</v>
       </c>
-      <c r="H530" s="3">
+      <c r="H530" s="2">
         <v>2668.86</v>
       </c>
     </row>
@@ -16189,10 +16195,10 @@
       <c r="F531" t="s">
         <v>10</v>
       </c>
-      <c r="G531" s="1">
+      <c r="G531" s="3">
         <v>46149</v>
       </c>
-      <c r="H531" s="3">
+      <c r="H531" s="2">
         <v>8327.2099999999991</v>
       </c>
     </row>
@@ -16215,10 +16221,10 @@
       <c r="F532" t="s">
         <v>28</v>
       </c>
-      <c r="G532">
+      <c r="G532" s="3">
         <v>46148</v>
       </c>
-      <c r="H532" s="3">
+      <c r="H532" s="2">
         <v>2583.0300000000002</v>
       </c>
     </row>
@@ -16241,10 +16247,10 @@
       <c r="F533" t="s">
         <v>28</v>
       </c>
-      <c r="G533">
+      <c r="G533" s="3">
         <v>46148</v>
       </c>
-      <c r="H533" s="3">
+      <c r="H533" s="2">
         <v>4082.15</v>
       </c>
     </row>
@@ -16267,10 +16273,10 @@
       <c r="F534" t="s">
         <v>31</v>
       </c>
-      <c r="G534" t="s">
+      <c r="G534" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H534" s="3">
+      <c r="H534" s="2">
         <v>9337.44</v>
       </c>
     </row>
@@ -16293,10 +16299,10 @@
       <c r="F535" t="s">
         <v>28</v>
       </c>
-      <c r="G535">
+      <c r="G535" s="3">
         <v>46148</v>
       </c>
-      <c r="H535" s="3">
+      <c r="H535" s="2">
         <v>5489.04</v>
       </c>
     </row>
@@ -16319,10 +16325,10 @@
       <c r="F536" t="s">
         <v>50</v>
       </c>
-      <c r="G536">
+      <c r="G536" s="3">
         <v>46167</v>
       </c>
-      <c r="H536" s="3">
+      <c r="H536" s="2">
         <v>7733.8</v>
       </c>
     </row>
@@ -16345,10 +16351,10 @@
       <c r="F537" t="s">
         <v>28</v>
       </c>
-      <c r="G537">
+      <c r="G537" s="3">
         <v>46148</v>
       </c>
-      <c r="H537" s="3">
+      <c r="H537" s="2">
         <v>3108.92</v>
       </c>
     </row>
@@ -16371,10 +16377,10 @@
       <c r="F538" t="s">
         <v>10</v>
       </c>
-      <c r="G538">
+      <c r="G538" s="3">
         <v>46151</v>
       </c>
-      <c r="H538" s="3">
+      <c r="H538" s="2">
         <v>8917.4599999999991</v>
       </c>
     </row>
@@ -16397,10 +16403,10 @@
       <c r="F539" t="s">
         <v>28</v>
       </c>
-      <c r="G539">
+      <c r="G539" s="3">
         <v>46148</v>
       </c>
-      <c r="H539" s="3">
+      <c r="H539" s="2">
         <v>4255.07</v>
       </c>
     </row>
@@ -16423,10 +16429,10 @@
       <c r="F540" t="s">
         <v>31</v>
       </c>
-      <c r="G540" s="1" t="s">
+      <c r="G540" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H540" s="3">
+      <c r="H540" s="2">
         <v>5718.55</v>
       </c>
     </row>
@@ -16449,10 +16455,10 @@
       <c r="F541" t="s">
         <v>26</v>
       </c>
-      <c r="G541" t="s">
+      <c r="G541" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H541" s="3">
+      <c r="H541" s="2">
         <v>11231</v>
       </c>
     </row>
@@ -16475,10 +16481,10 @@
       <c r="F542" t="s">
         <v>10</v>
       </c>
-      <c r="G542" s="1">
+      <c r="G542" s="3">
         <v>46149</v>
       </c>
-      <c r="H542" s="3">
+      <c r="H542" s="2">
         <v>3319.3</v>
       </c>
     </row>
@@ -16501,10 +16507,10 @@
       <c r="F543" t="s">
         <v>28</v>
       </c>
-      <c r="G543">
+      <c r="G543" s="3">
         <v>46148</v>
       </c>
-      <c r="H543" s="3">
+      <c r="H543" s="2">
         <v>4013.86</v>
       </c>
     </row>
@@ -16527,10 +16533,10 @@
       <c r="F544" t="s">
         <v>10</v>
       </c>
-      <c r="G544">
+      <c r="G544" s="3">
         <v>46151</v>
       </c>
-      <c r="H544" s="3">
+      <c r="H544" s="2">
         <v>3790.28</v>
       </c>
     </row>
@@ -16553,10 +16559,10 @@
       <c r="F545" t="s">
         <v>10</v>
       </c>
-      <c r="G545" s="1">
+      <c r="G545" s="3">
         <v>46151</v>
       </c>
-      <c r="H545" s="3">
+      <c r="H545" s="2">
         <v>3190.31</v>
       </c>
     </row>
@@ -16579,10 +16585,10 @@
       <c r="F546" t="s">
         <v>28</v>
       </c>
-      <c r="G546">
+      <c r="G546" s="3">
         <v>46148</v>
       </c>
-      <c r="H546" s="3">
+      <c r="H546" s="2">
         <v>2584.35</v>
       </c>
     </row>
@@ -16605,10 +16611,10 @@
       <c r="F547" t="s">
         <v>28</v>
       </c>
-      <c r="G547">
+      <c r="G547" s="3">
         <v>46148</v>
       </c>
-      <c r="H547" s="3">
+      <c r="H547" s="2">
         <v>7472.36</v>
       </c>
     </row>
@@ -16631,10 +16637,10 @@
       <c r="F548" t="s">
         <v>10</v>
       </c>
-      <c r="G548">
+      <c r="G548" s="3">
         <v>46151</v>
       </c>
-      <c r="H548" s="3">
+      <c r="H548" s="2">
         <v>3852.11</v>
       </c>
     </row>
@@ -16657,10 +16663,10 @@
       <c r="F549" t="s">
         <v>10</v>
       </c>
-      <c r="G549" s="1">
+      <c r="G549" s="3">
         <v>46151</v>
       </c>
-      <c r="H549" s="3">
+      <c r="H549" s="2">
         <v>5264.69</v>
       </c>
     </row>
@@ -16683,10 +16689,10 @@
       <c r="F550" t="s">
         <v>10</v>
       </c>
-      <c r="G550">
+      <c r="G550" s="3">
         <v>46151</v>
       </c>
-      <c r="H550" s="3">
+      <c r="H550" s="2">
         <v>1925.41</v>
       </c>
     </row>
@@ -16709,10 +16715,10 @@
       <c r="F551" t="s">
         <v>28</v>
       </c>
-      <c r="G551">
+      <c r="G551" s="3">
         <v>46148</v>
       </c>
-      <c r="H551" s="3">
+      <c r="H551" s="2">
         <v>2485.7399999999998</v>
       </c>
     </row>
@@ -16735,10 +16741,10 @@
       <c r="F552" t="s">
         <v>10</v>
       </c>
-      <c r="G552">
+      <c r="G552" s="3">
         <v>46149</v>
       </c>
-      <c r="H552" s="3">
+      <c r="H552" s="2">
         <v>9419.51</v>
       </c>
     </row>
@@ -16761,10 +16767,10 @@
       <c r="F553" t="s">
         <v>10</v>
       </c>
-      <c r="G553">
+      <c r="G553" s="3">
         <v>46149</v>
       </c>
-      <c r="H553" s="3">
+      <c r="H553" s="2">
         <v>5501.23</v>
       </c>
     </row>
@@ -16787,10 +16793,10 @@
       <c r="F554" t="s">
         <v>10</v>
       </c>
-      <c r="G554" t="s">
+      <c r="G554" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H554" s="3">
+      <c r="H554" s="2">
         <v>10763.2</v>
       </c>
     </row>
@@ -16813,10 +16819,10 @@
       <c r="F555" t="s">
         <v>28</v>
       </c>
-      <c r="G555">
+      <c r="G555" s="3">
         <v>46148</v>
       </c>
-      <c r="H555" s="3">
+      <c r="H555" s="2">
         <v>2334.9899999999998</v>
       </c>
     </row>
@@ -16839,10 +16845,10 @@
       <c r="F556" t="s">
         <v>28</v>
       </c>
-      <c r="G556" s="1">
+      <c r="G556" s="3">
         <v>46148</v>
       </c>
-      <c r="H556" s="3">
+      <c r="H556" s="2">
         <v>4804.8900000000003</v>
       </c>
     </row>
@@ -16865,10 +16871,10 @@
       <c r="F557" t="s">
         <v>10</v>
       </c>
-      <c r="G557">
+      <c r="G557" s="3">
         <v>46149</v>
       </c>
-      <c r="H557" s="3">
+      <c r="H557" s="2">
         <v>2713.26</v>
       </c>
     </row>
@@ -16891,10 +16897,10 @@
       <c r="F558" t="s">
         <v>28</v>
       </c>
-      <c r="G558">
+      <c r="G558" s="3">
         <v>46148</v>
       </c>
-      <c r="H558" s="3">
+      <c r="H558" s="2">
         <v>2919.33</v>
       </c>
     </row>
@@ -16917,10 +16923,10 @@
       <c r="F559" t="s">
         <v>28</v>
       </c>
-      <c r="G559">
+      <c r="G559" s="3">
         <v>46148</v>
       </c>
-      <c r="H559" s="3">
+      <c r="H559" s="2">
         <v>3585.54</v>
       </c>
     </row>
@@ -16943,10 +16949,10 @@
       <c r="F560" t="s">
         <v>28</v>
       </c>
-      <c r="G560">
+      <c r="G560" s="3">
         <v>46148</v>
       </c>
-      <c r="H560" s="3">
+      <c r="H560" s="2">
         <v>2586.54</v>
       </c>
     </row>
@@ -16969,10 +16975,10 @@
       <c r="F561" t="s">
         <v>10</v>
       </c>
-      <c r="G561">
+      <c r="G561" s="3">
         <v>46163</v>
       </c>
-      <c r="H561" s="3">
+      <c r="H561" s="2">
         <v>7519.63</v>
       </c>
     </row>
@@ -16995,10 +17001,10 @@
       <c r="F562" t="s">
         <v>50</v>
       </c>
-      <c r="G562" s="1" t="s">
+      <c r="G562" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H562" s="3">
+      <c r="H562" s="2">
         <v>57852.9</v>
       </c>
     </row>
@@ -17021,10 +17027,10 @@
       <c r="F563" t="s">
         <v>10</v>
       </c>
-      <c r="G563">
+      <c r="G563" s="3">
         <v>46149</v>
       </c>
-      <c r="H563" s="3">
+      <c r="H563" s="2">
         <v>1851.04</v>
       </c>
     </row>
@@ -17047,10 +17053,10 @@
       <c r="F564" t="s">
         <v>26</v>
       </c>
-      <c r="G564" s="1" t="s">
+      <c r="G564" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H564" s="3">
+      <c r="H564" s="2">
         <v>10202.07</v>
       </c>
     </row>
@@ -17073,10 +17079,10 @@
       <c r="F565" t="s">
         <v>28</v>
       </c>
-      <c r="G565">
+      <c r="G565" s="3">
         <v>46148</v>
       </c>
-      <c r="H565" s="3">
+      <c r="H565" s="2">
         <v>3713.28</v>
       </c>
     </row>
@@ -17099,10 +17105,10 @@
       <c r="F566" t="s">
         <v>28</v>
       </c>
-      <c r="G566" s="1">
+      <c r="G566" s="3">
         <v>46148</v>
       </c>
-      <c r="H566" s="3">
+      <c r="H566" s="2">
         <v>12784.03</v>
       </c>
     </row>
@@ -17125,10 +17131,10 @@
       <c r="F567" t="s">
         <v>20</v>
       </c>
-      <c r="G567">
+      <c r="G567" s="3">
         <v>46149</v>
       </c>
-      <c r="H567" s="3">
+      <c r="H567" s="2">
         <v>746.69</v>
       </c>
     </row>
@@ -17151,10 +17157,10 @@
       <c r="F568" t="s">
         <v>10</v>
       </c>
-      <c r="G568">
+      <c r="G568" s="3">
         <v>46149</v>
       </c>
-      <c r="H568" s="3">
+      <c r="H568" s="2">
         <v>7841.25</v>
       </c>
     </row>
@@ -17177,10 +17183,10 @@
       <c r="F569" t="s">
         <v>10</v>
       </c>
-      <c r="G569" s="1">
+      <c r="G569" s="3">
         <v>46151</v>
       </c>
-      <c r="H569" s="3">
+      <c r="H569" s="2">
         <v>3233.91</v>
       </c>
     </row>
@@ -17203,10 +17209,10 @@
       <c r="F570" t="s">
         <v>10</v>
       </c>
-      <c r="G570" s="1" t="s">
+      <c r="G570" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H570" s="3">
+      <c r="H570" s="2">
         <v>3846.63</v>
       </c>
     </row>
@@ -17229,10 +17235,10 @@
       <c r="F571" t="s">
         <v>10</v>
       </c>
-      <c r="G571">
+      <c r="G571" s="3">
         <v>46148</v>
       </c>
-      <c r="H571" s="3">
+      <c r="H571" s="2">
         <v>3907.48</v>
       </c>
     </row>
@@ -17255,10 +17261,10 @@
       <c r="F572" t="s">
         <v>10</v>
       </c>
-      <c r="G572" s="1">
+      <c r="G572" s="3">
         <v>46160</v>
       </c>
-      <c r="H572" s="3">
+      <c r="H572" s="2">
         <v>43109.54</v>
       </c>
     </row>
@@ -17281,10 +17287,10 @@
       <c r="F573" t="s">
         <v>10</v>
       </c>
-      <c r="G573">
+      <c r="G573" s="3">
         <v>46149</v>
       </c>
-      <c r="H573" s="3">
+      <c r="H573" s="2">
         <v>1392.9</v>
       </c>
     </row>
@@ -17307,10 +17313,10 @@
       <c r="F574" t="s">
         <v>10</v>
       </c>
-      <c r="G574" s="1">
+      <c r="G574" s="3">
         <v>46151</v>
       </c>
-      <c r="H574" s="3">
+      <c r="H574" s="2">
         <v>2568.4299999999998</v>
       </c>
     </row>
@@ -17333,10 +17339,10 @@
       <c r="F575" t="s">
         <v>31</v>
       </c>
-      <c r="G575" t="s">
+      <c r="G575" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H575" s="3">
+      <c r="H575" s="2">
         <v>6527.83</v>
       </c>
     </row>
@@ -17359,10 +17365,10 @@
       <c r="F576" t="s">
         <v>31</v>
       </c>
-      <c r="G576" t="s">
+      <c r="G576" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H576" s="3">
+      <c r="H576" s="2">
         <v>6518.61</v>
       </c>
     </row>
@@ -17385,10 +17391,10 @@
       <c r="F577" t="s">
         <v>31</v>
       </c>
-      <c r="G577" t="s">
+      <c r="G577" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H577" s="3">
+      <c r="H577" s="2">
         <v>3390.68</v>
       </c>
     </row>
@@ -17411,10 +17417,10 @@
       <c r="F578" t="s">
         <v>10</v>
       </c>
-      <c r="G578" s="1">
+      <c r="G578" s="3">
         <v>46149</v>
       </c>
-      <c r="H578" s="3">
+      <c r="H578" s="2">
         <v>18639.78</v>
       </c>
     </row>
@@ -17437,10 +17443,10 @@
       <c r="F579" t="s">
         <v>28</v>
       </c>
-      <c r="G579" s="1">
+      <c r="G579" s="3">
         <v>46148</v>
       </c>
-      <c r="H579" s="3">
+      <c r="H579" s="2">
         <v>3598.27</v>
       </c>
     </row>
@@ -17463,10 +17469,10 @@
       <c r="F580" t="s">
         <v>28</v>
       </c>
-      <c r="G580" s="1">
+      <c r="G580" s="3">
         <v>46148</v>
       </c>
-      <c r="H580" s="3">
+      <c r="H580" s="2">
         <v>4378.71</v>
       </c>
     </row>
@@ -17489,10 +17495,10 @@
       <c r="F581" t="s">
         <v>31</v>
       </c>
-      <c r="G581" t="s">
+      <c r="G581" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H581" s="3">
+      <c r="H581" s="2">
         <v>2517.0700000000002</v>
       </c>
     </row>
@@ -17515,10 +17521,10 @@
       <c r="F582" t="s">
         <v>10</v>
       </c>
-      <c r="G582" s="1">
+      <c r="G582" s="3">
         <v>46149</v>
       </c>
-      <c r="H582" s="3">
+      <c r="H582" s="2">
         <v>4497.63</v>
       </c>
     </row>
@@ -17541,10 +17547,10 @@
       <c r="F583" t="s">
         <v>10</v>
       </c>
-      <c r="G583">
+      <c r="G583" s="3">
         <v>46149</v>
       </c>
-      <c r="H583" s="3">
+      <c r="H583" s="2">
         <v>4497.63</v>
       </c>
     </row>
@@ -17567,10 +17573,10 @@
       <c r="F584" t="s">
         <v>10</v>
       </c>
-      <c r="G584">
+      <c r="G584" s="3">
         <v>46155</v>
       </c>
-      <c r="H584" s="3">
+      <c r="H584" s="2">
         <v>6505.55</v>
       </c>
     </row>
@@ -17593,10 +17599,10 @@
       <c r="F585" t="s">
         <v>10</v>
       </c>
-      <c r="G585">
+      <c r="G585" s="3">
         <v>46151</v>
       </c>
-      <c r="H585" s="3">
+      <c r="H585" s="2">
         <v>6571.44</v>
       </c>
     </row>
@@ -17619,10 +17625,10 @@
       <c r="F586" t="s">
         <v>10</v>
       </c>
-      <c r="G586" s="1">
+      <c r="G586" s="3">
         <v>46149</v>
       </c>
-      <c r="H586" s="3">
+      <c r="H586" s="2">
         <v>4657.3500000000004</v>
       </c>
     </row>
@@ -17645,10 +17651,10 @@
       <c r="F587" t="s">
         <v>50</v>
       </c>
-      <c r="G587" t="s">
+      <c r="G587" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H587" s="3">
+      <c r="H587" s="2">
         <v>56229.27</v>
       </c>
     </row>
@@ -17671,10 +17677,10 @@
       <c r="F588" t="s">
         <v>85</v>
       </c>
-      <c r="G588" s="1">
+      <c r="G588" s="3">
         <v>46149</v>
       </c>
-      <c r="H588" s="3">
+      <c r="H588" s="2">
         <v>3008.55</v>
       </c>
     </row>
@@ -17697,10 +17703,10 @@
       <c r="F589" t="s">
         <v>10</v>
       </c>
-      <c r="G589" s="1">
+      <c r="G589" s="3">
         <v>46148</v>
       </c>
-      <c r="H589" s="3">
+      <c r="H589" s="2">
         <v>18559.419999999998</v>
       </c>
     </row>
@@ -17723,10 +17729,10 @@
       <c r="F590" t="s">
         <v>20</v>
       </c>
-      <c r="G590" s="1">
+      <c r="G590" s="3">
         <v>46149</v>
       </c>
-      <c r="H590" s="3">
+      <c r="H590" s="2">
         <v>750.85</v>
       </c>
     </row>
@@ -17749,10 +17755,10 @@
       <c r="F591" t="s">
         <v>31</v>
       </c>
-      <c r="G591" s="1" t="s">
+      <c r="G591" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H591" s="3">
+      <c r="H591" s="2">
         <v>9932.15</v>
       </c>
     </row>
@@ -17775,10 +17781,10 @@
       <c r="F592" t="s">
         <v>117</v>
       </c>
-      <c r="G592" s="1">
+      <c r="G592" s="3">
         <v>46149</v>
       </c>
-      <c r="H592" s="3">
+      <c r="H592" s="2">
         <v>2677.04</v>
       </c>
     </row>
@@ -17801,10 +17807,10 @@
       <c r="F593" t="s">
         <v>31</v>
       </c>
-      <c r="G593" t="s">
+      <c r="G593" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H593" s="3">
+      <c r="H593" s="2">
         <v>3118.36</v>
       </c>
     </row>
@@ -17827,10 +17833,10 @@
       <c r="F594" t="s">
         <v>28</v>
       </c>
-      <c r="G594">
+      <c r="G594" s="3">
         <v>46148</v>
       </c>
-      <c r="H594" s="3">
+      <c r="H594" s="2">
         <v>2921.23</v>
       </c>
     </row>
@@ -17853,10 +17859,10 @@
       <c r="F595" t="s">
         <v>28</v>
       </c>
-      <c r="G595">
+      <c r="G595" s="3">
         <v>46148</v>
       </c>
-      <c r="H595" s="3">
+      <c r="H595" s="2">
         <v>3355.66</v>
       </c>
     </row>
@@ -17879,10 +17885,10 @@
       <c r="F596" t="s">
         <v>28</v>
       </c>
-      <c r="G596">
+      <c r="G596" s="3">
         <v>46148</v>
       </c>
-      <c r="H596" s="3">
+      <c r="H596" s="2">
         <v>3544.85</v>
       </c>
     </row>
@@ -17905,10 +17911,10 @@
       <c r="F597" t="s">
         <v>28</v>
       </c>
-      <c r="G597">
+      <c r="G597" s="3">
         <v>46148</v>
       </c>
-      <c r="H597" s="3">
+      <c r="H597" s="2">
         <v>15.43</v>
       </c>
     </row>
@@ -17931,10 +17937,10 @@
       <c r="F598" t="s">
         <v>10</v>
       </c>
-      <c r="G598">
+      <c r="G598" s="3">
         <v>46149</v>
       </c>
-      <c r="H598" s="3">
+      <c r="H598" s="2">
         <v>4095.12</v>
       </c>
     </row>
@@ -17957,10 +17963,10 @@
       <c r="F599" t="s">
         <v>28</v>
       </c>
-      <c r="G599" s="1">
+      <c r="G599" s="3">
         <v>46148</v>
       </c>
-      <c r="H599" s="3">
+      <c r="H599" s="2">
         <v>22226.14</v>
       </c>
     </row>
@@ -17983,10 +17989,10 @@
       <c r="F600" t="s">
         <v>31</v>
       </c>
-      <c r="G600" t="s">
+      <c r="G600" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H600" s="3">
+      <c r="H600" s="2">
         <v>2682.01</v>
       </c>
     </row>
@@ -18009,10 +18015,10 @@
       <c r="F601" t="s">
         <v>28</v>
       </c>
-      <c r="G601">
+      <c r="G601" s="3">
         <v>46148</v>
       </c>
-      <c r="H601" s="3">
+      <c r="H601" s="2">
         <v>4877.88</v>
       </c>
     </row>
@@ -18035,10 +18041,10 @@
       <c r="F602" t="s">
         <v>31</v>
       </c>
-      <c r="G602" t="s">
+      <c r="G602" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H602" s="3">
+      <c r="H602" s="2">
         <v>17831.36</v>
       </c>
     </row>
@@ -18061,10 +18067,10 @@
       <c r="F603" t="s">
         <v>28</v>
       </c>
-      <c r="G603">
+      <c r="G603" s="3">
         <v>46148</v>
       </c>
-      <c r="H603" s="3">
+      <c r="H603" s="2">
         <v>34503.29</v>
       </c>
     </row>
@@ -18087,10 +18093,10 @@
       <c r="F604" t="s">
         <v>31</v>
       </c>
-      <c r="G604" s="1" t="s">
+      <c r="G604" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H604" s="3">
+      <c r="H604" s="2">
         <v>7834.14</v>
       </c>
     </row>
@@ -18113,10 +18119,10 @@
       <c r="F605" t="s">
         <v>31</v>
       </c>
-      <c r="G605" t="s">
+      <c r="G605" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H605" s="3">
+      <c r="H605" s="2">
         <v>6043.53</v>
       </c>
     </row>
@@ -18139,10 +18145,10 @@
       <c r="F606" t="s">
         <v>28</v>
       </c>
-      <c r="G606" s="1">
+      <c r="G606" s="3">
         <v>46148</v>
       </c>
-      <c r="H606" s="3">
+      <c r="H606" s="2">
         <v>12585.52</v>
       </c>
     </row>
@@ -18165,10 +18171,10 @@
       <c r="F607" t="s">
         <v>31</v>
       </c>
-      <c r="G607" t="s">
+      <c r="G607" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H607" s="3">
+      <c r="H607" s="2">
         <v>8320.16</v>
       </c>
     </row>
@@ -18191,10 +18197,10 @@
       <c r="F608" t="s">
         <v>28</v>
       </c>
-      <c r="G608" s="1">
+      <c r="G608" s="3">
         <v>46148</v>
       </c>
-      <c r="H608" s="3">
+      <c r="H608" s="2">
         <v>4918.78</v>
       </c>
     </row>
@@ -18217,10 +18223,10 @@
       <c r="F609" t="s">
         <v>31</v>
       </c>
-      <c r="G609" s="1" t="s">
+      <c r="G609" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H609" s="3">
+      <c r="H609" s="2">
         <v>2472.69</v>
       </c>
     </row>
@@ -18243,10 +18249,10 @@
       <c r="F610" t="s">
         <v>28</v>
       </c>
-      <c r="G610">
+      <c r="G610" s="3">
         <v>46148</v>
       </c>
-      <c r="H610" s="3">
+      <c r="H610" s="2">
         <v>4739.45</v>
       </c>
     </row>
@@ -18269,10 +18275,10 @@
       <c r="F611" t="s">
         <v>31</v>
       </c>
-      <c r="G611" t="s">
+      <c r="G611" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H611" s="3">
+      <c r="H611" s="2">
         <v>14300.88</v>
       </c>
     </row>
@@ -18295,10 +18301,10 @@
       <c r="F612" t="s">
         <v>28</v>
       </c>
-      <c r="G612">
+      <c r="G612" s="3">
         <v>46148</v>
       </c>
-      <c r="H612" s="3">
+      <c r="H612" s="2">
         <v>6377.63</v>
       </c>
     </row>
@@ -18321,10 +18327,10 @@
       <c r="F613" t="s">
         <v>10</v>
       </c>
-      <c r="G613" s="1">
+      <c r="G613" s="3">
         <v>46151</v>
       </c>
-      <c r="H613" s="3">
+      <c r="H613" s="2">
         <v>4380.1499999999996</v>
       </c>
     </row>
@@ -18347,10 +18353,10 @@
       <c r="F614" t="s">
         <v>31</v>
       </c>
-      <c r="G614" s="1" t="s">
+      <c r="G614" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H614" s="3">
+      <c r="H614" s="2">
         <v>11220.12</v>
       </c>
     </row>
@@ -18373,10 +18379,10 @@
       <c r="F615" t="s">
         <v>28</v>
       </c>
-      <c r="G615" s="1">
+      <c r="G615" s="3">
         <v>46148</v>
       </c>
-      <c r="H615" s="3">
+      <c r="H615" s="2">
         <v>4377.32</v>
       </c>
     </row>
@@ -18399,10 +18405,10 @@
       <c r="F616" t="s">
         <v>28</v>
       </c>
-      <c r="G616" s="1">
+      <c r="G616" s="3">
         <v>46148</v>
       </c>
-      <c r="H616" s="3">
+      <c r="H616" s="2">
         <v>9678.4599999999991</v>
       </c>
     </row>
@@ -18425,10 +18431,10 @@
       <c r="F617" t="s">
         <v>28</v>
       </c>
-      <c r="G617" s="1">
+      <c r="G617" s="3">
         <v>46148</v>
       </c>
-      <c r="H617" s="3">
+      <c r="H617" s="2">
         <v>7844.69</v>
       </c>
     </row>
@@ -18451,10 +18457,10 @@
       <c r="F618" t="s">
         <v>31</v>
       </c>
-      <c r="G618" t="s">
+      <c r="G618" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H618" s="3">
+      <c r="H618" s="2">
         <v>585.95000000000005</v>
       </c>
     </row>
@@ -18477,10 +18483,10 @@
       <c r="F619" t="s">
         <v>31</v>
       </c>
-      <c r="G619" t="s">
+      <c r="G619" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H619" s="3">
+      <c r="H619" s="2">
         <v>164205.09</v>
       </c>
     </row>
@@ -18503,10 +18509,10 @@
       <c r="F620" t="s">
         <v>10</v>
       </c>
-      <c r="G620">
+      <c r="G620" s="3">
         <v>46151</v>
       </c>
-      <c r="H620" s="3">
+      <c r="H620" s="2">
         <v>2645.5</v>
       </c>
     </row>
@@ -18529,10 +18535,10 @@
       <c r="F621" t="s">
         <v>31</v>
       </c>
-      <c r="G621" t="s">
+      <c r="G621" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H621" s="3">
+      <c r="H621" s="2">
         <v>4136.46</v>
       </c>
     </row>
@@ -18555,10 +18561,10 @@
       <c r="F622" t="s">
         <v>10</v>
       </c>
-      <c r="G622" s="1">
+      <c r="G622" s="3">
         <v>46148</v>
       </c>
-      <c r="H622" s="3">
+      <c r="H622" s="2">
         <v>2351.2399999999998</v>
       </c>
     </row>
@@ -18581,10 +18587,10 @@
       <c r="F623" t="s">
         <v>10</v>
       </c>
-      <c r="G623" s="1">
+      <c r="G623" s="3">
         <v>46149</v>
       </c>
-      <c r="H623" s="3">
+      <c r="H623" s="2">
         <v>6984.76</v>
       </c>
     </row>
@@ -18607,10 +18613,10 @@
       <c r="F624" t="s">
         <v>50</v>
       </c>
-      <c r="G624" s="1" t="s">
+      <c r="G624" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H624" s="3">
+      <c r="H624" s="2">
         <v>33802.879999999997</v>
       </c>
     </row>
@@ -18633,10 +18639,10 @@
       <c r="F625" t="s">
         <v>31</v>
       </c>
-      <c r="G625" s="1" t="s">
+      <c r="G625" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H625" s="3">
+      <c r="H625" s="2">
         <v>2571.04</v>
       </c>
     </row>
@@ -18659,10 +18665,10 @@
       <c r="F626" t="s">
         <v>28</v>
       </c>
-      <c r="G626">
+      <c r="G626" s="3">
         <v>46148</v>
       </c>
-      <c r="H626" s="3">
+      <c r="H626" s="2">
         <v>4905.7299999999996</v>
       </c>
     </row>
@@ -18685,10 +18691,10 @@
       <c r="F627" t="s">
         <v>28</v>
       </c>
-      <c r="G627">
+      <c r="G627" s="3">
         <v>46148</v>
       </c>
-      <c r="H627" s="3">
+      <c r="H627" s="2">
         <v>3038.3</v>
       </c>
     </row>
@@ -18711,10 +18717,10 @@
       <c r="F628" t="s">
         <v>28</v>
       </c>
-      <c r="G628" s="1">
+      <c r="G628" s="3">
         <v>46148</v>
       </c>
-      <c r="H628" s="3">
+      <c r="H628" s="2">
         <v>10102.08</v>
       </c>
     </row>
@@ -18737,10 +18743,10 @@
       <c r="F629" t="s">
         <v>31</v>
       </c>
-      <c r="G629" s="1" t="s">
+      <c r="G629" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H629" s="3">
+      <c r="H629" s="2">
         <v>6072.65</v>
       </c>
     </row>
@@ -18763,10 +18769,10 @@
       <c r="F630" t="s">
         <v>31</v>
       </c>
-      <c r="G630" s="1">
+      <c r="G630" s="3">
         <v>46148</v>
       </c>
-      <c r="H630" s="3">
+      <c r="H630" s="2">
         <v>2965.24</v>
       </c>
     </row>
@@ -18789,10 +18795,10 @@
       <c r="F631" t="s">
         <v>117</v>
       </c>
-      <c r="G631">
+      <c r="G631" s="3">
         <v>46149</v>
       </c>
-      <c r="H631" s="3">
+      <c r="H631" s="2">
         <v>1299.8</v>
       </c>
     </row>
@@ -18815,10 +18821,10 @@
       <c r="F632" t="s">
         <v>28</v>
       </c>
-      <c r="G632" s="1">
+      <c r="G632" s="3">
         <v>46148</v>
       </c>
-      <c r="H632" s="3">
+      <c r="H632" s="2">
         <v>12542.05</v>
       </c>
     </row>
@@ -18841,10 +18847,10 @@
       <c r="F633" t="s">
         <v>117</v>
       </c>
-      <c r="G633">
+      <c r="G633" s="3">
         <v>46149</v>
       </c>
-      <c r="H633" s="3">
+      <c r="H633" s="2">
         <v>963.58</v>
       </c>
     </row>
@@ -18867,10 +18873,10 @@
       <c r="F634" t="s">
         <v>117</v>
       </c>
-      <c r="G634">
+      <c r="G634" s="3">
         <v>46149</v>
       </c>
-      <c r="H634" s="3">
+      <c r="H634" s="2">
         <v>764.74</v>
       </c>
     </row>
@@ -18893,10 +18899,10 @@
       <c r="F635" t="s">
         <v>31</v>
       </c>
-      <c r="G635" t="s">
+      <c r="G635" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H635" s="3">
+      <c r="H635" s="2">
         <v>17614.05</v>
       </c>
     </row>
@@ -18919,10 +18925,10 @@
       <c r="F636" t="s">
         <v>117</v>
       </c>
-      <c r="G636">
+      <c r="G636" s="3">
         <v>46149</v>
       </c>
-      <c r="H636" s="3">
+      <c r="H636" s="2">
         <v>1958.81</v>
       </c>
     </row>
@@ -18945,10 +18951,10 @@
       <c r="F637" t="s">
         <v>31</v>
       </c>
-      <c r="G637" t="s">
+      <c r="G637" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H637" s="3">
+      <c r="H637" s="2">
         <v>1241.57</v>
       </c>
     </row>
@@ -18971,10 +18977,10 @@
       <c r="F638" t="s">
         <v>50</v>
       </c>
-      <c r="G638" s="1" t="s">
+      <c r="G638" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H638" s="3">
+      <c r="H638" s="2">
         <v>5517.44</v>
       </c>
     </row>
@@ -18997,10 +19003,10 @@
       <c r="F639" t="s">
         <v>31</v>
       </c>
-      <c r="G639" t="s">
+      <c r="G639" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H639" s="3">
+      <c r="H639" s="2">
         <v>1344.94</v>
       </c>
     </row>
@@ -19023,10 +19029,10 @@
       <c r="F640" t="s">
         <v>20</v>
       </c>
-      <c r="G640" s="1">
+      <c r="G640" s="3">
         <v>46149</v>
       </c>
-      <c r="H640" s="3">
+      <c r="H640" s="2">
         <v>3004.7</v>
       </c>
     </row>
@@ -19049,10 +19055,10 @@
       <c r="F641" t="s">
         <v>31</v>
       </c>
-      <c r="G641" s="1" t="s">
+      <c r="G641" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H641" s="3">
+      <c r="H641" s="2">
         <v>2605.36</v>
       </c>
     </row>
@@ -19075,10 +19081,10 @@
       <c r="F642" t="s">
         <v>20</v>
       </c>
-      <c r="G642">
+      <c r="G642" s="3">
         <v>46149</v>
       </c>
-      <c r="H642" s="3">
+      <c r="H642" s="2">
         <v>1319.15</v>
       </c>
     </row>
@@ -19101,10 +19107,10 @@
       <c r="F643" t="s">
         <v>31</v>
       </c>
-      <c r="G643">
+      <c r="G643" s="3">
         <v>46148</v>
       </c>
-      <c r="H643" s="3">
+      <c r="H643" s="2">
         <v>7266.87</v>
       </c>
     </row>
@@ -19127,10 +19133,10 @@
       <c r="F644" t="s">
         <v>31</v>
       </c>
-      <c r="G644" s="1" t="s">
+      <c r="G644" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H644" s="3">
+      <c r="H644" s="2">
         <v>3508.97</v>
       </c>
     </row>
@@ -19153,10 +19159,10 @@
       <c r="F645" t="s">
         <v>31</v>
       </c>
-      <c r="G645" t="s">
+      <c r="G645" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H645" s="3">
+      <c r="H645" s="2">
         <v>731.07</v>
       </c>
     </row>
@@ -19179,10 +19185,10 @@
       <c r="F646" t="s">
         <v>31</v>
       </c>
-      <c r="G646" t="s">
+      <c r="G646" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H646" s="3">
+      <c r="H646" s="2">
         <v>504.66</v>
       </c>
     </row>
@@ -19205,10 +19211,10 @@
       <c r="F647" t="s">
         <v>117</v>
       </c>
-      <c r="G647">
+      <c r="G647" s="3">
         <v>46149</v>
       </c>
-      <c r="H647" s="3">
+      <c r="H647" s="2">
         <v>1669.99</v>
       </c>
     </row>

--- a/Pedidos.xlsx
+++ b/Pedidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E7C086B-C609-4997-9B19-8945AF0A6DDF}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B8DBC8E-C6DC-420E-963D-02779DAF5136}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2743" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="490">
   <si>
     <t>Pedido</t>
   </si>
@@ -2030,11 +2030,11 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2059,8 +2059,8 @@
     <tableColumn id="4" xr3:uid="{09C6AB47-50A6-4A77-84E1-F9C46CEFB0BA}" name="UF"/>
     <tableColumn id="5" xr3:uid="{60CC8499-AF85-4A3E-B15F-FAC268AEA396}" name="Status"/>
     <tableColumn id="6" xr3:uid="{A7B89925-D806-422B-A861-E9CDD8B38B51}" name="Motivo"/>
-    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{81A912E1-0DAE-4094-8FC5-6F9C3F7FEA4E}" name="Valor (R$)" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{81A912E1-0DAE-4094-8FC5-6F9C3F7FEA4E}" name="Valor (R$)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2392,7 +2392,7 @@
     <col min="4" max="4" width="5.42578125" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2467,8 +2467,8 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>11</v>
+      <c r="G3" t="s">
+        <v>14</v>
       </c>
       <c r="H3" s="2">
         <v>373.34</v>
@@ -2493,8 +2493,8 @@
       <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>11</v>
+      <c r="G4" t="s">
+        <v>14</v>
       </c>
       <c r="H4" s="2">
         <v>507.83</v>
@@ -2519,8 +2519,8 @@
       <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
+      <c r="G5" t="s">
+        <v>14</v>
       </c>
       <c r="H5" s="2">
         <v>507.83</v>
@@ -2545,8 +2545,8 @@
       <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>11</v>
+      <c r="G6" t="s">
+        <v>14</v>
       </c>
       <c r="H6" s="2">
         <v>507.83</v>
@@ -2571,8 +2571,8 @@
       <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>11</v>
+      <c r="G7" t="s">
+        <v>14</v>
       </c>
       <c r="H7" s="2">
         <v>281.19</v>
@@ -3793,8 +3793,8 @@
       <c r="F54" t="s">
         <v>14</v>
       </c>
-      <c r="G54" s="3">
-        <v>46149</v>
+      <c r="G54" t="s">
+        <v>14</v>
       </c>
       <c r="H54" s="2">
         <v>143022.59</v>
@@ -3819,8 +3819,8 @@
       <c r="F55" t="s">
         <v>14</v>
       </c>
-      <c r="G55" s="3">
-        <v>46149</v>
+      <c r="G55" t="s">
+        <v>14</v>
       </c>
       <c r="H55" s="2">
         <v>92986.37</v>
@@ -3845,8 +3845,8 @@
       <c r="F56" t="s">
         <v>14</v>
       </c>
-      <c r="G56" s="3">
-        <v>46149</v>
+      <c r="G56" t="s">
+        <v>14</v>
       </c>
       <c r="H56" s="2">
         <v>126974.77</v>
@@ -3871,8 +3871,8 @@
       <c r="F57" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="3">
-        <v>46149</v>
+      <c r="G57" t="s">
+        <v>14</v>
       </c>
       <c r="H57" s="2">
         <v>174088.36</v>
@@ -4027,8 +4027,8 @@
       <c r="F63" t="s">
         <v>14</v>
       </c>
-      <c r="G63" s="3">
-        <v>46149</v>
+      <c r="G63" t="s">
+        <v>14</v>
       </c>
       <c r="H63" s="2">
         <v>1609.29</v>
@@ -4105,8 +4105,8 @@
       <c r="F66" t="s">
         <v>14</v>
       </c>
-      <c r="G66" s="3">
-        <v>46149</v>
+      <c r="G66" t="s">
+        <v>14</v>
       </c>
       <c r="H66" s="2">
         <v>1003.73</v>
@@ -4131,8 +4131,8 @@
       <c r="F67" t="s">
         <v>14</v>
       </c>
-      <c r="G67" s="3">
-        <v>46149</v>
+      <c r="G67" t="s">
+        <v>14</v>
       </c>
       <c r="H67" s="2">
         <v>1278.51</v>
@@ -4209,8 +4209,8 @@
       <c r="F70" t="s">
         <v>14</v>
       </c>
-      <c r="G70" s="3">
-        <v>46149</v>
+      <c r="G70" t="s">
+        <v>14</v>
       </c>
       <c r="H70" s="2">
         <v>1062.9000000000001</v>
@@ -4261,8 +4261,8 @@
       <c r="F72" t="s">
         <v>14</v>
       </c>
-      <c r="G72" s="3">
-        <v>46149</v>
+      <c r="G72" t="s">
+        <v>14</v>
       </c>
       <c r="H72" s="2">
         <v>1437.46</v>
@@ -4287,8 +4287,8 @@
       <c r="F73" t="s">
         <v>14</v>
       </c>
-      <c r="G73" s="3">
-        <v>46149</v>
+      <c r="G73" t="s">
+        <v>14</v>
       </c>
       <c r="H73" s="2">
         <v>531.45000000000005</v>
@@ -4313,8 +4313,8 @@
       <c r="F74" t="s">
         <v>14</v>
       </c>
-      <c r="G74" s="3">
-        <v>46149</v>
+      <c r="G74" t="s">
+        <v>14</v>
       </c>
       <c r="H74" s="2">
         <v>239.58</v>
@@ -4339,8 +4339,8 @@
       <c r="F75" t="s">
         <v>14</v>
       </c>
-      <c r="G75" s="3">
-        <v>46149</v>
+      <c r="G75" t="s">
+        <v>14</v>
       </c>
       <c r="H75" s="2">
         <v>470.98</v>
@@ -4365,8 +4365,8 @@
       <c r="F76" t="s">
         <v>14</v>
       </c>
-      <c r="G76" s="3">
-        <v>46149</v>
+      <c r="G76" t="s">
+        <v>14</v>
       </c>
       <c r="H76" s="2">
         <v>1197.8800000000001</v>
@@ -4391,8 +4391,8 @@
       <c r="F77" t="s">
         <v>14</v>
       </c>
-      <c r="G77" s="3">
-        <v>46149</v>
+      <c r="G77" t="s">
+        <v>14</v>
       </c>
       <c r="H77" s="2">
         <v>1197.8800000000001</v>
@@ -4443,8 +4443,8 @@
       <c r="F79" t="s">
         <v>14</v>
       </c>
-      <c r="G79" s="3">
-        <v>46149</v>
+      <c r="G79" t="s">
+        <v>14</v>
       </c>
       <c r="H79" s="2">
         <v>479.15</v>
@@ -4469,8 +4469,8 @@
       <c r="F80" t="s">
         <v>14</v>
       </c>
-      <c r="G80" s="3">
-        <v>46149</v>
+      <c r="G80" t="s">
+        <v>14</v>
       </c>
       <c r="H80" s="2">
         <v>479.15</v>
@@ -4495,8 +4495,8 @@
       <c r="F81" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="3">
-        <v>46149</v>
+      <c r="G81" t="s">
+        <v>14</v>
       </c>
       <c r="H81" s="2">
         <v>479.15</v>
@@ -4547,8 +4547,8 @@
       <c r="F83" t="s">
         <v>14</v>
       </c>
-      <c r="G83" s="3">
-        <v>46149</v>
+      <c r="G83" t="s">
+        <v>14</v>
       </c>
       <c r="H83" s="2">
         <v>494.78</v>
@@ -4573,8 +4573,8 @@
       <c r="F84" t="s">
         <v>14</v>
       </c>
-      <c r="G84" s="3">
-        <v>46149</v>
+      <c r="G84" t="s">
+        <v>14</v>
       </c>
       <c r="H84" s="2">
         <v>1236.95</v>
@@ -4599,8 +4599,8 @@
       <c r="F85" t="s">
         <v>14</v>
       </c>
-      <c r="G85" s="3">
-        <v>46149</v>
+      <c r="G85" t="s">
+        <v>14</v>
       </c>
       <c r="H85" s="2">
         <v>277.42</v>
@@ -4625,8 +4625,8 @@
       <c r="F86" t="s">
         <v>14</v>
       </c>
-      <c r="G86" s="3">
-        <v>46149</v>
+      <c r="G86" t="s">
+        <v>14</v>
       </c>
       <c r="H86" s="2">
         <v>1009.75</v>
@@ -4651,8 +4651,8 @@
       <c r="F87" t="s">
         <v>14</v>
       </c>
-      <c r="G87" s="3">
-        <v>46149</v>
+      <c r="G87" t="s">
+        <v>14</v>
       </c>
       <c r="H87" s="2">
         <v>246.67</v>
@@ -4677,8 +4677,8 @@
       <c r="F88" t="s">
         <v>14</v>
       </c>
-      <c r="G88" s="3">
-        <v>46149</v>
+      <c r="G88" t="s">
+        <v>14</v>
       </c>
       <c r="H88" s="2">
         <v>757.31</v>
@@ -4703,8 +4703,8 @@
       <c r="F89" t="s">
         <v>14</v>
       </c>
-      <c r="G89" s="3">
-        <v>46149</v>
+      <c r="G89" t="s">
+        <v>14</v>
       </c>
       <c r="H89" s="2">
         <v>1262.19</v>
@@ -4729,8 +4729,8 @@
       <c r="F90" t="s">
         <v>14</v>
       </c>
-      <c r="G90" s="3">
-        <v>46149</v>
+      <c r="G90" t="s">
+        <v>14</v>
       </c>
       <c r="H90" s="2">
         <v>1009.75</v>
@@ -4781,8 +4781,8 @@
       <c r="F92" t="s">
         <v>14</v>
       </c>
-      <c r="G92" s="3">
-        <v>46149</v>
+      <c r="G92" t="s">
+        <v>14</v>
       </c>
       <c r="H92" s="2">
         <v>1009.75</v>
@@ -4807,8 +4807,8 @@
       <c r="F93" t="s">
         <v>14</v>
       </c>
-      <c r="G93" s="3">
-        <v>46149</v>
+      <c r="G93" t="s">
+        <v>14</v>
       </c>
       <c r="H93" s="2">
         <v>757.73</v>
@@ -4833,8 +4833,8 @@
       <c r="F94" t="s">
         <v>14</v>
       </c>
-      <c r="G94" s="3">
-        <v>46149</v>
+      <c r="G94" t="s">
+        <v>14</v>
       </c>
       <c r="H94" s="2">
         <v>749.34</v>
@@ -4859,8 +4859,8 @@
       <c r="F95" t="s">
         <v>14</v>
       </c>
-      <c r="G95" s="3">
-        <v>46149</v>
+      <c r="G95" t="s">
+        <v>14</v>
       </c>
       <c r="H95" s="2">
         <v>263.41000000000003</v>
@@ -4885,8 +4885,8 @@
       <c r="F96" t="s">
         <v>14</v>
       </c>
-      <c r="G96" s="3">
-        <v>46149</v>
+      <c r="G96" t="s">
+        <v>14</v>
       </c>
       <c r="H96" s="2">
         <v>1317.03</v>
@@ -4911,8 +4911,8 @@
       <c r="F97" t="s">
         <v>14</v>
       </c>
-      <c r="G97" s="3">
-        <v>46149</v>
+      <c r="G97" t="s">
+        <v>14</v>
       </c>
       <c r="H97" s="2">
         <v>265.72000000000003</v>
@@ -4937,8 +4937,8 @@
       <c r="F98" t="s">
         <v>14</v>
       </c>
-      <c r="G98" s="3">
-        <v>46149</v>
+      <c r="G98" t="s">
+        <v>14</v>
       </c>
       <c r="H98" s="2">
         <v>445.9</v>
@@ -4963,8 +4963,8 @@
       <c r="F99" t="s">
         <v>14</v>
       </c>
-      <c r="G99" s="3">
-        <v>46149</v>
+      <c r="G99" t="s">
+        <v>14</v>
       </c>
       <c r="H99" s="2">
         <v>445.9</v>
@@ -4989,8 +4989,8 @@
       <c r="F100" t="s">
         <v>14</v>
       </c>
-      <c r="G100" s="3">
-        <v>46149</v>
+      <c r="G100" t="s">
+        <v>14</v>
       </c>
       <c r="H100" s="2">
         <v>268.02</v>
@@ -5015,8 +5015,8 @@
       <c r="F101" t="s">
         <v>14</v>
       </c>
-      <c r="G101" s="3">
-        <v>46149</v>
+      <c r="G101" t="s">
+        <v>14</v>
       </c>
       <c r="H101" s="2">
         <v>488.93</v>
@@ -5067,8 +5067,8 @@
       <c r="F103" t="s">
         <v>14</v>
       </c>
-      <c r="G103" s="3">
-        <v>46149</v>
+      <c r="G103" t="s">
+        <v>14</v>
       </c>
       <c r="H103" s="2">
         <v>227.17</v>
@@ -5093,8 +5093,8 @@
       <c r="F104" t="s">
         <v>14</v>
       </c>
-      <c r="G104" s="3">
-        <v>46149</v>
+      <c r="G104" t="s">
+        <v>14</v>
       </c>
       <c r="H104" s="2">
         <v>1341.07</v>
@@ -5119,8 +5119,8 @@
       <c r="F105" t="s">
         <v>14</v>
       </c>
-      <c r="G105" s="3">
-        <v>46149</v>
+      <c r="G105" t="s">
+        <v>14</v>
       </c>
       <c r="H105" s="2">
         <v>2675.52</v>
@@ -5145,8 +5145,8 @@
       <c r="F106" t="s">
         <v>14</v>
       </c>
-      <c r="G106" s="3">
-        <v>46149</v>
+      <c r="G106" t="s">
+        <v>14</v>
       </c>
       <c r="H106" s="2">
         <v>646.14</v>
@@ -5171,8 +5171,8 @@
       <c r="F107" t="s">
         <v>14</v>
       </c>
-      <c r="G107" s="3">
-        <v>46149</v>
+      <c r="G107" t="s">
+        <v>14</v>
       </c>
       <c r="H107" s="2">
         <v>1062.9000000000001</v>
@@ -5197,8 +5197,8 @@
       <c r="F108" t="s">
         <v>14</v>
       </c>
-      <c r="G108" s="3">
-        <v>46149</v>
+      <c r="G108" t="s">
+        <v>14</v>
       </c>
       <c r="H108" s="2">
         <v>454.34</v>
@@ -5223,8 +5223,8 @@
       <c r="F109" t="s">
         <v>14</v>
       </c>
-      <c r="G109" s="3">
-        <v>46149</v>
+      <c r="G109" t="s">
+        <v>14</v>
       </c>
       <c r="H109" s="2">
         <v>998.83</v>
@@ -5249,8 +5249,8 @@
       <c r="F110" t="s">
         <v>14</v>
       </c>
-      <c r="G110" s="3">
-        <v>46149</v>
+      <c r="G110" t="s">
+        <v>14</v>
       </c>
       <c r="H110" s="2">
         <v>1466.8</v>
@@ -5275,8 +5275,8 @@
       <c r="F111" t="s">
         <v>14</v>
       </c>
-      <c r="G111" s="3">
-        <v>46149</v>
+      <c r="G111" t="s">
+        <v>14</v>
       </c>
       <c r="H111" s="2">
         <v>1072.8599999999999</v>
@@ -5327,8 +5327,8 @@
       <c r="F113" t="s">
         <v>14</v>
       </c>
-      <c r="G113" s="3">
-        <v>46149</v>
+      <c r="G113" t="s">
+        <v>14</v>
       </c>
       <c r="H113" s="2">
         <v>92.7</v>
@@ -5353,8 +5353,8 @@
       <c r="F114" t="s">
         <v>14</v>
       </c>
-      <c r="G114" s="3">
-        <v>46149</v>
+      <c r="G114" t="s">
+        <v>14</v>
       </c>
       <c r="H114" s="2">
         <v>1062.9000000000001</v>
@@ -5431,8 +5431,8 @@
       <c r="F117" t="s">
         <v>14</v>
       </c>
-      <c r="G117" s="3">
-        <v>46149</v>
+      <c r="G117" t="s">
+        <v>14</v>
       </c>
       <c r="H117" s="2">
         <v>749.12</v>
@@ -5457,8 +5457,8 @@
       <c r="F118" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="3">
-        <v>46149</v>
+      <c r="G118" t="s">
+        <v>14</v>
       </c>
       <c r="H118" s="2">
         <v>1363.02</v>
@@ -5483,8 +5483,8 @@
       <c r="F119" t="s">
         <v>14</v>
       </c>
-      <c r="G119" s="3">
-        <v>46149</v>
+      <c r="G119" t="s">
+        <v>14</v>
       </c>
       <c r="H119" s="2">
         <v>840.6</v>
@@ -5509,8 +5509,8 @@
       <c r="F120" t="s">
         <v>14</v>
       </c>
-      <c r="G120" s="3">
-        <v>46149</v>
+      <c r="G120" t="s">
+        <v>14</v>
       </c>
       <c r="H120" s="2">
         <v>559.62</v>
@@ -5535,8 +5535,8 @@
       <c r="F121" t="s">
         <v>14</v>
       </c>
-      <c r="G121" s="3">
-        <v>46149</v>
+      <c r="G121" t="s">
+        <v>14</v>
       </c>
       <c r="H121" s="2">
         <v>1932.44</v>
@@ -5639,8 +5639,8 @@
       <c r="F125" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="3">
-        <v>46149</v>
+      <c r="G125" t="s">
+        <v>14</v>
       </c>
       <c r="H125" s="2">
         <v>1148.1099999999999</v>
@@ -5925,8 +5925,8 @@
       <c r="F136" t="s">
         <v>14</v>
       </c>
-      <c r="G136" s="3">
-        <v>46149</v>
+      <c r="G136" t="s">
+        <v>14</v>
       </c>
       <c r="H136" s="2">
         <v>1329</v>
@@ -6341,8 +6341,8 @@
       <c r="F152" t="s">
         <v>14</v>
       </c>
-      <c r="G152" s="3">
-        <v>46149</v>
+      <c r="G152" t="s">
+        <v>14</v>
       </c>
       <c r="H152" s="2">
         <v>844.75</v>
@@ -6471,8 +6471,8 @@
       <c r="F157" t="s">
         <v>14</v>
       </c>
-      <c r="G157" s="3">
-        <v>46149</v>
+      <c r="G157" t="s">
+        <v>14</v>
       </c>
       <c r="H157" s="2">
         <v>827.49</v>
@@ -6705,8 +6705,8 @@
       <c r="F166" t="s">
         <v>14</v>
       </c>
-      <c r="G166" s="3">
-        <v>46149</v>
+      <c r="G166" t="s">
+        <v>14</v>
       </c>
       <c r="H166" s="2">
         <v>805.13</v>
@@ -6731,8 +6731,8 @@
       <c r="F167" t="s">
         <v>14</v>
       </c>
-      <c r="G167" s="3">
-        <v>46149</v>
+      <c r="G167" t="s">
+        <v>14</v>
       </c>
       <c r="H167" s="2">
         <v>10373.65</v>
@@ -6939,8 +6939,8 @@
       <c r="F175" t="s">
         <v>14</v>
       </c>
-      <c r="G175" s="3">
-        <v>46149</v>
+      <c r="G175" t="s">
+        <v>14</v>
       </c>
       <c r="H175" s="2">
         <v>267.39</v>
@@ -7147,8 +7147,8 @@
       <c r="F183" t="s">
         <v>14</v>
       </c>
-      <c r="G183" s="3">
-        <v>46149</v>
+      <c r="G183" t="s">
+        <v>14</v>
       </c>
       <c r="H183" s="2">
         <v>563.16999999999996</v>
@@ -7173,8 +7173,8 @@
       <c r="F184" t="s">
         <v>14</v>
       </c>
-      <c r="G184" s="3">
-        <v>46149</v>
+      <c r="G184" t="s">
+        <v>14</v>
       </c>
       <c r="H184" s="2">
         <v>2251.67</v>
@@ -7381,8 +7381,8 @@
       <c r="F192" t="s">
         <v>14</v>
       </c>
-      <c r="G192" s="3">
-        <v>46149</v>
+      <c r="G192" t="s">
+        <v>14</v>
       </c>
       <c r="H192" s="2">
         <v>1639.89</v>
@@ -7407,8 +7407,8 @@
       <c r="F193" t="s">
         <v>14</v>
       </c>
-      <c r="G193" s="3">
-        <v>46149</v>
+      <c r="G193" t="s">
+        <v>14</v>
       </c>
       <c r="H193" s="2">
         <v>294.2</v>
@@ -7719,8 +7719,8 @@
       <c r="F205" t="s">
         <v>14</v>
       </c>
-      <c r="G205" s="3">
-        <v>46149</v>
+      <c r="G205" t="s">
+        <v>14</v>
       </c>
       <c r="H205" s="2">
         <v>922.89</v>
@@ -7745,8 +7745,8 @@
       <c r="F206" t="s">
         <v>14</v>
       </c>
-      <c r="G206" s="3">
-        <v>46149</v>
+      <c r="G206" t="s">
+        <v>14</v>
       </c>
       <c r="H206" s="2">
         <v>2674.64</v>
@@ -8109,8 +8109,8 @@
       <c r="F220" t="s">
         <v>14</v>
       </c>
-      <c r="G220" s="3">
-        <v>46149</v>
+      <c r="G220" t="s">
+        <v>14</v>
       </c>
       <c r="H220" s="2">
         <v>1223.49</v>
@@ -9019,8 +9019,8 @@
       <c r="F255" t="s">
         <v>14</v>
       </c>
-      <c r="G255" s="3">
-        <v>46149</v>
+      <c r="G255" t="s">
+        <v>14</v>
       </c>
       <c r="H255" s="2">
         <v>12966.57</v>
@@ -9825,8 +9825,8 @@
       <c r="F286" t="s">
         <v>14</v>
       </c>
-      <c r="G286" s="3">
-        <v>46149</v>
+      <c r="G286" t="s">
+        <v>14</v>
       </c>
       <c r="H286" s="2">
         <v>296.81</v>
@@ -10007,8 +10007,8 @@
       <c r="F293" t="s">
         <v>14</v>
       </c>
-      <c r="G293" s="3">
-        <v>46149</v>
+      <c r="G293" t="s">
+        <v>14</v>
       </c>
       <c r="H293" s="2">
         <v>475.96</v>
@@ -11645,8 +11645,8 @@
       <c r="F356" t="s">
         <v>14</v>
       </c>
-      <c r="G356" s="3">
-        <v>46149</v>
+      <c r="G356" t="s">
+        <v>14</v>
       </c>
       <c r="H356" s="2">
         <v>1846.27</v>
@@ -11697,8 +11697,8 @@
       <c r="F358" t="s">
         <v>14</v>
       </c>
-      <c r="G358" s="3">
-        <v>46149</v>
+      <c r="G358" t="s">
+        <v>14</v>
       </c>
       <c r="H358" s="2">
         <v>1609.21</v>
@@ -15233,8 +15233,8 @@
       <c r="F494" t="s">
         <v>14</v>
       </c>
-      <c r="G494" s="3">
-        <v>46149</v>
+      <c r="G494" t="s">
+        <v>14</v>
       </c>
       <c r="H494" s="2">
         <v>6741.46</v>

--- a/Pedidos.xlsx
+++ b/Pedidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A45B568-B530-426F-8F32-B3490B150728}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F0BBE3-CFA1-442E-830B-A26C09ED37BC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
+    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3531" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3478" uniqueCount="546">
   <si>
     <t>Pedido</t>
   </si>
@@ -1655,14 +1655,18 @@
   </si>
   <si>
     <t>M S H PORTELLA ME</t>
+  </si>
+  <si>
+    <t>CNPJ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="00\.000\.000\/0000\-00"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -2141,7 +2145,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2149,6 +2153,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2194,13 +2199,16 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="167" formatCode="00\.000\.000\/0000\-00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2216,18 +2224,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8D7DE48-BC19-48D4-80C5-DD934A925EB7}" name="TabelaPedidos" displayName="TabelaPedidos" ref="A1:I649" totalsRowShown="0">
-  <autoFilter ref="A1:I649" xr:uid="{D8D7DE48-BC19-48D4-80C5-DD934A925EB7}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8D7DE48-BC19-48D4-80C5-DD934A925EB7}" name="TabelaPedidos" displayName="TabelaPedidos" ref="A1:J649" totalsRowShown="0">
+  <autoFilter ref="A1:J649" xr:uid="{D8D7DE48-BC19-48D4-80C5-DD934A925EB7}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F779E64C-ADAA-4D54-8902-56E277786201}" name="RC"/>
     <tableColumn id="2" xr3:uid="{C62B1A3A-DDAA-490B-80CE-E589A36EE54C}" name="Pedido"/>
     <tableColumn id="3" xr3:uid="{C05D51E9-5E2E-464D-A79D-DC4B8DD8B1B5}" name="Cliente"/>
     <tableColumn id="4" xr3:uid="{09C6AB47-50A6-4A77-84E1-F9C46CEFB0BA}" name="UF"/>
     <tableColumn id="5" xr3:uid="{60CC8499-AF85-4A3E-B15F-FAC268AEA396}" name="Status"/>
     <tableColumn id="6" xr3:uid="{A7B89925-D806-422B-A861-E9CDD8B38B51}" name="Motivo"/>
-    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{81A912E1-0DAE-4094-8FC5-6F9C3F7FEA4E}" name="Valor (R$)" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{98E6D74D-D3C5-467A-B9E0-46B2439E66AE}" name="Coordenador"/>
+    <tableColumn id="10" xr3:uid="{1413044C-F6B3-417B-90E7-5F6797B59268}" name="CNPJ" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2550,7 +2559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906ACCD0-13B7-452C-BEC4-FB1DD312FFC4}">
-  <dimension ref="A1:I649"/>
+  <dimension ref="A1:J649"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -2562,9 +2571,10 @@
     <col min="7" max="7" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>184</v>
       </c>
@@ -2592,8 +2602,11 @@
       <c r="I1" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="5" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>818</v>
       </c>
@@ -2621,8 +2634,11 @@
       <c r="I2" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="5">
+        <v>10230480004047</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1090</v>
       </c>
@@ -2642,7 +2658,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H3" s="2">
         <v>373.34</v>
@@ -2650,8 +2666,11 @@
       <c r="I3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="5">
+        <v>41248067000399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>969</v>
       </c>
@@ -2671,7 +2690,7 @@
         <v>14</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2">
         <v>507.83</v>
@@ -2679,8 +2698,11 @@
       <c r="I4" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="5">
+        <v>10944409000110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>969</v>
       </c>
@@ -2700,7 +2722,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2">
         <v>507.83</v>
@@ -2708,8 +2730,11 @@
       <c r="I5" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" s="5">
+        <v>28108302000105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>969</v>
       </c>
@@ -2729,7 +2754,7 @@
         <v>14</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2">
         <v>507.83</v>
@@ -2737,8 +2762,11 @@
       <c r="I6" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="5">
+        <v>17193124000133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2069</v>
       </c>
@@ -2758,7 +2786,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2">
         <v>281.19</v>
@@ -2766,8 +2794,11 @@
       <c r="I7" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="5">
+        <v>9436414000132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>770</v>
       </c>
@@ -2795,8 +2826,11 @@
       <c r="I8" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="5">
+        <v>70220389000670</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1019</v>
       </c>
@@ -2824,8 +2858,11 @@
       <c r="I9" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="5">
+        <v>5477011000180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3069</v>
       </c>
@@ -2853,8 +2890,11 @@
       <c r="I10" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="5">
+        <v>49351171000154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1090</v>
       </c>
@@ -2882,8 +2922,11 @@
       <c r="I11" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="5">
+        <v>41248067001522</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1090</v>
       </c>
@@ -2911,8 +2954,11 @@
       <c r="I12" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="5">
+        <v>2155469000982</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>818</v>
       </c>
@@ -2940,8 +2986,11 @@
       <c r="I13" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="5">
+        <v>17022421000116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>818</v>
       </c>
@@ -2969,8 +3018,11 @@
       <c r="I14" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="5">
+        <v>11165236000102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>770</v>
       </c>
@@ -2998,8 +3050,11 @@
       <c r="I15" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="5">
+        <v>262666000118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1054</v>
       </c>
@@ -3027,8 +3082,11 @@
       <c r="I16" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="5">
+        <v>55989054000113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>665</v>
       </c>
@@ -3056,8 +3114,11 @@
       <c r="I17" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="5">
+        <v>58493318000131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2041</v>
       </c>
@@ -3085,8 +3146,11 @@
       <c r="I18" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="5">
+        <v>60594729000165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2041</v>
       </c>
@@ -3114,8 +3178,11 @@
       <c r="I19" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="5">
+        <v>27754079000100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>968</v>
       </c>
@@ -3143,8 +3210,11 @@
       <c r="I20" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="5">
+        <v>63201867000125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1019</v>
       </c>
@@ -3172,8 +3242,11 @@
       <c r="I21" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="5">
+        <v>10808699000174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1090</v>
       </c>
@@ -3201,8 +3274,11 @@
       <c r="I22" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="5">
+        <v>3104367000305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3069</v>
       </c>
@@ -3230,8 +3306,11 @@
       <c r="I23" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="5">
+        <v>46676168000112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>863</v>
       </c>
@@ -3259,8 +3338,11 @@
       <c r="I24" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="5">
+        <v>54710956000106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3045</v>
       </c>
@@ -3288,8 +3370,11 @@
       <c r="I25" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="5">
+        <v>13305660000122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>665</v>
       </c>
@@ -3317,8 +3402,11 @@
       <c r="I26" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" s="5">
+        <v>42091402000199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2020</v>
       </c>
@@ -3346,8 +3434,11 @@
       <c r="I27" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="5">
+        <v>9018345000147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>609</v>
       </c>
@@ -3375,8 +3466,11 @@
       <c r="I28" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="5">
+        <v>97748958003031</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>711</v>
       </c>
@@ -3404,8 +3498,11 @@
       <c r="I29" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="5">
+        <v>99002623999931</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>898</v>
       </c>
@@ -3433,8 +3530,11 @@
       <c r="I30" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" s="5">
+        <v>89086144000540</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>918</v>
       </c>
@@ -3462,8 +3562,11 @@
       <c r="I31" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>918</v>
       </c>
@@ -3491,8 +3594,11 @@
       <c r="I32" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>918</v>
       </c>
@@ -3520,8 +3626,11 @@
       <c r="I33" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>918</v>
       </c>
@@ -3549,8 +3658,11 @@
       <c r="I34" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>918</v>
       </c>
@@ -3578,8 +3690,11 @@
       <c r="I35" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>60</v>
       </c>
@@ -3607,8 +3722,11 @@
       <c r="I36" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" s="5">
+        <v>1675208000173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1162</v>
       </c>
@@ -3627,8 +3745,8 @@
       <c r="F37" t="s">
         <v>14</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>14</v>
+      <c r="G37" s="4">
+        <v>46155</v>
       </c>
       <c r="H37" s="2">
         <v>143022.59</v>
@@ -3636,8 +3754,11 @@
       <c r="I37" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" s="5">
+        <v>25769266000124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1162</v>
       </c>
@@ -3656,8 +3777,8 @@
       <c r="F38" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>14</v>
+      <c r="G38" s="4">
+        <v>46155</v>
       </c>
       <c r="H38" s="2">
         <v>92986.37</v>
@@ -3665,8 +3786,11 @@
       <c r="I38" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" s="5">
+        <v>25769266000124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1162</v>
       </c>
@@ -3685,8 +3809,8 @@
       <c r="F39" t="s">
         <v>14</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>14</v>
+      <c r="G39" s="4">
+        <v>46155</v>
       </c>
       <c r="H39" s="2">
         <v>126974.77</v>
@@ -3694,8 +3818,11 @@
       <c r="I39" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" s="5">
+        <v>25769266000124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1162</v>
       </c>
@@ -3714,8 +3841,8 @@
       <c r="F40" t="s">
         <v>14</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>14</v>
+      <c r="G40" s="4">
+        <v>46155</v>
       </c>
       <c r="H40" s="2">
         <v>174088.36</v>
@@ -3723,8 +3850,11 @@
       <c r="I40" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J40" s="5">
+        <v>25769266000124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>918</v>
       </c>
@@ -3752,8 +3882,11 @@
       <c r="I41" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J41" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>918</v>
       </c>
@@ -3781,8 +3914,11 @@
       <c r="I42" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J42" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>918</v>
       </c>
@@ -3810,8 +3946,11 @@
       <c r="I43" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>918</v>
       </c>
@@ -3839,8 +3978,11 @@
       <c r="I44" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J44" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>918</v>
       </c>
@@ -3868,8 +4010,11 @@
       <c r="I45" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J45" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>918</v>
       </c>
@@ -3897,8 +4042,11 @@
       <c r="I46" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J46" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>564</v>
       </c>
@@ -3917,8 +4065,8 @@
       <c r="F47" t="s">
         <v>14</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>14</v>
+      <c r="G47" s="4">
+        <v>46155</v>
       </c>
       <c r="H47" s="2">
         <v>1003.73</v>
@@ -3926,8 +4074,11 @@
       <c r="I47" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J47" s="5">
+        <v>83109504001305</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1021</v>
       </c>
@@ -3946,8 +4097,8 @@
       <c r="F48" t="s">
         <v>14</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>14</v>
+      <c r="G48" s="4">
+        <v>46155</v>
       </c>
       <c r="H48" s="2">
         <v>1278.51</v>
@@ -3955,8 +4106,11 @@
       <c r="I48" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J48" s="5">
+        <v>10808924000172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3075</v>
       </c>
@@ -3984,8 +4138,11 @@
       <c r="I49" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J49" s="5">
+        <v>3107202000397</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1807</v>
       </c>
@@ -4013,8 +4170,11 @@
       <c r="I50" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J50" s="5">
+        <v>47926159000103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>948</v>
       </c>
@@ -4033,8 +4193,8 @@
       <c r="F51" t="s">
         <v>14</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>14</v>
+      <c r="G51" s="4">
+        <v>46155</v>
       </c>
       <c r="H51" s="2">
         <v>1062.9000000000001</v>
@@ -4042,8 +4202,11 @@
       <c r="I51" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J51" s="5">
+        <v>31991083000232</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>90</v>
       </c>
@@ -4062,8 +4225,8 @@
       <c r="F52" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="4" t="s">
-        <v>14</v>
+      <c r="G52" s="4">
+        <v>46155</v>
       </c>
       <c r="H52" s="2">
         <v>1437.46</v>
@@ -4071,8 +4234,11 @@
       <c r="I52" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J52" s="5">
+        <v>206861000554</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>90</v>
       </c>
@@ -4091,8 +4257,8 @@
       <c r="F53" t="s">
         <v>14</v>
       </c>
-      <c r="G53" s="4" t="s">
-        <v>14</v>
+      <c r="G53" s="4">
+        <v>46155</v>
       </c>
       <c r="H53" s="2">
         <v>531.45000000000005</v>
@@ -4100,8 +4266,11 @@
       <c r="I53" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J53" s="5">
+        <v>38945763000188</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>90</v>
       </c>
@@ -4120,8 +4289,8 @@
       <c r="F54" t="s">
         <v>14</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>14</v>
+      <c r="G54" s="4">
+        <v>46155</v>
       </c>
       <c r="H54" s="2">
         <v>239.58</v>
@@ -4129,8 +4298,11 @@
       <c r="I54" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J54" s="5">
+        <v>206861001100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>722</v>
       </c>
@@ -4149,8 +4321,8 @@
       <c r="F55" t="s">
         <v>14</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>14</v>
+      <c r="G55" s="4">
+        <v>46155</v>
       </c>
       <c r="H55" s="2">
         <v>470.98</v>
@@ -4158,8 +4330,11 @@
       <c r="I55" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J55" s="5">
+        <v>2930802000126</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>90</v>
       </c>
@@ -4178,8 +4353,8 @@
       <c r="F56" t="s">
         <v>14</v>
       </c>
-      <c r="G56" s="4" t="s">
-        <v>14</v>
+      <c r="G56" s="4">
+        <v>46155</v>
       </c>
       <c r="H56" s="2">
         <v>1197.8800000000001</v>
@@ -4187,8 +4362,11 @@
       <c r="I56" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56" s="5">
+        <v>206861001364</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>90</v>
       </c>
@@ -4207,8 +4385,8 @@
       <c r="F57" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="4" t="s">
-        <v>14</v>
+      <c r="G57" s="4">
+        <v>46155</v>
       </c>
       <c r="H57" s="2">
         <v>1197.8800000000001</v>
@@ -4216,8 +4394,11 @@
       <c r="I57" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J57" s="5">
+        <v>206861001445</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>90</v>
       </c>
@@ -4236,8 +4417,8 @@
       <c r="F58" t="s">
         <v>14</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>14</v>
+      <c r="G58" s="4">
+        <v>46155</v>
       </c>
       <c r="H58" s="2">
         <v>479.15</v>
@@ -4245,8 +4426,11 @@
       <c r="I58" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J58" s="5">
+        <v>206861001950</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>90</v>
       </c>
@@ -4265,8 +4449,8 @@
       <c r="F59" t="s">
         <v>14</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>14</v>
+      <c r="G59" s="4">
+        <v>46155</v>
       </c>
       <c r="H59" s="2">
         <v>479.15</v>
@@ -4274,8 +4458,11 @@
       <c r="I59" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J59" s="5">
+        <v>206861002255</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>90</v>
       </c>
@@ -4294,8 +4481,8 @@
       <c r="F60" t="s">
         <v>14</v>
       </c>
-      <c r="G60" s="4" t="s">
-        <v>14</v>
+      <c r="G60" s="4">
+        <v>46155</v>
       </c>
       <c r="H60" s="2">
         <v>479.15</v>
@@ -4303,8 +4490,11 @@
       <c r="I60" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J60" s="5">
+        <v>206861002174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>90</v>
       </c>
@@ -4323,8 +4513,8 @@
       <c r="F61" t="s">
         <v>14</v>
       </c>
-      <c r="G61" s="4" t="s">
-        <v>14</v>
+      <c r="G61" s="4">
+        <v>46155</v>
       </c>
       <c r="H61" s="2">
         <v>494.78</v>
@@ -4332,8 +4522,11 @@
       <c r="I61" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J61" s="5">
+        <v>42171829000105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>90</v>
       </c>
@@ -4352,8 +4545,8 @@
       <c r="F62" t="s">
         <v>14</v>
       </c>
-      <c r="G62" s="4" t="s">
-        <v>14</v>
+      <c r="G62" s="4">
+        <v>46155</v>
       </c>
       <c r="H62" s="2">
         <v>1236.95</v>
@@ -4361,8 +4554,11 @@
       <c r="I62" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J62" s="5">
+        <v>12126674000116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>951</v>
       </c>
@@ -4381,8 +4577,8 @@
       <c r="F63" t="s">
         <v>14</v>
       </c>
-      <c r="G63" s="4" t="s">
-        <v>14</v>
+      <c r="G63" s="4">
+        <v>46155</v>
       </c>
       <c r="H63" s="2">
         <v>277.42</v>
@@ -4390,8 +4586,11 @@
       <c r="I63" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J63" s="5">
+        <v>62315650000507</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2034</v>
       </c>
@@ -4410,8 +4609,8 @@
       <c r="F64" t="s">
         <v>14</v>
       </c>
-      <c r="G64" s="4" t="s">
-        <v>14</v>
+      <c r="G64" s="4">
+        <v>46155</v>
       </c>
       <c r="H64" s="2">
         <v>246.67</v>
@@ -4419,8 +4618,11 @@
       <c r="I64" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J64" s="5">
+        <v>34565675000108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>90</v>
       </c>
@@ -4439,8 +4641,8 @@
       <c r="F65" t="s">
         <v>14</v>
       </c>
-      <c r="G65" s="4" t="s">
-        <v>14</v>
+      <c r="G65" s="4">
+        <v>46155</v>
       </c>
       <c r="H65" s="2">
         <v>757.31</v>
@@ -4448,8 +4650,11 @@
       <c r="I65" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J65" s="5">
+        <v>26018708000163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>90</v>
       </c>
@@ -4468,8 +4673,8 @@
       <c r="F66" t="s">
         <v>14</v>
       </c>
-      <c r="G66" s="4" t="s">
-        <v>14</v>
+      <c r="G66" s="4">
+        <v>46155</v>
       </c>
       <c r="H66" s="2">
         <v>1262.19</v>
@@ -4477,8 +4682,11 @@
       <c r="I66" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J66" s="5">
+        <v>11381620000134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>90</v>
       </c>
@@ -4497,8 +4705,8 @@
       <c r="F67" t="s">
         <v>14</v>
       </c>
-      <c r="G67" s="4" t="s">
-        <v>14</v>
+      <c r="G67" s="4">
+        <v>46155</v>
       </c>
       <c r="H67" s="2">
         <v>1009.75</v>
@@ -4506,8 +4714,11 @@
       <c r="I67" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J67" s="5">
+        <v>47992284000375</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>951</v>
       </c>
@@ -4526,8 +4737,8 @@
       <c r="F68" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="4" t="s">
-        <v>14</v>
+      <c r="G68" s="4">
+        <v>46155</v>
       </c>
       <c r="H68" s="2">
         <v>1401.09</v>
@@ -4535,8 +4746,11 @@
       <c r="I68" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J68" s="5">
+        <v>197752000194</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>90</v>
       </c>
@@ -4555,8 +4769,8 @@
       <c r="F69" t="s">
         <v>14</v>
       </c>
-      <c r="G69" s="4" t="s">
-        <v>14</v>
+      <c r="G69" s="4">
+        <v>46155</v>
       </c>
       <c r="H69" s="2">
         <v>1009.75</v>
@@ -4564,8 +4778,11 @@
       <c r="I69" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J69" s="5">
+        <v>49082222000190</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>3078</v>
       </c>
@@ -4593,8 +4810,11 @@
       <c r="I70" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J70" s="5">
+        <v>44367514000317</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>3078</v>
       </c>
@@ -4622,8 +4842,11 @@
       <c r="I71" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J71" s="5">
+        <v>44367514000155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>3078</v>
       </c>
@@ -4642,8 +4865,8 @@
       <c r="F72" t="s">
         <v>14</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>14</v>
+      <c r="G72" s="4">
+        <v>46155</v>
       </c>
       <c r="H72" s="2">
         <v>263.41000000000003</v>
@@ -4651,8 +4874,11 @@
       <c r="I72" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J72" s="5">
+        <v>8693413000100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>3078</v>
       </c>
@@ -4680,8 +4906,11 @@
       <c r="I73" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J73" s="5">
+        <v>44367514000236</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>951</v>
       </c>
@@ -4700,8 +4929,8 @@
       <c r="F74" t="s">
         <v>14</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>14</v>
+      <c r="G74" s="4">
+        <v>46155</v>
       </c>
       <c r="H74" s="2">
         <v>265.72000000000003</v>
@@ -4709,8 +4938,11 @@
       <c r="I74" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J74" s="5">
+        <v>33041706000312</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>380</v>
       </c>
@@ -4729,8 +4961,8 @@
       <c r="F75" t="s">
         <v>14</v>
       </c>
-      <c r="G75" s="4" t="s">
-        <v>14</v>
+      <c r="G75" s="4">
+        <v>46155</v>
       </c>
       <c r="H75" s="2">
         <v>445.9</v>
@@ -4738,8 +4970,11 @@
       <c r="I75" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J75" s="5">
+        <v>67331538001202</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>380</v>
       </c>
@@ -4758,8 +4993,8 @@
       <c r="F76" t="s">
         <v>14</v>
       </c>
-      <c r="G76" s="4" t="s">
-        <v>14</v>
+      <c r="G76" s="4">
+        <v>46155</v>
       </c>
       <c r="H76" s="2">
         <v>445.9</v>
@@ -4767,8 +5002,11 @@
       <c r="I76" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J76" s="5">
+        <v>67331538000400</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>916</v>
       </c>
@@ -4787,8 +5025,8 @@
       <c r="F77" t="s">
         <v>14</v>
       </c>
-      <c r="G77" s="4" t="s">
-        <v>14</v>
+      <c r="G77" s="4">
+        <v>46155</v>
       </c>
       <c r="H77" s="2">
         <v>268.02</v>
@@ -4796,8 +5034,11 @@
       <c r="I77" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J77" s="5">
+        <v>92664028002519</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>699</v>
       </c>
@@ -4825,8 +5066,11 @@
       <c r="I78" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J78" s="5">
+        <v>5419552000233</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>3058</v>
       </c>
@@ -4854,8 +5098,11 @@
       <c r="I79" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J79" s="5">
+        <v>44194771000132</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>916</v>
       </c>
@@ -4874,8 +5121,8 @@
       <c r="F80" t="s">
         <v>14</v>
       </c>
-      <c r="G80" s="4" t="s">
-        <v>14</v>
+      <c r="G80" s="4">
+        <v>46155</v>
       </c>
       <c r="H80" s="2">
         <v>227.17</v>
@@ -4883,8 +5130,11 @@
       <c r="I80" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J80" s="5">
+        <v>92664028002780</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2027</v>
       </c>
@@ -4903,8 +5153,8 @@
       <c r="F81" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="4" t="s">
-        <v>14</v>
+      <c r="G81" s="4">
+        <v>46155</v>
       </c>
       <c r="H81" s="2">
         <v>1341.07</v>
@@ -4912,8 +5162,11 @@
       <c r="I81" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J81" s="5">
+        <v>7550459000108</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>593</v>
       </c>
@@ -4932,8 +5185,8 @@
       <c r="F82" t="s">
         <v>14</v>
       </c>
-      <c r="G82" s="4" t="s">
-        <v>14</v>
+      <c r="G82" s="4">
+        <v>46155</v>
       </c>
       <c r="H82" s="2">
         <v>646.14</v>
@@ -4941,8 +5194,11 @@
       <c r="I82" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J82" s="5">
+        <v>41570941000148</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2032</v>
       </c>
@@ -4961,8 +5217,8 @@
       <c r="F83" t="s">
         <v>14</v>
       </c>
-      <c r="G83" s="4" t="s">
-        <v>14</v>
+      <c r="G83" s="4">
+        <v>46155</v>
       </c>
       <c r="H83" s="2">
         <v>1062.9000000000001</v>
@@ -4970,8 +5226,11 @@
       <c r="I83" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J83" s="5">
+        <v>47102117000140</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1021</v>
       </c>
@@ -4990,8 +5249,8 @@
       <c r="F84" t="s">
         <v>14</v>
       </c>
-      <c r="G84" s="4" t="s">
-        <v>14</v>
+      <c r="G84" s="4">
+        <v>46155</v>
       </c>
       <c r="H84" s="2">
         <v>454.34</v>
@@ -4999,8 +5258,11 @@
       <c r="I84" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J84" s="5">
+        <v>14924194000126</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1099</v>
       </c>
@@ -5019,8 +5281,8 @@
       <c r="F85" t="s">
         <v>14</v>
       </c>
-      <c r="G85" s="4" t="s">
-        <v>14</v>
+      <c r="G85" s="4">
+        <v>46155</v>
       </c>
       <c r="H85" s="2">
         <v>1072.8599999999999</v>
@@ -5028,8 +5290,11 @@
       <c r="I85" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J85" s="5">
+        <v>52277238000162</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>3089</v>
       </c>
@@ -5057,8 +5322,11 @@
       <c r="I86" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J86" s="5">
+        <v>3200802000133</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>750</v>
       </c>
@@ -5077,8 +5345,8 @@
       <c r="F87" t="s">
         <v>14</v>
       </c>
-      <c r="G87" s="4" t="s">
-        <v>14</v>
+      <c r="G87" s="4">
+        <v>46155</v>
       </c>
       <c r="H87" s="2">
         <v>92.7</v>
@@ -5086,8 +5354,11 @@
       <c r="I87" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J87" s="5">
+        <v>74263062000122</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>3058</v>
       </c>
@@ -5106,8 +5377,8 @@
       <c r="F88" t="s">
         <v>14</v>
       </c>
-      <c r="G88" s="4" t="s">
-        <v>14</v>
+      <c r="G88" s="4">
+        <v>46155</v>
       </c>
       <c r="H88" s="2">
         <v>1062.9000000000001</v>
@@ -5115,8 +5386,11 @@
       <c r="I88" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J88" s="5">
+        <v>60340928000147</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2027</v>
       </c>
@@ -5135,8 +5409,8 @@
       <c r="F89" t="s">
         <v>14</v>
       </c>
-      <c r="G89" s="4" t="s">
-        <v>14</v>
+      <c r="G89" s="4">
+        <v>46155</v>
       </c>
       <c r="H89" s="2">
         <v>749.12</v>
@@ -5144,8 +5418,11 @@
       <c r="I89" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J89" s="5">
+        <v>567027000160</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>737</v>
       </c>
@@ -5164,8 +5441,8 @@
       <c r="F90" t="s">
         <v>14</v>
       </c>
-      <c r="G90" s="4" t="s">
-        <v>14</v>
+      <c r="G90" s="4">
+        <v>46155</v>
       </c>
       <c r="H90" s="2">
         <v>840.6</v>
@@ -5173,8 +5450,11 @@
       <c r="I90" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J90" s="5">
+        <v>7161840000185</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>722</v>
       </c>
@@ -5193,8 +5473,8 @@
       <c r="F91" t="s">
         <v>14</v>
       </c>
-      <c r="G91" s="4" t="s">
-        <v>14</v>
+      <c r="G91" s="4">
+        <v>46155</v>
       </c>
       <c r="H91" s="2">
         <v>1932.44</v>
@@ -5202,8 +5482,11 @@
       <c r="I91" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J91" s="5">
+        <v>2890979000146</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1021</v>
       </c>
@@ -5231,8 +5514,11 @@
       <c r="I92" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J92" s="5">
+        <v>7394278000130</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>308</v>
       </c>
@@ -5260,8 +5546,11 @@
       <c r="I93" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J93" s="5">
+        <v>56723091000148</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>308</v>
       </c>
@@ -5289,8 +5578,11 @@
       <c r="I94" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J94" s="5">
+        <v>56723091000148</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>380</v>
       </c>
@@ -5309,8 +5601,8 @@
       <c r="F95" t="s">
         <v>14</v>
       </c>
-      <c r="G95" s="4" t="s">
-        <v>14</v>
+      <c r="G95" s="4">
+        <v>46155</v>
       </c>
       <c r="H95" s="2">
         <v>1148.1099999999999</v>
@@ -5318,8 +5610,11 @@
       <c r="I95" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J95" s="5">
+        <v>871342000187</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2081</v>
       </c>
@@ -5347,8 +5642,11 @@
       <c r="I96" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J96" s="5">
+        <v>43283811003922</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2081</v>
       </c>
@@ -5376,8 +5674,11 @@
       <c r="I97" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J97" s="5">
+        <v>43283811003922</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2081</v>
       </c>
@@ -5405,8 +5706,11 @@
       <c r="I98" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J98" s="5">
+        <v>43283811003922</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2081</v>
       </c>
@@ -5434,8 +5738,11 @@
       <c r="I99" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J99" s="5">
+        <v>43283811003922</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2081</v>
       </c>
@@ -5463,8 +5770,11 @@
       <c r="I100" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J100" s="5">
+        <v>43283811003922</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>147</v>
       </c>
@@ -5492,8 +5802,11 @@
       <c r="I101" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J101" s="5">
+        <v>7521323000170</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>694</v>
       </c>
@@ -5521,8 +5834,11 @@
       <c r="I102" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J102" s="5">
+        <v>43631191000100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>943</v>
       </c>
@@ -5550,8 +5866,11 @@
       <c r="I103" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J103" s="5">
+        <v>58681719000115</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>916</v>
       </c>
@@ -5579,8 +5898,11 @@
       <c r="I104" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J104" s="5">
+        <v>76639285003192</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>918</v>
       </c>
@@ -5608,8 +5930,11 @@
       <c r="I105" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J105" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>918</v>
       </c>
@@ -5637,8 +5962,11 @@
       <c r="I106" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J106" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>918</v>
       </c>
@@ -5666,8 +5994,11 @@
       <c r="I107" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J107" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>918</v>
       </c>
@@ -5695,8 +6026,11 @@
       <c r="I108" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J108" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>60</v>
       </c>
@@ -5724,8 +6058,11 @@
       <c r="I109" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J109" s="5">
+        <v>1675208000173</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>60</v>
       </c>
@@ -5753,8 +6090,11 @@
       <c r="I110" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J110" s="5">
+        <v>1675208000173</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>60</v>
       </c>
@@ -5782,8 +6122,11 @@
       <c r="I111" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J111" s="5">
+        <v>1279711000100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>60</v>
       </c>
@@ -5811,8 +6154,11 @@
       <c r="I112" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J112" s="5">
+        <v>1279711000100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>60</v>
       </c>
@@ -5840,8 +6186,11 @@
       <c r="I113" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J113" s="5">
+        <v>1279711000100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>60</v>
       </c>
@@ -5869,8 +6218,11 @@
       <c r="I114" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J114" s="5">
+        <v>1279711000100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>979</v>
       </c>
@@ -5898,8 +6250,11 @@
       <c r="I115" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J115" s="5">
+        <v>64372760000102</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>614</v>
       </c>
@@ -5918,8 +6273,8 @@
       <c r="F116" t="s">
         <v>14</v>
       </c>
-      <c r="G116" s="4" t="s">
-        <v>14</v>
+      <c r="G116" s="4">
+        <v>46155</v>
       </c>
       <c r="H116" s="2">
         <v>844.75</v>
@@ -5927,8 +6282,11 @@
       <c r="I116" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J116" s="5">
+        <v>4358835000179</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>918</v>
       </c>
@@ -5956,8 +6314,11 @@
       <c r="I117" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J117" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>918</v>
       </c>
@@ -5985,8 +6346,11 @@
       <c r="I118" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J118" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>918</v>
       </c>
@@ -6014,8 +6378,11 @@
       <c r="I119" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J119" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>829</v>
       </c>
@@ -6034,8 +6401,8 @@
       <c r="F120" t="s">
         <v>14</v>
       </c>
-      <c r="G120" s="4" t="s">
-        <v>14</v>
+      <c r="G120" s="4">
+        <v>46155</v>
       </c>
       <c r="H120" s="2">
         <v>827.49</v>
@@ -6043,8 +6410,11 @@
       <c r="I120" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J120" s="5">
+        <v>39952724000170</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>918</v>
       </c>
@@ -6072,8 +6442,11 @@
       <c r="I121" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J121" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>918</v>
       </c>
@@ -6101,8 +6474,11 @@
       <c r="I122" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J122" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>918</v>
       </c>
@@ -6130,8 +6506,11 @@
       <c r="I123" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J123" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>614</v>
       </c>
@@ -6159,8 +6538,11 @@
       <c r="I124" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J124" s="5">
+        <v>37460888000155</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>375</v>
       </c>
@@ -6188,8 +6570,11 @@
       <c r="I125" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J125" s="5">
+        <v>41329776000137</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>918</v>
       </c>
@@ -6217,8 +6602,11 @@
       <c r="I126" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J126" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>918</v>
       </c>
@@ -6246,8 +6634,11 @@
       <c r="I127" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J127" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>979</v>
       </c>
@@ -6275,8 +6666,11 @@
       <c r="I128" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J128" s="5">
+        <v>25055125000140</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>632</v>
       </c>
@@ -6304,8 +6698,11 @@
       <c r="I129" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J129" s="5">
+        <v>11081954000192</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>3085</v>
       </c>
@@ -6333,8 +6730,11 @@
       <c r="I130" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J130" s="5">
+        <v>14396540000140</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>1019</v>
       </c>
@@ -6362,8 +6762,11 @@
       <c r="I131" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J131" s="5">
+        <v>10889989000190</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>1019</v>
       </c>
@@ -6391,8 +6794,11 @@
       <c r="I132" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J132" s="5">
+        <v>10889989000190</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>979</v>
       </c>
@@ -6420,8 +6826,11 @@
       <c r="I133" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J133" s="5">
+        <v>12385207000100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>749</v>
       </c>
@@ -6449,8 +6858,11 @@
       <c r="I134" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J134" s="5">
+        <v>107079000154</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>257</v>
       </c>
@@ -6478,8 +6890,11 @@
       <c r="I135" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J135" s="5">
+        <v>89637490017030</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>703</v>
       </c>
@@ -6507,8 +6922,11 @@
       <c r="I136" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J136" s="5">
+        <v>39542023000163</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>614</v>
       </c>
@@ -6536,8 +6954,11 @@
       <c r="I137" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J137" s="5">
+        <v>5746774000180</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2027</v>
       </c>
@@ -6565,8 +6986,11 @@
       <c r="I138" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J138" s="5">
+        <v>47398315000100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>699</v>
       </c>
@@ -6594,8 +7018,11 @@
       <c r="I139" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J139" s="5">
+        <v>39711325000118</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>90</v>
       </c>
@@ -6623,8 +7050,11 @@
       <c r="I140" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J140" s="5">
+        <v>35977579000121</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>3075</v>
       </c>
@@ -6652,8 +7082,11 @@
       <c r="I141" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J141" s="5">
+        <v>3107202000397</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>836</v>
       </c>
@@ -6672,8 +7105,8 @@
       <c r="F142" t="s">
         <v>14</v>
       </c>
-      <c r="G142" s="4" t="s">
-        <v>14</v>
+      <c r="G142" s="4">
+        <v>46155</v>
       </c>
       <c r="H142" s="2">
         <v>1639.89</v>
@@ -6681,8 +7114,11 @@
       <c r="I142" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J142" s="5">
+        <v>288671000108</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>836</v>
       </c>
@@ -6701,8 +7137,8 @@
       <c r="F143" t="s">
         <v>14</v>
       </c>
-      <c r="G143" s="4" t="s">
-        <v>14</v>
+      <c r="G143" s="4">
+        <v>46155</v>
       </c>
       <c r="H143" s="2">
         <v>294.2</v>
@@ -6710,8 +7146,11 @@
       <c r="I143" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J143" s="5">
+        <v>48957013000260</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2091</v>
       </c>
@@ -6739,8 +7178,11 @@
       <c r="I144" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J144" s="5">
+        <v>35239343000198</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2081</v>
       </c>
@@ -6768,8 +7210,11 @@
       <c r="I145" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J145" s="5">
+        <v>43283811003922</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>933</v>
       </c>
@@ -6797,8 +7242,11 @@
       <c r="I146" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J146" s="5">
+        <v>11886530000103</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>294</v>
       </c>
@@ -6817,8 +7265,8 @@
       <c r="F147" t="s">
         <v>14</v>
       </c>
-      <c r="G147" s="4" t="s">
-        <v>14</v>
+      <c r="G147" s="4">
+        <v>46155</v>
       </c>
       <c r="H147" s="2">
         <v>2674.64</v>
@@ -6826,8 +7274,11 @@
       <c r="I147" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J147" s="5">
+        <v>1713958000354</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>3060</v>
       </c>
@@ -6855,8 +7306,11 @@
       <c r="I148" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J148" s="5">
+        <v>50336098000120</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>257</v>
       </c>
@@ -6884,8 +7338,11 @@
       <c r="I149" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J149" s="5">
+        <v>28238084000115</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2073</v>
       </c>
@@ -6913,8 +7370,11 @@
       <c r="I150" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J150" s="5">
+        <v>96243852000189</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>703</v>
       </c>
@@ -6942,8 +7402,11 @@
       <c r="I151" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J151" s="5">
+        <v>8747307000839</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>703</v>
       </c>
@@ -6962,8 +7425,8 @@
       <c r="F152" t="s">
         <v>14</v>
       </c>
-      <c r="G152" s="4" t="s">
-        <v>14</v>
+      <c r="G152" s="4">
+        <v>46155</v>
       </c>
       <c r="H152" s="2">
         <v>1223.49</v>
@@ -6971,8 +7434,11 @@
       <c r="I152" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J152" s="5">
+        <v>11284739000199</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>3069</v>
       </c>
@@ -7000,8 +7466,11 @@
       <c r="I153" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J153" s="5">
+        <v>43100861000154</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>62</v>
       </c>
@@ -7021,7 +7490,7 @@
         <v>29</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H154" s="2">
         <v>1962.77</v>
@@ -7029,8 +7498,11 @@
       <c r="I154" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J154" s="5">
+        <v>60403110000630</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>293</v>
       </c>
@@ -7058,8 +7530,11 @@
       <c r="I155" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J155" s="5">
+        <v>49701707000114</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>3092</v>
       </c>
@@ -7079,7 +7554,7 @@
         <v>29</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H156" s="2">
         <v>5499.11</v>
@@ -7087,8 +7562,11 @@
       <c r="I156" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J156" s="5">
+        <v>8244165000110</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>1021</v>
       </c>
@@ -7108,7 +7586,7 @@
         <v>29</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H157" s="2">
         <v>49841.98</v>
@@ -7116,8 +7594,11 @@
       <c r="I157" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J157" s="5">
+        <v>77044618000340</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1019</v>
       </c>
@@ -7145,8 +7626,11 @@
       <c r="I158" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J158" s="5">
+        <v>10889989000190</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>1019</v>
       </c>
@@ -7174,8 +7658,11 @@
       <c r="I159" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J159" s="5">
+        <v>10889989000190</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>294</v>
       </c>
@@ -7195,7 +7682,7 @@
         <v>29</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H160" s="2">
         <v>22147.42</v>
@@ -7203,8 +7690,11 @@
       <c r="I160" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J160" s="5">
+        <v>21020430000307</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>377</v>
       </c>
@@ -7224,7 +7714,7 @@
         <v>29</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H161" s="2">
         <v>740.64</v>
@@ -7232,8 +7722,11 @@
       <c r="I161" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J161" s="5">
+        <v>13003958000188</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>90</v>
       </c>
@@ -7253,7 +7746,7 @@
         <v>29</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H162" s="2">
         <v>2491.98</v>
@@ -7261,8 +7754,11 @@
       <c r="I162" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J162" s="5">
+        <v>61726410000109</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>880</v>
       </c>
@@ -7282,7 +7778,7 @@
         <v>29</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H163" s="2">
         <v>3854.76</v>
@@ -7290,8 +7786,11 @@
       <c r="I163" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J163" s="5">
+        <v>4905356000125</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2073</v>
       </c>
@@ -7319,8 +7818,11 @@
       <c r="I164" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J164" s="5">
+        <v>52369082000140</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>699</v>
       </c>
@@ -7348,8 +7850,11 @@
       <c r="I165" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J165" s="5">
+        <v>38780193000113</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>773</v>
       </c>
@@ -7377,8 +7882,11 @@
       <c r="I166" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J166" s="5">
+        <v>3790896000148</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>773</v>
       </c>
@@ -7406,8 +7914,11 @@
       <c r="I167" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J167" s="5">
+        <v>3790896001039</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>773</v>
       </c>
@@ -7435,8 +7946,11 @@
       <c r="I168" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J168" s="5">
+        <v>3790896001110</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>773</v>
       </c>
@@ -7464,8 +7978,11 @@
       <c r="I169" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J169" s="5">
+        <v>3790896000229</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2038</v>
       </c>
@@ -7493,8 +8010,11 @@
       <c r="I170" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J170" s="5">
+        <v>41392231000175</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>614</v>
       </c>
@@ -7514,7 +8034,7 @@
         <v>29</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H171" s="2">
         <v>4850.1099999999997</v>
@@ -7522,8 +8042,11 @@
       <c r="I171" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J171" s="5">
+        <v>2972891000173</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>773</v>
       </c>
@@ -7543,7 +8066,7 @@
         <v>29</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H172" s="2">
         <v>5767.51</v>
@@ -7551,8 +8074,11 @@
       <c r="I172" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J172" s="5">
+        <v>3790896000300</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>979</v>
       </c>
@@ -7580,8 +8106,11 @@
       <c r="I173" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J173" s="5">
+        <v>3445212000170</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>773</v>
       </c>
@@ -7601,7 +8130,7 @@
         <v>29</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H174" s="2">
         <v>29335.43</v>
@@ -7609,8 +8138,11 @@
       <c r="I174" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J174" s="5">
+        <v>13338773000477</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>722</v>
       </c>
@@ -7638,8 +8170,11 @@
       <c r="I175" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J175" s="5">
+        <v>16691059000103</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>614</v>
       </c>
@@ -7667,8 +8202,11 @@
       <c r="I176" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J176" s="5">
+        <v>7176055000104</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1807</v>
       </c>
@@ -7696,8 +8234,11 @@
       <c r="I177" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J177" s="5">
+        <v>72704299000176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2072</v>
       </c>
@@ -7716,8 +8257,8 @@
       <c r="F178" t="s">
         <v>14</v>
       </c>
-      <c r="G178" s="4" t="s">
-        <v>14</v>
+      <c r="G178" s="4">
+        <v>46155</v>
       </c>
       <c r="H178" s="2">
         <v>475.96</v>
@@ -7725,8 +8266,11 @@
       <c r="I178" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J178" s="5">
+        <v>45345377000110</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>589</v>
       </c>
@@ -7754,8 +8298,11 @@
       <c r="I179" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J179" s="5">
+        <v>27849935000101</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2032</v>
       </c>
@@ -7783,8 +8330,11 @@
       <c r="I180" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J180" s="5">
+        <v>8693986000134</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>1027</v>
       </c>
@@ -7812,8 +8362,11 @@
       <c r="I181" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J181" s="5">
+        <v>43973913000105</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>723</v>
       </c>
@@ -7841,8 +8394,11 @@
       <c r="I182" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J182" s="5">
+        <v>43214055000107</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>90</v>
       </c>
@@ -7870,8 +8426,11 @@
       <c r="I183" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J183" s="5">
+        <v>12710369000177</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>699</v>
       </c>
@@ -7891,7 +8450,7 @@
         <v>29</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H184" s="2">
         <v>6002.64</v>
@@ -7899,8 +8458,11 @@
       <c r="I184" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J184" s="5">
+        <v>59246090000148</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>723</v>
       </c>
@@ -7920,7 +8482,7 @@
         <v>29</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H185" s="2">
         <v>6262.57</v>
@@ -7928,8 +8490,11 @@
       <c r="I185" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J185" s="5">
+        <v>43214055001693</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>723</v>
       </c>
@@ -7957,8 +8522,11 @@
       <c r="I186" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J186" s="5">
+        <v>43214055004013</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>723</v>
       </c>
@@ -7978,7 +8546,7 @@
         <v>29</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H187" s="2">
         <v>8534.49</v>
@@ -7986,8 +8554,11 @@
       <c r="I187" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J187" s="5">
+        <v>43214055001774</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>90</v>
       </c>
@@ -8015,8 +8586,11 @@
       <c r="I188" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J188" s="5">
+        <v>47820541000120</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>694</v>
       </c>
@@ -8044,8 +8618,11 @@
       <c r="I189" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J189" s="5">
+        <v>71527618000152</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>118</v>
       </c>
@@ -8073,8 +8650,11 @@
       <c r="I190" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J190" s="5">
+        <v>54116134000100</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>62</v>
       </c>
@@ -8102,8 +8682,11 @@
       <c r="I191" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J191" s="5">
+        <v>1438784001330</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>614</v>
       </c>
@@ -8123,7 +8706,7 @@
         <v>29</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H192" s="2">
         <v>29749.62</v>
@@ -8131,8 +8714,11 @@
       <c r="I192" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J192" s="5">
+        <v>37509833000192</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>3078</v>
       </c>
@@ -8160,8 +8746,11 @@
       <c r="I193" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J193" s="5">
+        <v>44367514000660</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>380</v>
       </c>
@@ -8189,8 +8778,11 @@
       <c r="I194" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J194" s="5">
+        <v>67128785000153</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>3078</v>
       </c>
@@ -8218,8 +8810,11 @@
       <c r="I195" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J195" s="5">
+        <v>44367514000589</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1027</v>
       </c>
@@ -8247,8 +8842,11 @@
       <c r="I196" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J196" s="5">
+        <v>26264272000192</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>3078</v>
       </c>
@@ -8276,8 +8874,11 @@
       <c r="I197" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J197" s="5">
+        <v>44367514000317</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>3078</v>
       </c>
@@ -8305,8 +8906,11 @@
       <c r="I198" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J198" s="5">
+        <v>44367514000236</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>3078</v>
       </c>
@@ -8334,8 +8938,11 @@
       <c r="I199" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J199" s="5">
+        <v>44367514000155</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>90</v>
       </c>
@@ -8363,8 +8970,11 @@
       <c r="I200" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J200" s="5">
+        <v>3353021000189</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>773</v>
       </c>
@@ -8384,7 +8994,7 @@
         <v>29</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H201" s="2">
         <v>6074.99</v>
@@ -8392,8 +9002,11 @@
       <c r="I201" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J201" s="5">
+        <v>13338773000396</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>90</v>
       </c>
@@ -8421,8 +9034,11 @@
       <c r="I202" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J202" s="5">
+        <v>2957750000343</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>62</v>
       </c>
@@ -8442,7 +9058,7 @@
         <v>29</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H203" s="2">
         <v>241.12</v>
@@ -8450,8 +9066,11 @@
       <c r="I203" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J203" s="5">
+        <v>23476033001260</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2099</v>
       </c>
@@ -8479,8 +9098,11 @@
       <c r="I204" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J204" s="5">
+        <v>15375991002027</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>62</v>
       </c>
@@ -8500,7 +9122,7 @@
         <v>29</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H205" s="2">
         <v>241.12</v>
@@ -8508,8 +9130,11 @@
       <c r="I205" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J205" s="5">
+        <v>23476033000370</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>574</v>
       </c>
@@ -8537,8 +9162,11 @@
       <c r="I206" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J206" s="5">
+        <v>7342785001100</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>62</v>
       </c>
@@ -8558,7 +9186,7 @@
         <v>29</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H207" s="2">
         <v>243.17</v>
@@ -8566,8 +9194,11 @@
       <c r="I207" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J207" s="5">
+        <v>23476033002151</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>62</v>
       </c>
@@ -8587,7 +9218,7 @@
         <v>29</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H208" s="2">
         <v>964.48</v>
@@ -8595,8 +9226,11 @@
       <c r="I208" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J208" s="5">
+        <v>23476033000299</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>281</v>
       </c>
@@ -8624,8 +9258,11 @@
       <c r="I209" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J209" s="5">
+        <v>26171645000938</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>706</v>
       </c>
@@ -8645,7 +9282,7 @@
         <v>29</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H210" s="2">
         <v>13812.5</v>
@@ -8653,8 +9290,11 @@
       <c r="I210" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J210" s="5">
+        <v>5300197000602</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>574</v>
       </c>
@@ -8682,8 +9322,11 @@
       <c r="I211" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J211" s="5">
+        <v>7342785000553</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>281</v>
       </c>
@@ -8711,8 +9354,11 @@
       <c r="I212" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J212" s="5">
+        <v>26171645001403</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>281</v>
       </c>
@@ -8731,8 +9377,8 @@
       <c r="F213" t="s">
         <v>14</v>
       </c>
-      <c r="G213" s="4" t="s">
-        <v>14</v>
+      <c r="G213" s="4">
+        <v>46155</v>
       </c>
       <c r="H213" s="2">
         <v>1846.27</v>
@@ -8740,8 +9386,11 @@
       <c r="I213" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J213" s="5">
+        <v>26171645000695</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>281</v>
       </c>
@@ -8760,8 +9409,8 @@
       <c r="F214" t="s">
         <v>14</v>
       </c>
-      <c r="G214" s="4" t="s">
-        <v>14</v>
+      <c r="G214" s="4">
+        <v>46155</v>
       </c>
       <c r="H214" s="2">
         <v>1635.9</v>
@@ -8769,8 +9418,11 @@
       <c r="I214" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J214" s="5">
+        <v>26171645002639</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>281</v>
       </c>
@@ -8789,8 +9441,8 @@
       <c r="F215" t="s">
         <v>14</v>
       </c>
-      <c r="G215" s="4" t="s">
-        <v>14</v>
+      <c r="G215" s="4">
+        <v>46155</v>
       </c>
       <c r="H215" s="2">
         <v>1609.21</v>
@@ -8798,8 +9450,11 @@
       <c r="I215" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J215" s="5">
+        <v>26171645001829</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>281</v>
       </c>
@@ -8827,8 +9482,11 @@
       <c r="I216" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J216" s="5">
+        <v>26171645002558</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>574</v>
       </c>
@@ -8856,8 +9514,11 @@
       <c r="I217" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J217" s="5">
+        <v>48288160000104</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>281</v>
       </c>
@@ -8885,8 +9546,11 @@
       <c r="I218" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J218" s="5">
+        <v>26171645000180</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>574</v>
       </c>
@@ -8914,8 +9578,11 @@
       <c r="I219" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J219" s="5">
+        <v>45141688000168</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>281</v>
       </c>
@@ -8943,8 +9610,11 @@
       <c r="I220" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J220" s="5">
+        <v>26171645000423</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>281</v>
       </c>
@@ -8972,8 +9642,11 @@
       <c r="I221" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J221" s="5">
+        <v>86440674000122</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>281</v>
       </c>
@@ -9001,8 +9674,11 @@
       <c r="I222" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J222" s="5">
+        <v>8094841000117</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>281</v>
       </c>
@@ -9030,8 +9706,11 @@
       <c r="I223" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J223" s="5">
+        <v>8094841000206</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>281</v>
       </c>
@@ -9059,8 +9738,11 @@
       <c r="I224" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J224" s="5">
+        <v>86440674000203</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>377</v>
       </c>
@@ -9088,8 +9770,11 @@
       <c r="I225" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J225" s="5">
+        <v>64663968000180</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>281</v>
       </c>
@@ -9117,8 +9802,11 @@
       <c r="I226" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J226" s="5">
+        <v>86440674000394</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>867</v>
       </c>
@@ -9146,8 +9834,11 @@
       <c r="I227" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J227" s="5">
+        <v>11170837000103</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>281</v>
       </c>
@@ -9175,8 +9866,11 @@
       <c r="I228" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J228" s="5">
+        <v>28347577000193</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>281</v>
       </c>
@@ -9204,8 +9898,11 @@
       <c r="I229" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J229" s="5">
+        <v>86440674000556</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>614</v>
       </c>
@@ -9233,8 +9930,11 @@
       <c r="I230" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J230" s="5">
+        <v>27587789000185</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>3069</v>
       </c>
@@ -9262,8 +9962,11 @@
       <c r="I231" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J231" s="5">
+        <v>47319598000140</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>90</v>
       </c>
@@ -9291,8 +9994,11 @@
       <c r="I232" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J232" s="5">
+        <v>5384001000109</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2090</v>
       </c>
@@ -9320,8 +10026,11 @@
       <c r="I233" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J233" s="5">
+        <v>37475663000172</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>377</v>
       </c>
@@ -9349,8 +10058,11 @@
       <c r="I234" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J234" s="5">
+        <v>42534309000101</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1807</v>
       </c>
@@ -9378,8 +10090,11 @@
       <c r="I235" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J235" s="5">
+        <v>42846494000250</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>90</v>
       </c>
@@ -9407,8 +10122,11 @@
       <c r="I236" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J236" s="5">
+        <v>65338706000103</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>703</v>
       </c>
@@ -9436,8 +10154,11 @@
       <c r="I237" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J237" s="5">
+        <v>1147821000118</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>574</v>
       </c>
@@ -9465,8 +10186,11 @@
       <c r="I238" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J238" s="5">
+        <v>62757095000140</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>377</v>
       </c>
@@ -9494,8 +10218,11 @@
       <c r="I239" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J239" s="5">
+        <v>39450996000172</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>62</v>
       </c>
@@ -9523,8 +10250,11 @@
       <c r="I240" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J240" s="5">
+        <v>1438784000601</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>62</v>
       </c>
@@ -9552,8 +10282,11 @@
       <c r="I241" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J241" s="5">
+        <v>1438784003899</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>62</v>
       </c>
@@ -9581,8 +10314,11 @@
       <c r="I242" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J242" s="5">
+        <v>1438784001926</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>62</v>
       </c>
@@ -9610,8 +10346,11 @@
       <c r="I243" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J243" s="5">
+        <v>1438784007371</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>62</v>
       </c>
@@ -9639,8 +10378,11 @@
       <c r="I244" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J244" s="5">
+        <v>1438784002493</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>62</v>
       </c>
@@ -9668,8 +10410,11 @@
       <c r="I245" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J245" s="5">
+        <v>1438784000369</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>62</v>
       </c>
@@ -9697,8 +10442,11 @@
       <c r="I246" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J246" s="5">
+        <v>1438784004780</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>62</v>
       </c>
@@ -9726,8 +10474,11 @@
       <c r="I247" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J247" s="5">
+        <v>1438784001179</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>62</v>
       </c>
@@ -9755,8 +10506,11 @@
       <c r="I248" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J248" s="5">
+        <v>1438784005166</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>62</v>
       </c>
@@ -9784,8 +10538,11 @@
       <c r="I249" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J249" s="5">
+        <v>1438784004607</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>62</v>
       </c>
@@ -9813,8 +10570,11 @@
       <c r="I250" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J250" s="5">
+        <v>1438784001098</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>62</v>
       </c>
@@ -9842,8 +10602,11 @@
       <c r="I251" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J251" s="5">
+        <v>1438784000601</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>62</v>
       </c>
@@ -9871,8 +10634,11 @@
       <c r="I252" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J252" s="5">
+        <v>1438784003112</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>62</v>
       </c>
@@ -9900,8 +10666,11 @@
       <c r="I253" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J253" s="5">
+        <v>1438784000288</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>62</v>
       </c>
@@ -9929,8 +10698,11 @@
       <c r="I254" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J254" s="5">
+        <v>1438784000440</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>62</v>
       </c>
@@ -9958,8 +10730,11 @@
       <c r="I255" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J255" s="5">
+        <v>1438784002060</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>62</v>
       </c>
@@ -9987,8 +10762,11 @@
       <c r="I256" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J256" s="5">
+        <v>1438784006308</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>62</v>
       </c>
@@ -10016,8 +10794,11 @@
       <c r="I257" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J257" s="5">
+        <v>1438784002655</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>62</v>
       </c>
@@ -10045,8 +10826,11 @@
       <c r="I258" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J258" s="5">
+        <v>1438784001764</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>62</v>
       </c>
@@ -10074,8 +10858,11 @@
       <c r="I259" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J259" s="5">
+        <v>1438784001330</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>62</v>
       </c>
@@ -10103,8 +10890,11 @@
       <c r="I260" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J260" s="5">
+        <v>1438784005085</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>62</v>
       </c>
@@ -10132,8 +10922,11 @@
       <c r="I261" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J261" s="5">
+        <v>1438784001250</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>62</v>
       </c>
@@ -10161,8 +10954,11 @@
       <c r="I262" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J262" s="5">
+        <v>1438784004356</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>62</v>
       </c>
@@ -10190,8 +10986,11 @@
       <c r="I263" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J263" s="5">
+        <v>1438784000792</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>62</v>
       </c>
@@ -10219,8 +11018,11 @@
       <c r="I264" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J264" s="5">
+        <v>1438784001683</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>62</v>
       </c>
@@ -10248,8 +11050,11 @@
       <c r="I265" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J265" s="5">
+        <v>1438784005590</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>62</v>
       </c>
@@ -10277,8 +11082,11 @@
       <c r="I266" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J266" s="5">
+        <v>1438784002140</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>62</v>
       </c>
@@ -10306,8 +11114,11 @@
       <c r="I267" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J267" s="5">
+        <v>1438784006723</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>62</v>
       </c>
@@ -10335,8 +11146,11 @@
       <c r="I268" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J268" s="5">
+        <v>1438784004941</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>62</v>
       </c>
@@ -10364,8 +11178,11 @@
       <c r="I269" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J269" s="5">
+        <v>1438784006219</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>62</v>
       </c>
@@ -10393,8 +11210,11 @@
       <c r="I270" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J270" s="5">
+        <v>1438784003627</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>62</v>
       </c>
@@ -10422,8 +11242,11 @@
       <c r="I271" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J271" s="5">
+        <v>1438784000520</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>62</v>
       </c>
@@ -10451,8 +11274,11 @@
       <c r="I272" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J272" s="5">
+        <v>1438784003970</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>62</v>
       </c>
@@ -10480,8 +11306,11 @@
       <c r="I273" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J273" s="5">
+        <v>1438784008424</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>62</v>
       </c>
@@ -10509,8 +11338,11 @@
       <c r="I274" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J274" s="5">
+        <v>1438784006804</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>62</v>
       </c>
@@ -10538,8 +11370,11 @@
       <c r="I275" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J275" s="5">
+        <v>1438784002302</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>918</v>
       </c>
@@ -10567,8 +11402,11 @@
       <c r="I276" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J276" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>918</v>
       </c>
@@ -10596,8 +11434,11 @@
       <c r="I277" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J277" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>918</v>
       </c>
@@ -10625,8 +11466,11 @@
       <c r="I278" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J278" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>918</v>
       </c>
@@ -10654,8 +11498,11 @@
       <c r="I279" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J279" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>918</v>
       </c>
@@ -10683,8 +11530,11 @@
       <c r="I280" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J280" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>918</v>
       </c>
@@ -10712,8 +11562,11 @@
       <c r="I281" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J281" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>918</v>
       </c>
@@ -10741,8 +11594,11 @@
       <c r="I282" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J282" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>918</v>
       </c>
@@ -10762,7 +11618,7 @@
         <v>29</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H283" s="2">
         <v>2126.3200000000002</v>
@@ -10770,8 +11626,11 @@
       <c r="I283" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J283" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>918</v>
       </c>
@@ -10799,8 +11658,11 @@
       <c r="I284" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J284" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>918</v>
       </c>
@@ -10828,8 +11690,11 @@
       <c r="I285" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J285" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>918</v>
       </c>
@@ -10857,8 +11722,11 @@
       <c r="I286" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J286" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>593</v>
       </c>
@@ -10886,8 +11754,11 @@
       <c r="I287" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J287" s="5">
+        <v>43879279000138</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>90</v>
       </c>
@@ -10915,8 +11786,11 @@
       <c r="I288" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J288" s="5">
+        <v>60887748000180</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>3078</v>
       </c>
@@ -10944,8 +11818,11 @@
       <c r="I289" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J289" s="5">
+        <v>5873001000164</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>3077</v>
       </c>
@@ -10973,8 +11850,11 @@
       <c r="I290" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J290" s="5">
+        <v>4657295000124</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>1019</v>
       </c>
@@ -11002,8 +11882,11 @@
       <c r="I291" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J291" s="5">
+        <v>16837482000179</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>996</v>
       </c>
@@ -11031,8 +11914,11 @@
       <c r="I292" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J292" s="5">
+        <v>87870952001469</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>933</v>
       </c>
@@ -11060,8 +11946,11 @@
       <c r="I293" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J293" s="5">
+        <v>25245341000158</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>90</v>
       </c>
@@ -11089,8 +11978,11 @@
       <c r="I294" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J294" s="5">
+        <v>52931599000180</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>60</v>
       </c>
@@ -11118,8 +12010,11 @@
       <c r="I295" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J295" s="5">
+        <v>1675208000173</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>60</v>
       </c>
@@ -11147,8 +12042,11 @@
       <c r="I296" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J296" s="5">
+        <v>1675208000173</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>60</v>
       </c>
@@ -11176,8 +12074,11 @@
       <c r="I297" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J297" s="5">
+        <v>1675208000173</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>2032</v>
       </c>
@@ -11205,8 +12106,11 @@
       <c r="I298" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J298" s="5">
+        <v>9521591000117</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>3092</v>
       </c>
@@ -11226,7 +12130,7 @@
         <v>29</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H299" s="2">
         <v>23667.82</v>
@@ -11234,8 +12138,11 @@
       <c r="I299" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J299" s="5">
+        <v>13501187000159</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>851</v>
       </c>
@@ -11263,8 +12170,11 @@
       <c r="I300" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J300" s="5">
+        <v>62906744000127</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>951</v>
       </c>
@@ -11284,7 +12194,7 @@
         <v>29</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H301" s="2">
         <v>9337.44</v>
@@ -11292,8 +12202,11 @@
       <c r="I301" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J301" s="5">
+        <v>33041706000150</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>118</v>
       </c>
@@ -11321,8 +12234,11 @@
       <c r="I302" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J302" s="5">
+        <v>11210407000160</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>874</v>
       </c>
@@ -11350,8 +12266,11 @@
       <c r="I303" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J303" s="5">
+        <v>53410742000151</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>653</v>
       </c>
@@ -11379,8 +12298,11 @@
       <c r="I304" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J304" s="5">
+        <v>9529479000122</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>669</v>
       </c>
@@ -11408,8 +12330,11 @@
       <c r="I305" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J305" s="5">
+        <v>21094851000200</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>380</v>
       </c>
@@ -11429,7 +12354,7 @@
         <v>29</v>
       </c>
       <c r="G306" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H306" s="2">
         <v>3790.28</v>
@@ -11437,8 +12362,11 @@
       <c r="I306" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J306" s="5">
+        <v>74538802000196</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>90</v>
       </c>
@@ -11458,7 +12386,7 @@
         <v>29</v>
       </c>
       <c r="G307" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H307" s="2">
         <v>3190.31</v>
@@ -11466,8 +12394,11 @@
       <c r="I307" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J307" s="5">
+        <v>60216861000133</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>703</v>
       </c>
@@ -11487,7 +12418,7 @@
         <v>29</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H308" s="2">
         <v>3852.11</v>
@@ -11495,8 +12426,11 @@
       <c r="I308" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J308" s="5">
+        <v>27881915001262</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>703</v>
       </c>
@@ -11516,7 +12450,7 @@
         <v>29</v>
       </c>
       <c r="G309" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H309" s="2">
         <v>5264.69</v>
@@ -11524,8 +12458,11 @@
       <c r="I309" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J309" s="5">
+        <v>53182854000100</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>979</v>
       </c>
@@ -11545,7 +12482,7 @@
         <v>29</v>
       </c>
       <c r="G310" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H310" s="2">
         <v>2713.26</v>
@@ -11553,8 +12490,11 @@
       <c r="I310" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J310" s="5">
+        <v>56724412000129</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>1807</v>
       </c>
@@ -11582,8 +12522,11 @@
       <c r="I311" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J311" s="5">
+        <v>42846494000250</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>874</v>
       </c>
@@ -11603,7 +12546,7 @@
         <v>29</v>
       </c>
       <c r="G312" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H312" s="2">
         <v>3233.91</v>
@@ -11611,8 +12554,11 @@
       <c r="I312" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J312" s="5">
+        <v>43523209000142</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>2073</v>
       </c>
@@ -11640,8 +12586,11 @@
       <c r="I313" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J313" s="5">
+        <v>60094849000101</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>90</v>
       </c>
@@ -11661,7 +12610,7 @@
         <v>29</v>
       </c>
       <c r="G314" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H314" s="2">
         <v>2568.4299999999998</v>
@@ -11669,8 +12618,11 @@
       <c r="I314" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J314" s="5">
+        <v>48524219000116</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>811</v>
       </c>
@@ -11698,8 +12650,11 @@
       <c r="I315" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J315" s="5">
+        <v>65327347000270</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>811</v>
       </c>
@@ -11727,8 +12682,11 @@
       <c r="I316" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J316" s="5">
+        <v>46970948000170</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>281</v>
       </c>
@@ -11756,8 +12714,11 @@
       <c r="I317" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J317" s="5">
+        <v>26390229000840</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>1027</v>
       </c>
@@ -11785,8 +12746,11 @@
       <c r="I318" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J318" s="5">
+        <v>96395298000155</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>90</v>
       </c>
@@ -11814,8 +12778,11 @@
       <c r="I319" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J319" s="5">
+        <v>10268687000102</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>3</v>
       </c>
@@ -11843,8 +12810,11 @@
       <c r="I320" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J320" s="5">
+        <v>5068650000273</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>3093</v>
       </c>
@@ -11872,8 +12842,11 @@
       <c r="I321" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J321" s="5">
+        <v>2301164000184</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>811</v>
       </c>
@@ -11901,8 +12874,11 @@
       <c r="I322" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J322" s="5">
+        <v>49508288000107</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>3049</v>
       </c>
@@ -11930,8 +12906,11 @@
       <c r="I323" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J323" s="5">
+        <v>5544928000150</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>377</v>
       </c>
@@ -11951,7 +12930,7 @@
         <v>29</v>
       </c>
       <c r="G324" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H324" s="2">
         <v>5365.63</v>
@@ -11959,8 +12938,11 @@
       <c r="I324" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J324" s="5">
+        <v>11178887000200</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>836</v>
       </c>
@@ -11988,8 +12970,11 @@
       <c r="I325" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J325" s="5">
+        <v>58169680000151</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>951</v>
       </c>
@@ -12017,8 +13002,11 @@
       <c r="I326" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J326" s="5">
+        <v>27027089000136</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>664</v>
       </c>
@@ -12038,7 +13026,7 @@
         <v>29</v>
       </c>
       <c r="G327" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H327" s="2">
         <v>8320.16</v>
@@ -12046,8 +13034,11 @@
       <c r="I327" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J327" s="5">
+        <v>10471596000161</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>967</v>
       </c>
@@ -12075,8 +13066,11 @@
       <c r="I328" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J328" s="5">
+        <v>28766370000153</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>711</v>
       </c>
@@ -12104,8 +13098,11 @@
       <c r="I329" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J329" s="5">
+        <v>99004569999963</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>3060</v>
       </c>
@@ -12125,7 +13122,7 @@
         <v>29</v>
       </c>
       <c r="G330" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H330" s="2">
         <v>2645.5</v>
@@ -12133,8 +13130,11 @@
       <c r="I330" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J330" s="5">
+        <v>18357787000109</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>951</v>
       </c>
@@ -12162,8 +13162,11 @@
       <c r="I331" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J331" s="5">
+        <v>44213965000138</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>60</v>
       </c>
@@ -12191,8 +13194,11 @@
       <c r="I332" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J332" s="5">
+        <v>60208692000190</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>642</v>
       </c>
@@ -12220,8 +13226,11 @@
       <c r="I333" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J333" s="5">
+        <v>1154956000534</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>699</v>
       </c>
@@ -12241,7 +13250,7 @@
         <v>29</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H334" s="2">
         <v>2941.96</v>
@@ -12249,8 +13258,11 @@
       <c r="I334" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J334" s="5">
+        <v>28264920000136</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>1097</v>
       </c>
@@ -12278,8 +13290,11 @@
       <c r="I335" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J335" s="5">
+        <v>23842015000100</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>918</v>
       </c>
@@ -12307,8 +13322,11 @@
       <c r="I336" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J336" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>293</v>
       </c>
@@ -12336,8 +13354,11 @@
       <c r="I337" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J337" s="5">
+        <v>49701707000114</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>918</v>
       </c>
@@ -12365,8 +13386,11 @@
       <c r="I338" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J338" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>2051</v>
       </c>
@@ -12394,8 +13418,11 @@
       <c r="I339" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J339" s="5">
+        <v>2635833000235</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>918</v>
       </c>
@@ -12423,8 +13450,11 @@
       <c r="I340" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J340" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>918</v>
       </c>
@@ -12452,8 +13482,11 @@
       <c r="I341" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J341" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>918</v>
       </c>
@@ -12481,8 +13514,11 @@
       <c r="I342" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J342" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>918</v>
       </c>
@@ -12510,8 +13546,11 @@
       <c r="I343" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J343" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>906</v>
       </c>
@@ -12539,8 +13578,11 @@
       <c r="I344" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J344" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>918</v>
       </c>
@@ -12568,8 +13610,11 @@
       <c r="I345" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J345" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>906</v>
       </c>
@@ -12597,8 +13642,11 @@
       <c r="I346" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J346" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>918</v>
       </c>
@@ -12626,8 +13674,11 @@
       <c r="I347" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J347" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>918</v>
       </c>
@@ -12655,8 +13706,11 @@
       <c r="I348" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J348" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>918</v>
       </c>
@@ -12684,8 +13738,11 @@
       <c r="I349" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J349" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>918</v>
       </c>
@@ -12713,8 +13770,11 @@
       <c r="I350" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J350" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>918</v>
       </c>
@@ -12742,8 +13802,11 @@
       <c r="I351" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J351" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>918</v>
       </c>
@@ -12771,8 +13834,11 @@
       <c r="I352" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J352" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>918</v>
       </c>
@@ -12800,8 +13866,11 @@
       <c r="I353" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J353" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>983</v>
       </c>
@@ -12829,8 +13898,11 @@
       <c r="I354" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J354" s="5">
+        <v>8102538000380</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>699</v>
       </c>
@@ -12858,8 +13930,11 @@
       <c r="I355" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J355" s="5">
+        <v>96659255000130</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>983</v>
       </c>
@@ -12887,8 +13962,11 @@
       <c r="I356" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J356" s="5">
+        <v>8102538000119</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>2064</v>
       </c>
@@ -12916,8 +13994,11 @@
       <c r="I357" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J357" s="5">
+        <v>2578288000101</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>2027</v>
       </c>
@@ -12945,8 +14026,11 @@
       <c r="I358" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J358" s="5">
+        <v>1612658000117</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>1807</v>
       </c>
@@ -12974,8 +14058,11 @@
       <c r="I359" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J359" s="5">
+        <v>3802720000169</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>703</v>
       </c>
@@ -13003,8 +14090,11 @@
       <c r="I360" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J360" s="5">
+        <v>197999000453</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>699</v>
       </c>
@@ -13032,8 +14122,11 @@
       <c r="I361" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J361" s="5">
+        <v>44390313000179</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>703</v>
       </c>
@@ -13061,8 +14154,11 @@
       <c r="I362" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J362" s="5">
+        <v>27881915000703</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>60</v>
       </c>
@@ -13090,8 +14186,11 @@
       <c r="I363" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J363" s="5">
+        <v>1279711000100</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>60</v>
       </c>
@@ -13119,8 +14218,11 @@
       <c r="I364" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J364" s="5">
+        <v>1279711000100</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>60</v>
       </c>
@@ -13148,8 +14250,11 @@
       <c r="I365" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J365" s="5">
+        <v>1279711000100</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>60</v>
       </c>
@@ -13177,8 +14282,11 @@
       <c r="I366" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J366" s="5">
+        <v>1279711000100</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>1021</v>
       </c>
@@ -13206,8 +14314,11 @@
       <c r="I367" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J367" s="5">
+        <v>77044618000340</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>2090</v>
       </c>
@@ -13235,8 +14346,11 @@
       <c r="I368" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J368" s="5">
+        <v>9211173001529</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>699</v>
       </c>
@@ -13264,8 +14378,11 @@
       <c r="I369" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J369" s="5">
+        <v>45165024000139</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>3078</v>
       </c>
@@ -13293,8 +14410,11 @@
       <c r="I370" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J370" s="5">
+        <v>27633733000110</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>3078</v>
       </c>
@@ -13314,7 +14434,7 @@
         <v>29</v>
       </c>
       <c r="G371" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H371" s="2">
         <v>6554.12</v>
@@ -13322,8 +14442,11 @@
       <c r="I371" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J371" s="5">
+        <v>44367514000317</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>90</v>
       </c>
@@ -13351,8 +14474,11 @@
       <c r="I372" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J372" s="5">
+        <v>47844113000137</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>2090</v>
       </c>
@@ -13380,8 +14506,11 @@
       <c r="I373" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J373" s="5">
+        <v>9211173001367</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>874</v>
       </c>
@@ -13409,8 +14538,11 @@
       <c r="I374" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J374" s="5">
+        <v>52867298000135</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>2041</v>
       </c>
@@ -13438,8 +14570,11 @@
       <c r="I375" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J375" s="5">
+        <v>3095221000340</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>3035</v>
       </c>
@@ -13467,8 +14602,11 @@
       <c r="I376" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J376" s="5">
+        <v>50300713000149</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>3</v>
       </c>
@@ -13496,8 +14634,11 @@
       <c r="I377" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J377" s="5">
+        <v>12940035000190</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>3089</v>
       </c>
@@ -13517,7 +14658,7 @@
         <v>29</v>
       </c>
       <c r="G378" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H378" s="2">
         <v>3613.7</v>
@@ -13525,8 +14666,11 @@
       <c r="I378" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J378" s="5">
+        <v>40962865000153</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>614</v>
       </c>
@@ -13554,8 +14698,11 @@
       <c r="I379" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J379" s="5">
+        <v>1390442000154</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>723</v>
       </c>
@@ -13575,7 +14722,7 @@
         <v>29</v>
       </c>
       <c r="G380" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H380" s="2">
         <v>9964.7900000000009</v>
@@ -13583,8 +14730,11 @@
       <c r="I380" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J380" s="5">
+        <v>31055405000150</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>723</v>
       </c>
@@ -13612,8 +14762,11 @@
       <c r="I381" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J381" s="5">
+        <v>22342369000115</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>669</v>
       </c>
@@ -13641,8 +14794,11 @@
       <c r="I382" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J382" s="5">
+        <v>22742494000112</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>418</v>
       </c>
@@ -13670,8 +14826,11 @@
       <c r="I383" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J383" s="5">
+        <v>73291536000187</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>1021</v>
       </c>
@@ -13691,7 +14850,7 @@
         <v>29</v>
       </c>
       <c r="G384" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H384" s="2">
         <v>15922.98</v>
@@ -13699,8 +14858,11 @@
       <c r="I384" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J384" s="5">
+        <v>7394278000130</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>3078</v>
       </c>
@@ -13728,8 +14890,11 @@
       <c r="I385" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J385" s="5">
+        <v>1906310000132</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>380</v>
       </c>
@@ -13749,7 +14914,7 @@
         <v>29</v>
       </c>
       <c r="G386" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H386" s="2">
         <v>7405.9</v>
@@ -13757,8 +14922,11 @@
       <c r="I386" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J386" s="5">
+        <v>871342000187</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>625</v>
       </c>
@@ -13786,8 +14954,11 @@
       <c r="I387" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J387" s="5">
+        <v>58426110000108</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>29</v>
       </c>
@@ -13815,8 +14986,11 @@
       <c r="I388" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J388" s="5">
+        <v>39590059000201</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>3072</v>
       </c>
@@ -13844,8 +15018,11 @@
       <c r="I389" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J389" s="5">
+        <v>4889603000147</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>829</v>
       </c>
@@ -13873,8 +15050,11 @@
       <c r="I390" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J390" s="5">
+        <v>34738149000194</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>380</v>
       </c>
@@ -13902,8 +15082,11 @@
       <c r="I391" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J391" s="5">
+        <v>9434194000108</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>293</v>
       </c>
@@ -13931,8 +15114,11 @@
       <c r="I392" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J392" s="5">
+        <v>64633909000160</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>62</v>
       </c>
@@ -13952,7 +15138,7 @@
         <v>29</v>
       </c>
       <c r="G393" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H393" s="2">
         <v>1680.07</v>
@@ -13960,8 +15146,11 @@
       <c r="I393" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J393" s="5">
+        <v>3439316003350</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>380</v>
       </c>
@@ -13989,8 +15178,11 @@
       <c r="I394" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J394" s="5">
+        <v>37837253001287</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>703</v>
       </c>
@@ -14018,8 +15210,11 @@
       <c r="I395" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J395" s="5">
+        <v>68186816000195</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>3060</v>
       </c>
@@ -14047,8 +15242,11 @@
       <c r="I396" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J396" s="5">
+        <v>57690523000124</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>281</v>
       </c>
@@ -14076,8 +15274,11 @@
       <c r="I397" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J397" s="5">
+        <v>50053140000104</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>593</v>
       </c>
@@ -14097,7 +15298,7 @@
         <v>29</v>
       </c>
       <c r="G398" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H398" s="2">
         <v>4390.71</v>
@@ -14105,8 +15306,11 @@
       <c r="I398" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J398" s="5">
+        <v>60166085000104</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>593</v>
       </c>
@@ -14126,7 +15330,7 @@
         <v>29</v>
       </c>
       <c r="G399" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H399" s="2">
         <v>4738.8500000000004</v>
@@ -14134,8 +15338,11 @@
       <c r="I399" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J399" s="5">
+        <v>25276994000285</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>593</v>
       </c>
@@ -14155,7 +15362,7 @@
         <v>29</v>
       </c>
       <c r="G400" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H400" s="2">
         <v>4138.33</v>
@@ -14163,8 +15370,11 @@
       <c r="I400" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J400" s="5">
+        <v>32250010000252</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>3055</v>
       </c>
@@ -14192,8 +15402,11 @@
       <c r="I401" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J401" s="5">
+        <v>74579566000156</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>3037</v>
       </c>
@@ -14221,8 +15434,11 @@
       <c r="I402" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J402" s="5">
+        <v>18074761000153</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>375</v>
       </c>
@@ -14250,8 +15466,11 @@
       <c r="I403" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J403" s="5">
+        <v>79653614000475</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>294</v>
       </c>
@@ -14279,8 +15498,11 @@
       <c r="I404" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J404" s="5">
+        <v>50433993000163</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>711</v>
       </c>
@@ -14308,8 +15530,11 @@
       <c r="I405" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J405" s="5">
+        <v>99004325999980</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>377</v>
       </c>
@@ -14337,8 +15562,11 @@
       <c r="I406" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J406" s="5">
+        <v>15370558000136</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>377</v>
       </c>
@@ -14366,8 +15594,11 @@
       <c r="I407" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J407" s="5">
+        <v>4035891000504</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>409</v>
       </c>
@@ -14395,8 +15626,11 @@
       <c r="I408" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J408" s="5">
+        <v>273134000186</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>614</v>
       </c>
@@ -14424,8 +15658,11 @@
       <c r="I409" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J409" s="5">
+        <v>1339514000139</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>377</v>
       </c>
@@ -14453,8 +15690,11 @@
       <c r="I410" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J410" s="5">
+        <v>4035891000768</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>874</v>
       </c>
@@ -14482,8 +15722,11 @@
       <c r="I411" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J411" s="5">
+        <v>20957428000134</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>675</v>
       </c>
@@ -14511,8 +15754,11 @@
       <c r="I412" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J412" s="5">
+        <v>32809568000144</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>773</v>
       </c>
@@ -14540,8 +15786,11 @@
       <c r="I413" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J413" s="5">
+        <v>50652704000117</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>2078</v>
       </c>
@@ -14569,8 +15818,11 @@
       <c r="I414" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J414" s="5">
+        <v>50153949000108</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>918</v>
       </c>
@@ -14598,8 +15850,11 @@
       <c r="I415" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J415" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>918</v>
       </c>
@@ -14627,8 +15882,11 @@
       <c r="I416" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J416" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>918</v>
       </c>
@@ -14656,8 +15914,11 @@
       <c r="I417" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J417" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>918</v>
       </c>
@@ -14685,8 +15946,11 @@
       <c r="I418" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J418" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>918</v>
       </c>
@@ -14714,8 +15978,11 @@
       <c r="I419" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J419" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>918</v>
       </c>
@@ -14743,8 +16010,11 @@
       <c r="I420" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J420" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>918</v>
       </c>
@@ -14772,8 +16042,11 @@
       <c r="I421" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J421" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>918</v>
       </c>
@@ -14801,8 +16074,11 @@
       <c r="I422" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J422" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>918</v>
       </c>
@@ -14830,8 +16106,11 @@
       <c r="I423" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J423" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>918</v>
       </c>
@@ -14859,8 +16138,11 @@
       <c r="I424" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J424" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>918</v>
       </c>
@@ -14888,8 +16170,11 @@
       <c r="I425" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J425" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>918</v>
       </c>
@@ -14917,8 +16202,11 @@
       <c r="I426" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J426" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>918</v>
       </c>
@@ -14946,8 +16234,11 @@
       <c r="I427" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J427" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>918</v>
       </c>
@@ -14975,8 +16266,11 @@
       <c r="I428" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J428" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>918</v>
       </c>
@@ -15004,8 +16298,11 @@
       <c r="I429" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J429" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>918</v>
       </c>
@@ -15033,8 +16330,11 @@
       <c r="I430" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J430" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>918</v>
       </c>
@@ -15062,8 +16362,11 @@
       <c r="I431" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J431" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>918</v>
       </c>
@@ -15091,8 +16394,11 @@
       <c r="I432" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J432" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>918</v>
       </c>
@@ -15120,8 +16426,11 @@
       <c r="I433" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J433" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>703</v>
       </c>
@@ -15149,8 +16458,11 @@
       <c r="I434" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J434" s="5">
+        <v>10974454000117</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>918</v>
       </c>
@@ -15178,8 +16490,11 @@
       <c r="I435" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J435" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>918</v>
       </c>
@@ -15207,8 +16522,11 @@
       <c r="I436" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J436" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>918</v>
       </c>
@@ -15236,8 +16554,11 @@
       <c r="I437" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J437" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>918</v>
       </c>
@@ -15265,8 +16586,11 @@
       <c r="I438" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J438" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>918</v>
       </c>
@@ -15294,8 +16618,11 @@
       <c r="I439" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J439" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>918</v>
       </c>
@@ -15323,8 +16650,11 @@
       <c r="I440" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J440" s="5">
+        <v>3840986006803</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>593</v>
       </c>
@@ -15352,8 +16682,11 @@
       <c r="I441" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J441" s="5">
+        <v>26408752000341</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>699</v>
       </c>
@@ -15381,8 +16714,11 @@
       <c r="I442" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J442" s="5">
+        <v>59246090000148</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>699</v>
       </c>
@@ -15410,8 +16746,11 @@
       <c r="I443" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J443" s="5">
+        <v>12147692000184</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>1027</v>
       </c>
@@ -15439,8 +16778,11 @@
       <c r="I444" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J444" s="5">
+        <v>15216145000100</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>3049</v>
       </c>
@@ -15468,8 +16810,11 @@
       <c r="I445" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J445" s="5">
+        <v>41218790000163</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>2084</v>
       </c>
@@ -15497,8 +16842,11 @@
       <c r="I446" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J446" s="5">
+        <v>51900904000104</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>699</v>
       </c>
@@ -15526,8 +16874,11 @@
       <c r="I447" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J447" s="5">
+        <v>49160722000100</v>
+      </c>
+    </row>
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>3060</v>
       </c>
@@ -15555,8 +16906,11 @@
       <c r="I448" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J448" s="5">
+        <v>57782534000134</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>380</v>
       </c>
@@ -15576,7 +16930,7 @@
         <v>29</v>
       </c>
       <c r="G449" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H449" s="2">
         <v>3772.25</v>
@@ -15584,8 +16938,11 @@
       <c r="I449" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J449" s="5">
+        <v>30611092000107</v>
+      </c>
+    </row>
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>3034</v>
       </c>
@@ -15613,8 +16970,11 @@
       <c r="I450" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J450" s="5">
+        <v>46957732000175</v>
+      </c>
+    </row>
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>1019</v>
       </c>
@@ -15633,8 +16993,8 @@
       <c r="F451" t="s">
         <v>14</v>
       </c>
-      <c r="G451" s="4" t="s">
-        <v>14</v>
+      <c r="G451" s="4">
+        <v>46155</v>
       </c>
       <c r="H451" s="2">
         <v>1761.08</v>
@@ -15642,8 +17002,11 @@
       <c r="I451" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J451" s="5">
+        <v>52068294000197</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>3060</v>
       </c>
@@ -15671,8 +17034,11 @@
       <c r="I452" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J452" s="5">
+        <v>58333224000103</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>380</v>
       </c>
@@ -15700,8 +17066,11 @@
       <c r="I453" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J453" s="5">
+        <v>27966435000141</v>
+      </c>
+    </row>
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>380</v>
       </c>
@@ -15721,7 +17090,7 @@
         <v>29</v>
       </c>
       <c r="G454" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H454" s="2">
         <v>4391.21</v>
@@ -15729,8 +17098,11 @@
       <c r="I454" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J454" s="5">
+        <v>45243835000100</v>
+      </c>
+    </row>
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>906</v>
       </c>
@@ -15758,8 +17130,11 @@
       <c r="I455" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J455" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>906</v>
       </c>
@@ -15787,8 +17162,11 @@
       <c r="I456" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J456" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>906</v>
       </c>
@@ -15816,8 +17194,11 @@
       <c r="I457" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J457" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>3060</v>
       </c>
@@ -15845,8 +17226,11 @@
       <c r="I458" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J458" s="5">
+        <v>67501445000126</v>
+      </c>
+    </row>
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>906</v>
       </c>
@@ -15874,8 +17258,11 @@
       <c r="I459" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J459" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>380</v>
       </c>
@@ -15903,8 +17290,11 @@
       <c r="I460" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J460" s="5">
+        <v>7028289000104</v>
+      </c>
+    </row>
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>906</v>
       </c>
@@ -15932,8 +17322,11 @@
       <c r="I461" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J461" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>380</v>
       </c>
@@ -15961,8 +17354,11 @@
       <c r="I462" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J462" s="5">
+        <v>5551036000187</v>
+      </c>
+    </row>
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>906</v>
       </c>
@@ -15990,8 +17386,11 @@
       <c r="I463" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J463" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>906</v>
       </c>
@@ -16019,8 +17418,11 @@
       <c r="I464" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J464" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>906</v>
       </c>
@@ -16048,8 +17450,11 @@
       <c r="I465" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J465" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>703</v>
       </c>
@@ -16077,8 +17482,11 @@
       <c r="I466" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J466" s="5">
+        <v>55173075000166</v>
+      </c>
+    </row>
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>951</v>
       </c>
@@ -16098,7 +17506,7 @@
         <v>29</v>
       </c>
       <c r="G467" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H467" s="2">
         <v>4015.43</v>
@@ -16106,8 +17514,11 @@
       <c r="I467" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J467" s="5">
+        <v>43681585000165</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>90</v>
       </c>
@@ -16135,8 +17546,11 @@
       <c r="I468" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J468" s="5">
+        <v>64575277000125</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>293</v>
       </c>
@@ -16164,8 +17578,11 @@
       <c r="I469" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J469" s="5">
+        <v>9059552000140</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>2088</v>
       </c>
@@ -16193,8 +17610,11 @@
       <c r="I470" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J470" s="5">
+        <v>17148366000105</v>
+      </c>
+    </row>
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>811</v>
       </c>
@@ -16222,8 +17642,11 @@
       <c r="I471" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J471" s="5">
+        <v>25161436000193</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>580</v>
       </c>
@@ -16251,8 +17674,11 @@
       <c r="I472" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J472" s="5">
+        <v>12613955000101</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>381</v>
       </c>
@@ -16271,8 +17697,8 @@
       <c r="F473" t="s">
         <v>14</v>
       </c>
-      <c r="G473" s="4" t="s">
-        <v>14</v>
+      <c r="G473" s="4">
+        <v>46155</v>
       </c>
       <c r="H473" s="2">
         <v>467.99</v>
@@ -16280,8 +17706,11 @@
       <c r="I473" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J473" s="5">
+        <v>9246333000170</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>2072</v>
       </c>
@@ -16309,8 +17738,11 @@
       <c r="I474" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J474" s="5">
+        <v>51164974000141</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>377</v>
       </c>
@@ -16330,7 +17762,7 @@
         <v>29</v>
       </c>
       <c r="G475" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H475" s="2">
         <v>5927.05</v>
@@ -16338,8 +17770,11 @@
       <c r="I475" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J475" s="5">
+        <v>45223335000107</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>675</v>
       </c>
@@ -16367,8 +17802,11 @@
       <c r="I476" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J476" s="5">
+        <v>9076777000104</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>381</v>
       </c>
@@ -16396,8 +17834,11 @@
       <c r="I477" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J477" s="5">
+        <v>4403408001307</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>653</v>
       </c>
@@ -16417,7 +17858,7 @@
         <v>29</v>
       </c>
       <c r="G478" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H478" s="2">
         <v>2722.41</v>
@@ -16425,8 +17866,11 @@
       <c r="I478" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J478" s="5">
+        <v>11065132000118</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>293</v>
       </c>
@@ -16454,8 +17898,11 @@
       <c r="I479" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J479" s="5">
+        <v>81721375000142</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>811</v>
       </c>
@@ -16483,8 +17930,11 @@
       <c r="I480" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J480" s="5">
+        <v>51241336000187</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>3034</v>
       </c>
@@ -16512,8 +17962,11 @@
       <c r="I481" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J481" s="5">
+        <v>33279777000196</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>983</v>
       </c>
@@ -16533,7 +17986,7 @@
         <v>29</v>
       </c>
       <c r="G482" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H482" s="2">
         <v>3337.35</v>
@@ -16541,8 +17994,11 @@
       <c r="I482" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J482" s="5">
+        <v>50798737000170</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>375</v>
       </c>
@@ -16570,8 +18026,11 @@
       <c r="I483" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J483" s="5">
+        <v>83054437000135</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>3060</v>
       </c>
@@ -16599,8 +18058,11 @@
       <c r="I484" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J484" s="5">
+        <v>40059848000100</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>614</v>
       </c>
@@ -16620,7 +18082,7 @@
         <v>29</v>
       </c>
       <c r="G485" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H485" s="2">
         <v>22025.43</v>
@@ -16628,8 +18090,11 @@
       <c r="I485" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J485" s="5">
+        <v>33319958000603</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>2047</v>
       </c>
@@ -16657,8 +18122,11 @@
       <c r="I486" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J486" s="5">
+        <v>2087258000100</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>3029</v>
       </c>
@@ -16686,8 +18154,11 @@
       <c r="I487" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J487" s="5">
+        <v>87360483000113</v>
+      </c>
+    </row>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>3037</v>
       </c>
@@ -16715,8 +18186,11 @@
       <c r="I488" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J488" s="5">
+        <v>27047066000193</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>3037</v>
       </c>
@@ -16736,7 +18210,7 @@
         <v>29</v>
       </c>
       <c r="G489" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H489" s="2">
         <v>12079.91</v>
@@ -16744,8 +18218,11 @@
       <c r="I489" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J489" s="5">
+        <v>41750673000146</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>134</v>
       </c>
@@ -16773,8 +18250,11 @@
       <c r="I490" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J490" s="5">
+        <v>7755964000199</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>134</v>
       </c>
@@ -16802,8 +18282,11 @@
       <c r="I491" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J491" s="5">
+        <v>5060677000139</v>
+      </c>
+    </row>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>2024</v>
       </c>
@@ -16831,8 +18314,11 @@
       <c r="I492" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J492" s="5">
+        <v>5121792000176</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>614</v>
       </c>
@@ -16860,8 +18346,11 @@
       <c r="I493" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J493" s="5">
+        <v>1906247000134</v>
+      </c>
+    </row>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>377</v>
       </c>
@@ -16889,8 +18378,11 @@
       <c r="I494" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J494" s="5">
+        <v>7064410000145</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>2024</v>
       </c>
@@ -16918,8 +18410,11 @@
       <c r="I495" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J495" s="5">
+        <v>51117339000103</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>699</v>
       </c>
@@ -16947,8 +18442,11 @@
       <c r="I496" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J496" s="5">
+        <v>3325708000100</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>699</v>
       </c>
@@ -16976,8 +18474,11 @@
       <c r="I497" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J497" s="5">
+        <v>8017398000180</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>699</v>
       </c>
@@ -17005,8 +18506,11 @@
       <c r="I498" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J498" s="5">
+        <v>49907888000130</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>639</v>
       </c>
@@ -17034,8 +18538,11 @@
       <c r="I499" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J499" s="5">
+        <v>8740783000151</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>2047</v>
       </c>
@@ -17063,8 +18570,11 @@
       <c r="I500" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J500" s="5">
+        <v>13453086000150</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>2047</v>
       </c>
@@ -17092,8 +18602,11 @@
       <c r="I501" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J501" s="5">
+        <v>60644543000173</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>2024</v>
       </c>
@@ -17121,8 +18634,11 @@
       <c r="I502" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J502" s="5">
+        <v>52287497000174</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>2090</v>
       </c>
@@ -17150,8 +18666,11 @@
       <c r="I503" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J503" s="5">
+        <v>63526588000212</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>1807</v>
       </c>
@@ -17179,8 +18698,11 @@
       <c r="I504" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J504" s="5">
+        <v>42846494000250</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>90</v>
       </c>
@@ -17200,7 +18722,7 @@
         <v>29</v>
       </c>
       <c r="G505" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H505" s="2">
         <v>11244.32</v>
@@ -17208,8 +18730,11 @@
       <c r="I505" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J505" s="5">
+        <v>8938757000132</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>737</v>
       </c>
@@ -17237,8 +18762,11 @@
       <c r="I506" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J506" s="5">
+        <v>6881434000124</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>3</v>
       </c>
@@ -17266,8 +18794,11 @@
       <c r="I507" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J507" s="5">
+        <v>11520001000183</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>3</v>
       </c>
@@ -17295,8 +18826,11 @@
       <c r="I508" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J508" s="5">
+        <v>47254461002289</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>653</v>
       </c>
@@ -17324,8 +18858,11 @@
       <c r="I509" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J509" s="5">
+        <v>1694377000150</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>90</v>
       </c>
@@ -17353,8 +18890,11 @@
       <c r="I510" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J510" s="5">
+        <v>10616729000140</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>90</v>
       </c>
@@ -17382,8 +18922,11 @@
       <c r="I511" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J511" s="5">
+        <v>14337486000162</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>90</v>
       </c>
@@ -17411,8 +18954,11 @@
       <c r="I512" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J512" s="5">
+        <v>54237185000181</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>3</v>
       </c>
@@ -17440,8 +18986,11 @@
       <c r="I513" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J513" s="5">
+        <v>46958948000155</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>843</v>
       </c>
@@ -17469,8 +19018,11 @@
       <c r="I514" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J514" s="5">
+        <v>4415471000111</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>843</v>
       </c>
@@ -17498,8 +19050,11 @@
       <c r="I515" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J515" s="5">
+        <v>2163789000127</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>843</v>
       </c>
@@ -17527,8 +19082,11 @@
       <c r="I516" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J516" s="5">
+        <v>36078911000340</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>1019</v>
       </c>
@@ -17556,8 +19114,11 @@
       <c r="I517" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J517" s="5">
+        <v>43326504000109</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>1016</v>
       </c>
@@ -17585,8 +19146,11 @@
       <c r="I518" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J518" s="5">
+        <v>60872306000674</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>3045</v>
       </c>
@@ -17614,8 +19178,11 @@
       <c r="I519" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J519" s="5">
+        <v>12622959000148</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>2088</v>
       </c>
@@ -17643,8 +19210,11 @@
       <c r="I520" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J520" s="5">
+        <v>40078887000155</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>951</v>
       </c>
@@ -17664,7 +19234,7 @@
         <v>29</v>
       </c>
       <c r="G521" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H521" s="2">
         <v>6026.77</v>
@@ -17672,8 +19242,11 @@
       <c r="I521" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J521" s="5">
+        <v>38779955000161</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>43</v>
       </c>
@@ -17701,8 +19274,11 @@
       <c r="I522" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J522" s="5">
+        <v>21559508000102</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>429</v>
       </c>
@@ -17730,8 +19306,11 @@
       <c r="I523" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J523" s="5">
+        <v>80142730000166</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>898</v>
       </c>
@@ -17759,8 +19338,11 @@
       <c r="I524" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J524" s="5">
+        <v>89086144000540</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>3035</v>
       </c>
@@ -17788,8 +19370,11 @@
       <c r="I525" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J525" s="5">
+        <v>15207513000145</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>645</v>
       </c>
@@ -17817,8 +19402,11 @@
       <c r="I526" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J526" s="5">
+        <v>21339965001074</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>3086</v>
       </c>
@@ -17846,8 +19434,11 @@
       <c r="I527" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J527" s="5">
+        <v>10236929000178</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>906</v>
       </c>
@@ -17875,8 +19466,11 @@
       <c r="I528" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J528" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>906</v>
       </c>
@@ -17904,8 +19498,11 @@
       <c r="I529" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J529" s="5">
+        <v>2907841000536</v>
+      </c>
+    </row>
+    <row r="530" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>922</v>
       </c>
@@ -17933,8 +19530,11 @@
       <c r="I530" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J530" s="5">
+        <v>77772473000131</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>906</v>
       </c>
@@ -17962,8 +19562,11 @@
       <c r="I531" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J531" s="5">
+        <v>2907841000102</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>284</v>
       </c>
@@ -17991,8 +19594,11 @@
       <c r="I532" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J532" s="5">
+        <v>91707968000108</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>916</v>
       </c>
@@ -18020,8 +19626,11 @@
       <c r="I533" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J533" s="5">
+        <v>76639285003354</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>694</v>
       </c>
@@ -18049,8 +19658,11 @@
       <c r="I534" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J534" s="5">
+        <v>13478113000300</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>593</v>
       </c>
@@ -18078,8 +19690,11 @@
       <c r="I535" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J535" s="5">
+        <v>50146538000187</v>
+      </c>
+    </row>
+    <row r="536" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>2041</v>
       </c>
@@ -18107,8 +19722,11 @@
       <c r="I536" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J536" s="5">
+        <v>54316733000169</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>614</v>
       </c>
@@ -18136,8 +19754,11 @@
       <c r="I537" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J537" s="5">
+        <v>51255215000194</v>
+      </c>
+    </row>
+    <row r="538" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>614</v>
       </c>
@@ -18165,8 +19786,11 @@
       <c r="I538" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J538" s="5">
+        <v>9134038000121</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>811</v>
       </c>
@@ -18194,8 +19818,11 @@
       <c r="I539" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J539" s="5">
+        <v>61418114000140</v>
+      </c>
+    </row>
+    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>293</v>
       </c>
@@ -18223,8 +19850,11 @@
       <c r="I540" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J540" s="5">
+        <v>8866382000142</v>
+      </c>
+    </row>
+    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>375</v>
       </c>
@@ -18252,8 +19882,11 @@
       <c r="I541" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J541" s="5">
+        <v>92791243000294</v>
+      </c>
+    </row>
+    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>90</v>
       </c>
@@ -18281,8 +19914,11 @@
       <c r="I542" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J542" s="5">
+        <v>38945763000188</v>
+      </c>
+    </row>
+    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>293</v>
       </c>
@@ -18310,8 +19946,11 @@
       <c r="I543" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J543" s="5">
+        <v>31642161000102</v>
+      </c>
+    </row>
+    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>294</v>
       </c>
@@ -18339,8 +19978,11 @@
       <c r="I544" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J544" s="5">
+        <v>37127025000160</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>645</v>
       </c>
@@ -18368,8 +20010,11 @@
       <c r="I545" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J545" s="5">
+        <v>86673704000140</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>778</v>
       </c>
@@ -18397,8 +20042,11 @@
       <c r="I546" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J546" s="5">
+        <v>2476827000100</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>2027</v>
       </c>
@@ -18426,8 +20074,11 @@
       <c r="I547" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J547" s="5">
+        <v>31819139000195</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>699</v>
       </c>
@@ -18455,8 +20106,11 @@
       <c r="I548" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J548" s="5">
+        <v>1795953000156</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>3037</v>
       </c>
@@ -18484,8 +20138,11 @@
       <c r="I549" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J549" s="5">
+        <v>49971376000132</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>293</v>
       </c>
@@ -18513,8 +20170,11 @@
       <c r="I550" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J550" s="5">
+        <v>1861489000400</v>
+      </c>
+    </row>
+    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>2051</v>
       </c>
@@ -18542,8 +20202,11 @@
       <c r="I551" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J551" s="5">
+        <v>24874539000138</v>
+      </c>
+    </row>
+    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>699</v>
       </c>
@@ -18571,8 +20234,11 @@
       <c r="I552" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J552" s="5">
+        <v>7083730000142</v>
+      </c>
+    </row>
+    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>703</v>
       </c>
@@ -18600,8 +20266,11 @@
       <c r="I553" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J553" s="5">
+        <v>46804861000123</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>2073</v>
       </c>
@@ -18629,8 +20298,11 @@
       <c r="I554" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J554" s="5">
+        <v>3087452000140</v>
+      </c>
+    </row>
+    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>979</v>
       </c>
@@ -18658,8 +20330,11 @@
       <c r="I555" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J555" s="5">
+        <v>42124836000148</v>
+      </c>
+    </row>
+    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>60</v>
       </c>
@@ -18687,8 +20362,11 @@
       <c r="I556" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J556" s="5">
+        <v>30166012000151</v>
+      </c>
+    </row>
+    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>293</v>
       </c>
@@ -18716,8 +20394,11 @@
       <c r="I557" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J557" s="5">
+        <v>97397178000150</v>
+      </c>
+    </row>
+    <row r="558" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>979</v>
       </c>
@@ -18745,8 +20426,11 @@
       <c r="I558" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J558" s="5">
+        <v>3445212000170</v>
+      </c>
+    </row>
+    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>3097</v>
       </c>
@@ -18774,8 +20458,11 @@
       <c r="I559" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J559" s="5">
+        <v>9430146000141</v>
+      </c>
+    </row>
+    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>377</v>
       </c>
@@ -18803,8 +20490,11 @@
       <c r="I560" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J560" s="5">
+        <v>24656431000179</v>
+      </c>
+    </row>
+    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>829</v>
       </c>
@@ -18832,8 +20522,11 @@
       <c r="I561" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J561" s="5">
+        <v>4776809000160</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>703</v>
       </c>
@@ -18861,8 +20554,11 @@
       <c r="I562" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J562" s="5">
+        <v>565813000129</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>60</v>
       </c>
@@ -18890,8 +20586,11 @@
       <c r="I563" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J563" s="5">
+        <v>1410577000134</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>569</v>
       </c>
@@ -18919,8 +20618,11 @@
       <c r="I564" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J564" s="5">
+        <v>1503399000196</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>829</v>
       </c>
@@ -18948,8 +20650,11 @@
       <c r="I565" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J565" s="5">
+        <v>38317611000130</v>
+      </c>
+    </row>
+    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>3057</v>
       </c>
@@ -18977,8 +20682,11 @@
       <c r="I566" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J566" s="5">
+        <v>8743836000198</v>
+      </c>
+    </row>
+    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>4005</v>
       </c>
@@ -19006,8 +20714,11 @@
       <c r="I567" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J567" s="5">
+        <v>83892182000775</v>
+      </c>
+    </row>
+    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>951</v>
       </c>
@@ -19035,8 +20746,11 @@
       <c r="I568" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J568" s="5">
+        <v>74469446000104</v>
+      </c>
+    </row>
+    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>377</v>
       </c>
@@ -19064,8 +20778,11 @@
       <c r="I569" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J569" s="5">
+        <v>7019715000135</v>
+      </c>
+    </row>
+    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>703</v>
       </c>
@@ -19093,8 +20810,11 @@
       <c r="I570" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J570" s="5">
+        <v>565813000986</v>
+      </c>
+    </row>
+    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>906</v>
       </c>
@@ -19122,8 +20842,11 @@
       <c r="I571" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J571" s="5">
+        <v>59941799000325</v>
+      </c>
+    </row>
+    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>906</v>
       </c>
@@ -19151,8 +20874,11 @@
       <c r="I572" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J572" s="5">
+        <v>10350401000125</v>
+      </c>
+    </row>
+    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>589</v>
       </c>
@@ -19180,8 +20906,11 @@
       <c r="I573" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J573" s="5">
+        <v>13229980000140</v>
+      </c>
+    </row>
+    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>3077</v>
       </c>
@@ -19209,8 +20938,11 @@
       <c r="I574" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J574" s="5">
+        <v>4657295000124</v>
+      </c>
+    </row>
+    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>2016</v>
       </c>
@@ -19238,8 +20970,11 @@
       <c r="I575" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J575" s="5">
+        <v>16865089000199</v>
+      </c>
+    </row>
+    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>381</v>
       </c>
@@ -19267,8 +21002,11 @@
       <c r="I576" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J576" s="5">
+        <v>11069316000318</v>
+      </c>
+    </row>
+    <row r="577" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>2016</v>
       </c>
@@ -19296,8 +21034,11 @@
       <c r="I577" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J577" s="5">
+        <v>16865089000199</v>
+      </c>
+    </row>
+    <row r="578" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>2016</v>
       </c>
@@ -19325,8 +21066,11 @@
       <c r="I578" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J578" s="5">
+        <v>16865089000199</v>
+      </c>
+    </row>
+    <row r="579" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>375</v>
       </c>
@@ -19354,8 +21098,11 @@
       <c r="I579" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J579" s="5">
+        <v>11308600000804</v>
+      </c>
+    </row>
+    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>2027</v>
       </c>
@@ -19383,8 +21130,11 @@
       <c r="I580" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J580" s="5">
+        <v>40609600000176</v>
+      </c>
+    </row>
+    <row r="581" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>3</v>
       </c>
@@ -19412,8 +21162,11 @@
       <c r="I581" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J581" s="5">
+        <v>50334614000340</v>
+      </c>
+    </row>
+    <row r="582" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>293</v>
       </c>
@@ -19441,8 +21194,11 @@
       <c r="I582" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J582" s="5">
+        <v>45118913000145</v>
+      </c>
+    </row>
+    <row r="583" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>936</v>
       </c>
@@ -19470,8 +21226,11 @@
       <c r="I583" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J583" s="5">
+        <v>10451376000176</v>
+      </c>
+    </row>
+    <row r="584" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>722</v>
       </c>
@@ -19491,7 +21250,7 @@
         <v>29</v>
       </c>
       <c r="G584" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H584" s="2">
         <v>3277.77</v>
@@ -19499,8 +21258,11 @@
       <c r="I584" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J584" s="5">
+        <v>11401855000140</v>
+      </c>
+    </row>
+    <row r="585" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>60</v>
       </c>
@@ -19528,8 +21290,11 @@
       <c r="I585" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J585" s="5">
+        <v>30166012000151</v>
+      </c>
+    </row>
+    <row r="586" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>118</v>
       </c>
@@ -19557,8 +21322,11 @@
       <c r="I586" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J586" s="5">
+        <v>5007317000173</v>
+      </c>
+    </row>
+    <row r="587" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>2024</v>
       </c>
@@ -19586,8 +21354,11 @@
       <c r="I587" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J587" s="5">
+        <v>29639711000192</v>
+      </c>
+    </row>
+    <row r="588" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>632</v>
       </c>
@@ -19615,8 +21386,11 @@
       <c r="I588" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J588" s="5">
+        <v>652150000180</v>
+      </c>
+    </row>
+    <row r="589" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>699</v>
       </c>
@@ -19644,8 +21418,11 @@
       <c r="I589" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J589" s="5">
+        <v>44624324000176</v>
+      </c>
+    </row>
+    <row r="590" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>2024</v>
       </c>
@@ -19673,8 +21450,11 @@
       <c r="I590" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J590" s="5">
+        <v>46783241000155</v>
+      </c>
+    </row>
+    <row r="591" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>951</v>
       </c>
@@ -19702,8 +21482,11 @@
       <c r="I591" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J591" s="5">
+        <v>17822780000158</v>
+      </c>
+    </row>
+    <row r="592" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>614</v>
       </c>
@@ -19731,8 +21514,11 @@
       <c r="I592" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J592" s="5">
+        <v>58918117000139</v>
+      </c>
+    </row>
+    <row r="593" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>614</v>
       </c>
@@ -19760,8 +21546,11 @@
       <c r="I593" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J593" s="5">
+        <v>30185147000164</v>
+      </c>
+    </row>
+    <row r="594" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>2041</v>
       </c>
@@ -19781,7 +21570,7 @@
         <v>29</v>
       </c>
       <c r="G594" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H594" s="2">
         <v>4593</v>
@@ -19789,8 +21578,11 @@
       <c r="I594" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J594" s="5">
+        <v>29809508000117</v>
+      </c>
+    </row>
+    <row r="595" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>670</v>
       </c>
@@ -19818,8 +21610,11 @@
       <c r="I595" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J595" s="5">
+        <v>18727192000106</v>
+      </c>
+    </row>
+    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>722</v>
       </c>
@@ -19847,8 +21642,11 @@
       <c r="I596" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J596" s="5">
+        <v>28301090000170</v>
+      </c>
+    </row>
+    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>418</v>
       </c>
@@ -19876,8 +21674,11 @@
       <c r="I597" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J597" s="5">
+        <v>7944839000127</v>
+      </c>
+    </row>
+    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>664</v>
       </c>
@@ -19905,8 +21706,11 @@
       <c r="I598" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J598" s="5">
+        <v>52822409000197</v>
+      </c>
+    </row>
+    <row r="599" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>1019</v>
       </c>
@@ -19934,8 +21738,11 @@
       <c r="I599" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J599" s="5">
+        <v>35353515000150</v>
+      </c>
+    </row>
+    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>722</v>
       </c>
@@ -19963,8 +21770,11 @@
       <c r="I600" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J600" s="5">
+        <v>8624088000124</v>
+      </c>
+    </row>
+    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>614</v>
       </c>
@@ -19984,7 +21794,7 @@
         <v>29</v>
       </c>
       <c r="G601" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H601" s="2">
         <v>4735.91</v>
@@ -19992,8 +21802,11 @@
       <c r="I601" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J601" s="5">
+        <v>26593095000198</v>
+      </c>
+    </row>
+    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>43</v>
       </c>
@@ -20021,8 +21834,11 @@
       <c r="I602" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J602" s="5">
+        <v>69196657000172</v>
+      </c>
+    </row>
+    <row r="603" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>293</v>
       </c>
@@ -20050,8 +21866,11 @@
       <c r="I603" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J603" s="5">
+        <v>21908856000130</v>
+      </c>
+    </row>
+    <row r="604" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>3029</v>
       </c>
@@ -20079,8 +21898,11 @@
       <c r="I604" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J604" s="5">
+        <v>442267528000013</v>
+      </c>
+    </row>
+    <row r="605" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>3</v>
       </c>
@@ -20108,8 +21930,11 @@
       <c r="I605" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J605" s="5">
+        <v>11520001000183</v>
+      </c>
+    </row>
+    <row r="606" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>407</v>
       </c>
@@ -20137,8 +21962,11 @@
       <c r="I606" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J606" s="5">
+        <v>1745592000133</v>
+      </c>
+    </row>
+    <row r="607" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>2091</v>
       </c>
@@ -20166,8 +21994,11 @@
       <c r="I607" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J607" s="5">
+        <v>9107815000149</v>
+      </c>
+    </row>
+    <row r="608" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>3</v>
       </c>
@@ -20195,8 +22026,11 @@
       <c r="I608" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J608" s="5">
+        <v>46958948000155</v>
+      </c>
+    </row>
+    <row r="609" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>3029</v>
       </c>
@@ -20224,8 +22058,11 @@
       <c r="I609" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J609" s="5">
+        <v>482822003000087</v>
+      </c>
+    </row>
+    <row r="610" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>3</v>
       </c>
@@ -20253,8 +22090,11 @@
       <c r="I610" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J610" s="5">
+        <v>45989050002044</v>
+      </c>
+    </row>
+    <row r="611" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>639</v>
       </c>
@@ -20282,8 +22122,11 @@
       <c r="I611" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J611" s="5">
+        <v>14807945000558</v>
+      </c>
+    </row>
+    <row r="612" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>773</v>
       </c>
@@ -20311,8 +22154,11 @@
       <c r="I612" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J612" s="5">
+        <v>13720869000152</v>
+      </c>
+    </row>
+    <row r="613" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>967</v>
       </c>
@@ -20340,8 +22186,11 @@
       <c r="I613" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J613" s="5">
+        <v>11905118000185</v>
+      </c>
+    </row>
+    <row r="614" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>2083</v>
       </c>
@@ -20369,8 +22218,11 @@
       <c r="I614" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J614" s="5">
+        <v>528808000146</v>
+      </c>
+    </row>
+    <row r="615" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>2078</v>
       </c>
@@ -20398,8 +22250,11 @@
       <c r="I615" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J615" s="5">
+        <v>67933200000178</v>
+      </c>
+    </row>
+    <row r="616" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>90</v>
       </c>
@@ -20427,8 +22282,11 @@
       <c r="I616" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J616" s="5">
+        <v>28572854000161</v>
+      </c>
+    </row>
+    <row r="617" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>90</v>
       </c>
@@ -20456,8 +22314,11 @@
       <c r="I617" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J617" s="5">
+        <v>13735984000109</v>
+      </c>
+    </row>
+    <row r="618" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>642</v>
       </c>
@@ -20485,8 +22346,11 @@
       <c r="I618" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J618" s="5">
+        <v>1111464000138</v>
+      </c>
+    </row>
+    <row r="619" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>3077</v>
       </c>
@@ -20514,8 +22378,11 @@
       <c r="I619" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J619" s="5">
+        <v>49605254000122</v>
+      </c>
+    </row>
+    <row r="620" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>1019</v>
       </c>
@@ -20544,7 +22411,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>1021</v>
       </c>
@@ -20573,7 +22440,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>2027</v>
       </c>
@@ -20602,7 +22469,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>2041</v>
       </c>
@@ -20631,7 +22498,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>2047</v>
       </c>
@@ -21387,8 +23254,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Pedidos.xlsx
+++ b/Pedidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F0BBE3-CFA1-442E-830B-A26C09ED37BC}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8300597D-7F83-4B24-9AAB-12D82BE896D8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
   </bookViews>
@@ -1666,7 +1666,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="00\.000\.000\/0000\-00"/>
+    <numFmt numFmtId="165" formatCode="00\.000\.000\/0000\-00"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -2153,7 +2153,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2201,7 +2201,7 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="167" formatCode="00\.000\.000\/0000\-00"/>
+      <numFmt numFmtId="165" formatCode="00\.000\.000\/0000\-00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
@@ -22410,6 +22410,9 @@
       <c r="I620" t="s">
         <v>339</v>
       </c>
+      <c r="J620" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="621" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A621">
@@ -22439,6 +22442,9 @@
       <c r="I621" t="s">
         <v>319</v>
       </c>
+      <c r="J621" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="622" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A622">
@@ -22468,6 +22474,9 @@
       <c r="I622" t="s">
         <v>325</v>
       </c>
+      <c r="J622" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="623" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A623">
@@ -22497,6 +22506,9 @@
       <c r="I623" t="s">
         <v>310</v>
       </c>
+      <c r="J623" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="624" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A624">
@@ -22526,8 +22538,11 @@
       <c r="I624" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J624" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>2091</v>
       </c>
@@ -22555,8 +22570,11 @@
       <c r="I625" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J625" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>2778</v>
       </c>
@@ -22584,8 +22602,11 @@
       <c r="I626" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J626" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>293</v>
       </c>
@@ -22613,8 +22634,11 @@
       <c r="I627" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J627" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>3035</v>
       </c>
@@ -22642,8 +22666,11 @@
       <c r="I628" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J628" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>3060</v>
       </c>
@@ -22671,8 +22698,11 @@
       <c r="I629" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J629" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>3064</v>
       </c>
@@ -22700,8 +22730,11 @@
       <c r="I630" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J630" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>3069</v>
       </c>
@@ -22729,8 +22762,11 @@
       <c r="I631" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J631" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>380</v>
       </c>
@@ -22758,8 +22794,11 @@
       <c r="I632" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J632" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>614</v>
       </c>
@@ -22787,8 +22826,11 @@
       <c r="I633" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J633" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>622</v>
       </c>
@@ -22816,8 +22858,11 @@
       <c r="I634" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J634" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>622</v>
       </c>
@@ -22845,8 +22890,11 @@
       <c r="I635" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J635" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>622</v>
       </c>
@@ -22874,8 +22922,11 @@
       <c r="I636" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J636" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>700</v>
       </c>
@@ -22903,8 +22954,11 @@
       <c r="I637" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J637" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>703</v>
       </c>
@@ -22932,8 +22986,11 @@
       <c r="I638" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J638" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>703</v>
       </c>
@@ -22961,8 +23018,11 @@
       <c r="I639" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J639" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>778</v>
       </c>
@@ -22990,8 +23050,11 @@
       <c r="I640" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J640" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>811</v>
       </c>
@@ -23019,8 +23082,11 @@
       <c r="I641" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J641" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>851</v>
       </c>
@@ -23048,8 +23114,11 @@
       <c r="I642" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J642" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>851</v>
       </c>
@@ -23077,8 +23146,11 @@
       <c r="I643" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J643" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>851</v>
       </c>
@@ -23106,8 +23178,11 @@
       <c r="I644" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J644" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>874</v>
       </c>
@@ -23135,8 +23210,11 @@
       <c r="I645" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J645" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>904</v>
       </c>
@@ -23164,8 +23242,11 @@
       <c r="I646" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J646" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>904</v>
       </c>
@@ -23193,8 +23274,11 @@
       <c r="I647" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J647" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>967</v>
       </c>
@@ -23222,8 +23306,11 @@
       <c r="I648" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J648" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>979</v>
       </c>
@@ -23250,6 +23337,9 @@
       </c>
       <c r="I649" t="s">
         <v>314</v>
+      </c>
+      <c r="J649" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Pedidos.xlsx
+++ b/Pedidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00131665-A552-4CC8-99B5-93F54AB947C0}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B2F71CA-201D-41E6-B8F0-DD7991888050}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="549">
   <si>
     <t>Pedido</t>
   </si>
@@ -1664,6 +1664,9 @@
   </si>
   <si>
     <t>COFER IMPORTADORA E DISTRIBUIDORA LT</t>
+  </si>
+  <si>
+    <t>ADERE PRODUTOS</t>
   </si>
 </sst>
 </file>
@@ -2230,8 +2233,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8D7DE48-BC19-48D4-80C5-DD934A925EB7}" name="TabelaPedidos" displayName="TabelaPedidos" ref="A1:J616" totalsRowShown="0">
-  <autoFilter ref="A1:J616" xr:uid="{D8D7DE48-BC19-48D4-80C5-DD934A925EB7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8D7DE48-BC19-48D4-80C5-DD934A925EB7}" name="TabelaPedidos" displayName="TabelaPedidos" ref="A1:J617" totalsRowShown="0">
+  <autoFilter ref="A1:J617" xr:uid="{D8D7DE48-BC19-48D4-80C5-DD934A925EB7}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F779E64C-ADAA-4D54-8902-56E277786201}" name="RC"/>
     <tableColumn id="2" xr3:uid="{C62B1A3A-DDAA-490B-80CE-E589A36EE54C}" name="Pedido"/>
@@ -2565,7 +2568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906ACCD0-13B7-452C-BEC4-FB1DD312FFC4}">
-  <dimension ref="A1:J616"/>
+  <dimension ref="A1:J617"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -22196,6 +22199,35 @@
         <v>197</v>
       </c>
     </row>
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A617">
+        <v>1</v>
+      </c>
+      <c r="B617">
+        <v>999999</v>
+      </c>
+      <c r="C617" t="s">
+        <v>548</v>
+      </c>
+      <c r="D617" t="s">
+        <v>40</v>
+      </c>
+      <c r="E617" t="s">
+        <v>240</v>
+      </c>
+      <c r="F617" t="s">
+        <v>240</v>
+      </c>
+      <c r="G617" t="s">
+        <v>240</v>
+      </c>
+      <c r="H617" s="2">
+        <v>2791.13</v>
+      </c>
+      <c r="I617" t="s">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Pedidos.xlsx
+++ b/Pedidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B2F71CA-201D-41E6-B8F0-DD7991888050}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4470DDDD-B48C-49A2-85CA-3458C4D5D45F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
+    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="1" r:id="rId1"/>
@@ -2210,14 +2210,14 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="165" formatCode="00\.000\.000\/0000\-00"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="165" formatCode="00\.000\.000\/0000\-00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2242,10 +2242,10 @@
     <tableColumn id="4" xr3:uid="{09C6AB47-50A6-4A77-84E1-F9C46CEFB0BA}" name="UF"/>
     <tableColumn id="5" xr3:uid="{60CC8499-AF85-4A3E-B15F-FAC268AEA396}" name="Status"/>
     <tableColumn id="6" xr3:uid="{A7B89925-D806-422B-A861-E9CDD8B38B51}" name="Motivo"/>
-    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{81A912E1-0DAE-4094-8FC5-6F9C3F7FEA4E}" name="Valor (R$)" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{98E6D74D-D3C5-467A-B9E0-46B2439E66AE}" name="Coordenador"/>
-    <tableColumn id="10" xr3:uid="{1413044C-F6B3-417B-90E7-5F6797B59268}" name="CNPJ" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{1413044C-F6B3-417B-90E7-5F6797B59268}" name="CNPJ" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2666,7 +2666,7 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="2">
@@ -2698,7 +2698,7 @@
       <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="2">
@@ -2730,7 +2730,7 @@
       <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H5" s="2">
@@ -2762,7 +2762,7 @@
       <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="2">
@@ -2794,7 +2794,7 @@
       <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="2">
@@ -3754,7 +3754,7 @@
       <c r="F37" t="s">
         <v>14</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H37" s="2">
@@ -3786,7 +3786,7 @@
       <c r="F38" t="s">
         <v>14</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H38" s="2">
@@ -3818,7 +3818,7 @@
       <c r="F39" t="s">
         <v>14</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H39" s="2">
@@ -3850,7 +3850,7 @@
       <c r="F40" t="s">
         <v>14</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H40" s="2">
@@ -3882,7 +3882,7 @@
       <c r="F41" t="s">
         <v>14</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H41" s="2">
@@ -3946,7 +3946,7 @@
       <c r="F43" t="s">
         <v>44</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H43" s="2">
@@ -3978,7 +3978,7 @@
       <c r="F44" t="s">
         <v>14</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="2">
@@ -4010,7 +4010,7 @@
       <c r="F45" t="s">
         <v>14</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H45" s="2">
@@ -4042,7 +4042,7 @@
       <c r="F46" t="s">
         <v>14</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H46" s="2">
@@ -4074,7 +4074,7 @@
       <c r="F47" t="s">
         <v>14</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H47" s="2">
@@ -4106,7 +4106,7 @@
       <c r="F48" t="s">
         <v>14</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H48" s="2">
@@ -4138,7 +4138,7 @@
       <c r="F49" t="s">
         <v>14</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H49" s="2">
@@ -4170,7 +4170,7 @@
       <c r="F50" t="s">
         <v>14</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H50" s="2">
@@ -4202,7 +4202,7 @@
       <c r="F51" t="s">
         <v>14</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H51" s="2">
@@ -4234,7 +4234,7 @@
       <c r="F52" t="s">
         <v>14</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H52" s="2">
@@ -4266,7 +4266,7 @@
       <c r="F53" t="s">
         <v>14</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H53" s="2">
@@ -4298,7 +4298,7 @@
       <c r="F54" t="s">
         <v>14</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G54" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H54" s="2">
@@ -4330,7 +4330,7 @@
       <c r="F55" t="s">
         <v>14</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G55" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H55" s="2">
@@ -4362,7 +4362,7 @@
       <c r="F56" t="s">
         <v>14</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G56" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="2">
@@ -4394,7 +4394,7 @@
       <c r="F57" t="s">
         <v>14</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G57" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H57" s="2">
@@ -4426,7 +4426,7 @@
       <c r="F58" t="s">
         <v>14</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H58" s="2">
@@ -4458,7 +4458,7 @@
       <c r="F59" t="s">
         <v>14</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H59" s="2">
@@ -4490,7 +4490,7 @@
       <c r="F60" t="s">
         <v>14</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H60" s="2">
@@ -4522,7 +4522,7 @@
       <c r="F61" t="s">
         <v>10</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="4">
         <v>46161</v>
       </c>
       <c r="H61" s="2">
@@ -4554,7 +4554,7 @@
       <c r="F62" t="s">
         <v>14</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="2">
@@ -4586,7 +4586,7 @@
       <c r="F63" t="s">
         <v>14</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H63" s="2">
@@ -4618,7 +4618,7 @@
       <c r="F64" t="s">
         <v>14</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="2">
@@ -4650,7 +4650,7 @@
       <c r="F65" t="s">
         <v>14</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H65" s="2">
@@ -4682,7 +4682,7 @@
       <c r="F66" t="s">
         <v>14</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="2">
@@ -4714,7 +4714,7 @@
       <c r="F67" t="s">
         <v>14</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H67" s="2">
@@ -4746,7 +4746,7 @@
       <c r="F68" t="s">
         <v>14</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H68" s="2">
@@ -4778,7 +4778,7 @@
       <c r="F69" t="s">
         <v>14</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H69" s="2">
@@ -4810,7 +4810,7 @@
       <c r="F70" t="s">
         <v>14</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G70" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H70" s="2">
@@ -4842,7 +4842,7 @@
       <c r="F71" t="s">
         <v>14</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H71" s="2">
@@ -4874,7 +4874,7 @@
       <c r="F72" t="s">
         <v>41</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G72" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H72" s="2">
@@ -4906,7 +4906,7 @@
       <c r="F73" t="s">
         <v>44</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H73" s="2">
@@ -4938,7 +4938,7 @@
       <c r="F74" t="s">
         <v>10</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="4">
         <v>46161</v>
       </c>
       <c r="H74" s="2">
@@ -4970,7 +4970,7 @@
       <c r="F75" t="s">
         <v>89</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="4">
         <v>46171</v>
       </c>
       <c r="H75" s="2">
@@ -5002,7 +5002,7 @@
       <c r="F76" t="s">
         <v>26</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="4">
         <v>46157</v>
       </c>
       <c r="H76" s="2">
@@ -5034,7 +5034,7 @@
       <c r="F77" t="s">
         <v>44</v>
       </c>
-      <c r="G77" t="s">
+      <c r="G77" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H77" s="2">
@@ -5066,7 +5066,7 @@
       <c r="F78" t="s">
         <v>44</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G78" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H78" s="2">
@@ -5098,7 +5098,7 @@
       <c r="F79" t="s">
         <v>44</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="4">
         <v>46171</v>
       </c>
       <c r="H79" s="2">
@@ -5130,7 +5130,7 @@
       <c r="F80" t="s">
         <v>26</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="4">
         <v>46157</v>
       </c>
       <c r="H80" s="2">
@@ -5162,7 +5162,7 @@
       <c r="F81" t="s">
         <v>41</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="4">
         <v>46171</v>
       </c>
       <c r="H81" s="2">
@@ -5194,7 +5194,7 @@
       <c r="F82" t="s">
         <v>44</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="4">
         <v>46171</v>
       </c>
       <c r="H82" s="2">
@@ -5226,7 +5226,7 @@
       <c r="F83" t="s">
         <v>26</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="4">
         <v>46157</v>
       </c>
       <c r="H83" s="2">
@@ -5258,7 +5258,7 @@
       <c r="F84" t="s">
         <v>14</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H84" s="2">
@@ -5290,7 +5290,7 @@
       <c r="F85" t="s">
         <v>14</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G85" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H85" s="2">
@@ -5322,7 +5322,7 @@
       <c r="F86" t="s">
         <v>10</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="4">
         <v>46161</v>
       </c>
       <c r="H86" s="2">
@@ -5354,7 +5354,7 @@
       <c r="F87" t="s">
         <v>26</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="4">
         <v>46157</v>
       </c>
       <c r="H87" s="2">
@@ -5386,7 +5386,7 @@
       <c r="F88" t="s">
         <v>44</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G88" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H88" s="2">
@@ -5514,7 +5514,7 @@
       <c r="F92" t="s">
         <v>14</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G92" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H92" s="2">
@@ -5546,7 +5546,7 @@
       <c r="F93" t="s">
         <v>14</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G93" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H93" s="2">
@@ -5610,7 +5610,7 @@
       <c r="F95" t="s">
         <v>14</v>
       </c>
-      <c r="G95" t="s">
+      <c r="G95" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H95" s="2">
@@ -5674,7 +5674,7 @@
       <c r="F97" t="s">
         <v>14</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G97" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="2">
@@ -5770,7 +5770,7 @@
       <c r="F100" t="s">
         <v>14</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G100" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H100" s="2">
@@ -5802,7 +5802,7 @@
       <c r="F101" t="s">
         <v>14</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="2">
@@ -5866,7 +5866,7 @@
       <c r="F103" t="s">
         <v>14</v>
       </c>
-      <c r="G103" t="s">
+      <c r="G103" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H103" s="2">
@@ -5994,7 +5994,7 @@
       <c r="F107" t="s">
         <v>26</v>
       </c>
-      <c r="G107">
+      <c r="G107" s="4">
         <v>46157</v>
       </c>
       <c r="H107" s="2">
@@ -6026,7 +6026,7 @@
       <c r="F108" t="s">
         <v>14</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G108" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H108" s="2">
@@ -6122,7 +6122,7 @@
       <c r="F111" t="s">
         <v>14</v>
       </c>
-      <c r="G111" t="s">
+      <c r="G111" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H111" s="2">
@@ -6154,7 +6154,7 @@
       <c r="F112" t="s">
         <v>14</v>
       </c>
-      <c r="G112" t="s">
+      <c r="G112" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H112" s="2">
@@ -6186,7 +6186,7 @@
       <c r="F113" t="s">
         <v>10</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G113" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H113" s="2">
@@ -6218,7 +6218,7 @@
       <c r="F114" t="s">
         <v>14</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G114" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H114" s="2">
@@ -6250,7 +6250,7 @@
       <c r="F115" t="s">
         <v>14</v>
       </c>
-      <c r="G115" t="s">
+      <c r="G115" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H115" s="2">
@@ -6314,7 +6314,7 @@
       <c r="F117" t="s">
         <v>26</v>
       </c>
-      <c r="G117">
+      <c r="G117" s="4">
         <v>46157</v>
       </c>
       <c r="H117" s="2">
@@ -6346,7 +6346,7 @@
       <c r="F118" t="s">
         <v>26</v>
       </c>
-      <c r="G118">
+      <c r="G118" s="4">
         <v>46157</v>
       </c>
       <c r="H118" s="2">
@@ -6378,7 +6378,7 @@
       <c r="F119" t="s">
         <v>26</v>
       </c>
-      <c r="G119">
+      <c r="G119" s="4">
         <v>46157</v>
       </c>
       <c r="H119" s="2">
@@ -6442,7 +6442,7 @@
       <c r="F121" t="s">
         <v>41</v>
       </c>
-      <c r="G121">
+      <c r="G121" s="4">
         <v>46160</v>
       </c>
       <c r="H121" s="2">
@@ -6538,7 +6538,7 @@
       <c r="F124" t="s">
         <v>26</v>
       </c>
-      <c r="G124">
+      <c r="G124" s="4">
         <v>46157</v>
       </c>
       <c r="H124" s="2">
@@ -6666,7 +6666,7 @@
       <c r="F128" t="s">
         <v>97</v>
       </c>
-      <c r="G128">
+      <c r="G128" s="4">
         <v>46158</v>
       </c>
       <c r="H128" s="2">
@@ -6794,7 +6794,7 @@
       <c r="F132" t="s">
         <v>26</v>
       </c>
-      <c r="G132">
+      <c r="G132" s="4">
         <v>46157</v>
       </c>
       <c r="H132" s="2">
@@ -6890,7 +6890,7 @@
       <c r="F135" t="s">
         <v>44</v>
       </c>
-      <c r="G135">
+      <c r="G135" s="4">
         <v>46171</v>
       </c>
       <c r="H135" s="2">
@@ -6922,7 +6922,7 @@
       <c r="F136" t="s">
         <v>20</v>
       </c>
-      <c r="G136">
+      <c r="G136" s="4">
         <v>46158</v>
       </c>
       <c r="H136" s="2">
@@ -6986,7 +6986,7 @@
       <c r="F138" t="s">
         <v>26</v>
       </c>
-      <c r="G138">
+      <c r="G138" s="4">
         <v>46157</v>
       </c>
       <c r="H138" s="2">
@@ -7210,7 +7210,7 @@
       <c r="F145" t="s">
         <v>44</v>
       </c>
-      <c r="G145">
+      <c r="G145" s="4">
         <v>46167</v>
       </c>
       <c r="H145" s="2">
@@ -7242,7 +7242,7 @@
       <c r="F146" t="s">
         <v>44</v>
       </c>
-      <c r="G146" t="s">
+      <c r="G146" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H146" s="2">
@@ -7274,7 +7274,7 @@
       <c r="F147" t="s">
         <v>10</v>
       </c>
-      <c r="G147">
+      <c r="G147" s="4">
         <v>46164</v>
       </c>
       <c r="H147" s="2">
@@ -7402,7 +7402,7 @@
       <c r="F151" t="s">
         <v>44</v>
       </c>
-      <c r="G151" t="s">
+      <c r="G151" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H151" s="2">
@@ -7434,7 +7434,7 @@
       <c r="F152" t="s">
         <v>14</v>
       </c>
-      <c r="G152" t="s">
+      <c r="G152" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H152" s="2">
@@ -7818,7 +7818,7 @@
       <c r="F164" t="s">
         <v>26</v>
       </c>
-      <c r="G164">
+      <c r="G164" s="4">
         <v>46157</v>
       </c>
       <c r="H164" s="2">
@@ -7850,7 +7850,7 @@
       <c r="F165" t="s">
         <v>26</v>
       </c>
-      <c r="G165">
+      <c r="G165" s="4">
         <v>46157</v>
       </c>
       <c r="H165" s="2">
@@ -8138,7 +8138,7 @@
       <c r="F174" t="s">
         <v>14</v>
       </c>
-      <c r="G174" t="s">
+      <c r="G174" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H174" s="2">
@@ -10666,7 +10666,7 @@
       <c r="F253" t="s">
         <v>14</v>
       </c>
-      <c r="G253" t="s">
+      <c r="G253" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H253" s="2">
@@ -13514,7 +13514,7 @@
       <c r="F342" t="s">
         <v>14</v>
       </c>
-      <c r="G342" t="s">
+      <c r="G342" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H342" s="2">
@@ -14314,7 +14314,7 @@
       <c r="F367" t="s">
         <v>26</v>
       </c>
-      <c r="G367">
+      <c r="G367" s="4">
         <v>46157</v>
       </c>
       <c r="H367" s="2">
@@ -14474,7 +14474,7 @@
       <c r="F372" t="s">
         <v>69</v>
       </c>
-      <c r="G372">
+      <c r="G372" s="4">
         <v>46158</v>
       </c>
       <c r="H372" s="2">
@@ -16138,7 +16138,7 @@
       <c r="F424" t="s">
         <v>26</v>
       </c>
-      <c r="G424">
+      <c r="G424" s="4">
         <v>46157</v>
       </c>
       <c r="H424" s="2">
@@ -21066,7 +21066,7 @@
       <c r="F578" t="s">
         <v>26</v>
       </c>
-      <c r="G578">
+      <c r="G578" s="4">
         <v>46157</v>
       </c>
       <c r="H578" s="2">
@@ -21194,7 +21194,7 @@
       <c r="F582" t="s">
         <v>26</v>
       </c>
-      <c r="G582">
+      <c r="G582" s="4">
         <v>46157</v>
       </c>
       <c r="H582" s="2">
@@ -21290,7 +21290,7 @@
       <c r="F585" t="s">
         <v>240</v>
       </c>
-      <c r="G585" t="s">
+      <c r="G585" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H585" s="2">
@@ -21319,7 +21319,7 @@
       <c r="F586" t="s">
         <v>240</v>
       </c>
-      <c r="G586" t="s">
+      <c r="G586" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H586" s="2">
@@ -21348,7 +21348,7 @@
       <c r="F587" t="s">
         <v>240</v>
       </c>
-      <c r="G587" t="s">
+      <c r="G587" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H587" s="2">
@@ -21377,7 +21377,7 @@
       <c r="F588" t="s">
         <v>240</v>
       </c>
-      <c r="G588" t="s">
+      <c r="G588" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H588" s="2">
@@ -21406,7 +21406,7 @@
       <c r="F589" t="s">
         <v>240</v>
       </c>
-      <c r="G589" t="s">
+      <c r="G589" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H589" s="2">
@@ -21435,7 +21435,7 @@
       <c r="F590" t="s">
         <v>240</v>
       </c>
-      <c r="G590" t="s">
+      <c r="G590" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H590" s="2">
@@ -21464,7 +21464,7 @@
       <c r="F591" t="s">
         <v>240</v>
       </c>
-      <c r="G591" t="s">
+      <c r="G591" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H591" s="2">
@@ -21493,7 +21493,7 @@
       <c r="F592" t="s">
         <v>240</v>
       </c>
-      <c r="G592" t="s">
+      <c r="G592" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H592" s="2">
@@ -21522,7 +21522,7 @@
       <c r="F593" t="s">
         <v>240</v>
       </c>
-      <c r="G593" t="s">
+      <c r="G593" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H593" s="2">
@@ -21551,7 +21551,7 @@
       <c r="F594" t="s">
         <v>240</v>
       </c>
-      <c r="G594" t="s">
+      <c r="G594" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H594" s="2">
@@ -21580,7 +21580,7 @@
       <c r="F595" t="s">
         <v>240</v>
       </c>
-      <c r="G595" t="s">
+      <c r="G595" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H595" s="2">
@@ -21609,7 +21609,7 @@
       <c r="F596" t="s">
         <v>240</v>
       </c>
-      <c r="G596" t="s">
+      <c r="G596" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H596" s="2">
@@ -21638,7 +21638,7 @@
       <c r="F597" t="s">
         <v>240</v>
       </c>
-      <c r="G597" t="s">
+      <c r="G597" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H597" s="2">
@@ -21667,7 +21667,7 @@
       <c r="F598" t="s">
         <v>240</v>
       </c>
-      <c r="G598" t="s">
+      <c r="G598" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H598" s="2">
@@ -21696,7 +21696,7 @@
       <c r="F599" t="s">
         <v>240</v>
       </c>
-      <c r="G599" t="s">
+      <c r="G599" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H599" s="2">
@@ -21725,7 +21725,7 @@
       <c r="F600" t="s">
         <v>240</v>
       </c>
-      <c r="G600" t="s">
+      <c r="G600" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H600" s="2">
@@ -21754,7 +21754,7 @@
       <c r="F601" t="s">
         <v>240</v>
       </c>
-      <c r="G601" t="s">
+      <c r="G601" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H601" s="2">
@@ -21783,7 +21783,7 @@
       <c r="F602" t="s">
         <v>240</v>
       </c>
-      <c r="G602" t="s">
+      <c r="G602" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H602" s="2">
@@ -21812,7 +21812,7 @@
       <c r="F603" t="s">
         <v>240</v>
       </c>
-      <c r="G603" t="s">
+      <c r="G603" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H603" s="2">
@@ -21841,7 +21841,7 @@
       <c r="F604" t="s">
         <v>240</v>
       </c>
-      <c r="G604" t="s">
+      <c r="G604" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H604" s="2">
@@ -21870,7 +21870,7 @@
       <c r="F605" t="s">
         <v>240</v>
       </c>
-      <c r="G605" t="s">
+      <c r="G605" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H605" s="2">
@@ -21899,7 +21899,7 @@
       <c r="F606" t="s">
         <v>240</v>
       </c>
-      <c r="G606" t="s">
+      <c r="G606" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H606" s="2">
@@ -21928,7 +21928,7 @@
       <c r="F607" t="s">
         <v>240</v>
       </c>
-      <c r="G607" t="s">
+      <c r="G607" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H607" s="2">
@@ -21957,7 +21957,7 @@
       <c r="F608" t="s">
         <v>240</v>
       </c>
-      <c r="G608" t="s">
+      <c r="G608" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H608" s="2">
@@ -21986,7 +21986,7 @@
       <c r="F609" t="s">
         <v>240</v>
       </c>
-      <c r="G609" t="s">
+      <c r="G609" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H609" s="2">
@@ -22015,7 +22015,7 @@
       <c r="F610" t="s">
         <v>240</v>
       </c>
-      <c r="G610" t="s">
+      <c r="G610" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H610" s="2">
@@ -22044,7 +22044,7 @@
       <c r="F611" t="s">
         <v>240</v>
       </c>
-      <c r="G611" t="s">
+      <c r="G611" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H611" s="2">
@@ -22073,7 +22073,7 @@
       <c r="F612" t="s">
         <v>240</v>
       </c>
-      <c r="G612" t="s">
+      <c r="G612" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H612" s="2">
@@ -22102,7 +22102,7 @@
       <c r="F613" t="s">
         <v>240</v>
       </c>
-      <c r="G613" t="s">
+      <c r="G613" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H613" s="2">
@@ -22131,7 +22131,7 @@
       <c r="F614" t="s">
         <v>240</v>
       </c>
-      <c r="G614" t="s">
+      <c r="G614" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H614" s="2">
@@ -22160,7 +22160,7 @@
       <c r="F615" t="s">
         <v>240</v>
       </c>
-      <c r="G615" t="s">
+      <c r="G615" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H615" s="2">
@@ -22189,7 +22189,7 @@
       <c r="F616" t="s">
         <v>240</v>
       </c>
-      <c r="G616" t="s">
+      <c r="G616" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H616" s="2">
@@ -22218,7 +22218,7 @@
       <c r="F617" t="s">
         <v>240</v>
       </c>
-      <c r="G617" t="s">
+      <c r="G617" s="4" t="s">
         <v>240</v>
       </c>
       <c r="H617" s="2">

--- a/Pedidos.xlsx
+++ b/Pedidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4470DDDD-B48C-49A2-85CA-3458C4D5D45F}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:9_{4A0A5F48-BC78-4120-95F7-B25EAF1D8D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E61DA14C-D41F-4EE3-B5C6-0168436C7129}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{1DA860D1-A447-45C6-AE58-962A8B346265}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="549">
   <si>
     <t>Pedido</t>
   </si>
@@ -2210,14 +2210,14 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="165" formatCode="00\.000\.000\/0000\-00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="00\.000\.000\/0000\-00"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2242,10 +2242,10 @@
     <tableColumn id="4" xr3:uid="{09C6AB47-50A6-4A77-84E1-F9C46CEFB0BA}" name="UF"/>
     <tableColumn id="5" xr3:uid="{60CC8499-AF85-4A3E-B15F-FAC268AEA396}" name="Status"/>
     <tableColumn id="6" xr3:uid="{A7B89925-D806-422B-A861-E9CDD8B38B51}" name="Motivo"/>
-    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{38FF8D10-D08F-4051-BA81-A33FD05D81FE}" name="Previsão" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{81A912E1-0DAE-4094-8FC5-6F9C3F7FEA4E}" name="Valor (R$)" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{98E6D74D-D3C5-467A-B9E0-46B2439E66AE}" name="Coordenador"/>
-    <tableColumn id="10" xr3:uid="{1413044C-F6B3-417B-90E7-5F6797B59268}" name="CNPJ" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{1413044C-F6B3-417B-90E7-5F6797B59268}" name="CNPJ" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -22213,13 +22213,13 @@
         <v>40</v>
       </c>
       <c r="E617" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="F617" t="s">
-        <v>240</v>
-      </c>
-      <c r="G617" s="4" t="s">
-        <v>240</v>
+        <v>193</v>
+      </c>
+      <c r="G617" s="4">
+        <v>46157</v>
       </c>
       <c r="H617" s="2">
         <v>2791.13</v>
